--- a/deliverables/Berka_TakeHome_Submission.xlsx
+++ b/deliverables/Berka_TakeHome_Submission.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T10:44:07+00:00</t>
+          <t>2026-10-22T10:55:22+00:00</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>95de493</t>
+          <t>b11c23f</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>make up &amp;&amp; make all (about 6 minutes end to end)</t>
+          <t>make up &amp;&amp; make all -- 4m28s end to end from an empty database</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>partner_bank and partner_account are both NULL; operation = NULL</t>
+          <t>partner_bank and partner_account are both NULL; operation = VKLAD</t>
         </is>
       </c>
     </row>
@@ -2593,19 +2593,19 @@
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>SELECT region, count(*) AS client_count, round(100.0 * count(*) / sum(count(*)) OVER (), 2) AS pct_of_clients FROM ai.client GROUP BY region ORDER BY client_count DESC, region</t>
+          <t>SELECT region, count(*) AS client_count FROM ai.client GROUP BY region ORDER BY client_count DESC, region</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>region=south Moravia | client_count=937 | pct_of_clients=17.45
-region=north Moravia | client_count=920 | pct_of_clients=17.14
-region=central Bohemia | client_count=664 | pct_of_clients=12.37
-region=Prague | client_count=663 | pct_of_clients=12.35
-region=east Bohemia | client_count=660 | pct_of_clients=12.29
-region=north Bohemia | client_count=561 | pct_of_clients=10.45
-region=west Bohemia | client_count=515 | pct_of_clients=9.59
-region=south Bohemia | client_count=449 | pct_of_clients=8.36</t>
+          <t>region=south Moravia | client_count=937
+region=north Moravia | client_count=920
+region=central Bohemia | client_count=664
+region=Prague | client_count=663
+region=east Bohemia | client_count=660
+region=north Bohemia | client_count=561
+region=west Bohemia | client_count=515
+region=south Bohemia | client_count=449</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
@@ -2859,21 +2859,21 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>SELECT t.account_district_id, t.account_district_name, t.account_region, SUM(t.amount) AS incoming_amount_czk, COUNT(*) AS credit_posting_count, COUNT(DISTINCT t.account_id) AS accounts_with_credits FROM ai.transaction t WHERE t.direction = 'credit' AND t.trans_date &gt;= DATE '1997-01-01' AND t.trans_date &lt; DATE '1998-01-01' GROUP BY t.account_district_id, t.account_district_name, t.account_region ORDER BY incoming_amount_czk DESC, t.account_district_name ASC LIMIT 10</t>
+          <t>SELECT account_district_id AS district_id, account_district_name AS district_name, account_region AS region, sum(amount) AS total_incoming_amount, count(*) AS credit_posting_count, count(DISTINCT account_id) AS account_count FROM ai.transaction WHERE direction = 'credit' AND trans_date &gt;= DATE '1997-01-01' AND trans_date &lt; DATE '1998-01-01' GROUP BY account_district_id, account_district_name, account_region ORDER BY sum(amount) DESC, account_district_id LIMIT 10</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>account_district_id=1 | account_district_name=Hl.m. Praha | account_region=Prague | incoming_amount_czk=115130200.1 | credit_posting_count=13611 | accounts_with_credits=554
-account_district_id=70 | account_district_name=Karvina | account_region=north Moravia | incoming_amount_czk=28506437.1 | credit_posting_count=3802 | accounts_with_credits=152
-account_district_id=74 | account_district_name=Ostrava - mesto | account_region=north Moravia | incoming_amount_czk=27689271.9 | credit_posting_count=3378 | accounts_with_credits=135
-account_district_id=54 | account_district_name=Brno - mesto | account_region=south Moravia | incoming_amount_czk=23095083.4 | credit_posting_count=3041 | accounts_with_credits=128
-account_district_id=64 | account_district_name=Zlin | account_region=south Moravia | incoming_amount_czk=19723168.5 | credit_posting_count=2299 | accounts_with_credits=92
-account_district_id=68 | account_district_name=Frydek - Mistek | account_region=north Moravia | incoming_amount_czk=19087598.8 | credit_posting_count=2006 | accounts_with_credits=83
-account_district_id=72 | account_district_name=Olomouc | account_region=north Moravia | incoming_amount_czk=15916397.0 | credit_posting_count=2129 | accounts_with_credits=88
-account_district_id=5 | account_district_name=Kolin | account_region=central Bohemia | incoming_amount_czk=14471603.6 | credit_posting_count=1542 | accounts_with_credits=65
-account_district_id=52 | account_district_name=Usti nad Orlici | account_region=east Bohemia | incoming_amount_czk=14085167.4 | credit_posting_count=1431 | accounts_with_credits=57
-account_district_id=19 | account_district_name=Prachatice | account_region=south Bohemia | incoming_amount_czk=12163147.0 | credit_posting_count=1359 | accounts_with_credits=55</t>
+          <t>district_id=1 | district_name=Hl.m. Praha | region=Prague | total_incoming_amount=115130200.1 | credit_posting_count=13611 | account_count=554
+district_id=70 | district_name=Karvina | region=north Moravia | total_incoming_amount=28506437.1 | credit_posting_count=3802 | account_count=152
+district_id=74 | district_name=Ostrava - mesto | region=north Moravia | total_incoming_amount=27689271.9 | credit_posting_count=3378 | account_count=135
+district_id=54 | district_name=Brno - mesto | region=south Moravia | total_incoming_amount=23095083.4 | credit_posting_count=3041 | account_count=128
+district_id=64 | district_name=Zlin | region=south Moravia | total_incoming_amount=19723168.5 | credit_posting_count=2299 | account_count=92
+district_id=68 | district_name=Frydek - Mistek | region=north Moravia | total_incoming_amount=19087598.8 | credit_posting_count=2006 | account_count=83
+district_id=72 | district_name=Olomouc | region=north Moravia | total_incoming_amount=15916397.0 | credit_posting_count=2129 | account_count=88
+district_id=5 | district_name=Kolin | region=central Bohemia | total_incoming_amount=14471603.6 | credit_posting_count=1542 | account_count=65
+district_id=52 | district_name=Usti nad Orlici | region=east Bohemia | total_incoming_amount=14085167.4 | credit_posting_count=1431 | account_count=57
+district_id=19 | district_name=Prachatice | region=south Bohemia | total_incoming_amount=12163147.0 | credit_posting_count=1359 | account_count=55</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>SELECT c.year_month AS month, c.month_start AS month_start, COUNT(a.account_id) AS new_accounts FROM ai.calendar c LEFT JOIN ai.account a ON a.open_date = c.date_key WHERE c.year = 1996 GROUP BY c.year_month, c.month_start ORDER BY c.month_start</t>
+          <t>SELECT c.year_month AS month, c.month_start AS month_start, count(a.account_id) AS new_accounts FROM ai.calendar c LEFT JOIN ai.account a ON a.open_date = c.date_key WHERE c.year = 1996 GROUP BY c.year_month, c.month_start ORDER BY c.month_start</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -3015,15 +3015,15 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>SELECT loan_status, status_code, count(*) AS loan_count, round(avg(owner_age_at_loan_start), 2) AS average_age_at_loan_start, count(*) FILTER (WHERE data_quality_flags @&gt; ARRAY['val_owner_age_at_loan_start']) AS under_15_flagged_loans, round(avg(owner_age_at_loan_start) FILTER (WHERE NOT (data_quality_flags @&gt; ARRAY['val_owner_age_at_loan_start'])), 2) AS average_age_excluding_flagged FROM ai.loan GROUP BY loan_status, status_code ORDER BY status_code</t>
+          <t>SELECT loan_status, count(*) AS loan_count, round(avg(owner_age_at_loan_start), 2) AS average_age_at_loan_start, count(*) FILTER (WHERE 'val_owner_age_at_loan_start' = ANY(data_quality_flags)) AS flagged_under_15_loans, round(avg(owner_age_at_loan_start) FILTER (WHERE NOT ('val_owner_age_at_loan_start' = ANY(data_quality_flags))), 2) AS average_age_excluding_flagged FROM ai.loan GROUP BY loan_status ORDER BY loan_status</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>loan_status=finished, paid in full | status_code=A | loan_count=203 | average_age_at_loan_start=37.07 | under_15_flagged_loans=4 | average_age_excluding_flagged=37.53
-loan_status=finished, unpaid (default) | status_code=B | loan_count=31 | average_age_at_loan_start=39.61 | under_15_flagged_loans=0 | average_age_excluding_flagged=39.61
-loan_status=running, no problem | status_code=C | loan_count=403 | average_age_at_loan_start=38.7 | under_15_flagged_loans=2 | average_age_excluding_flagged=38.82
-loan_status=running, client in debt | status_code=D | loan_count=45 | average_age_at_loan_start=37.0 | under_15_flagged_loans=0 | average_age_excluding_flagged=37.0</t>
+          <t>loan_status=finished, paid in full | loan_count=203 | average_age_at_loan_start=37.07 | flagged_under_15_loans=4 | average_age_excluding_flagged=37.53
+loan_status=finished, unpaid (default) | loan_count=31 | average_age_at_loan_start=39.61 | flagged_under_15_loans=0 | average_age_excluding_flagged=39.61
+loan_status=running, client in debt | loan_count=45 | average_age_at_loan_start=37.0 | flagged_under_15_loans=0 | average_age_excluding_flagged=37.0
+loan_status=running, no problem | loan_count=403 | average_age_at_loan_start=38.7 | flagged_under_15_loans=2 | average_age_excluding_flagged=38.82</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
@@ -3076,13 +3076,13 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>SELECT owner_gender AS gender, count(*) AS owner_count, sum(count(*)) OVER () AS total_gold_owners, round(100.0 * count(*) / sum(count(*)) OVER (), 2) AS share_pct FROM ai.account_owner WHERE owner_card_type = 'gold' GROUP BY owner_gender ORDER BY owner_gender</t>
+          <t>SELECT owner_gender AS gender, count(*) AS owner_count, round(100.0 * count(*) / sum(count(*)) OVER (), 2) AS share_pct, sum(count(*)) OVER () AS total_gold_card_owners FROM ai.account_owner WHERE owner_card_type = 'gold' GROUP BY owner_gender ORDER BY owner_gender</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>gender=female | owner_count=35 | total_gold_owners=88.0 | share_pct=39.77
-gender=male | owner_count=53 | total_gold_owners=88.0 | share_pct=60.23</t>
+          <t>gender=female | owner_count=35 | share_pct=39.77 | total_gold_card_owners=88.0
+gender=male | owner_count=53 | share_pct=60.23 | total_gold_card_owners=88.0</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
@@ -3138,12 +3138,12 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>SELECT round(avg(closing_balance), 2) AS average_month_end_balance, count(*) AS accounts_with_balance, count(*) FILTER (WHERE is_carried_forward) AS carried_forward_balances, count(*) FILTER (WHERE 'con_balance_reconciliation_material' = ANY(account_data_quality_flags)) AS accounts_with_reconciliation_flag FROM ai.account_month_end_balance WHERE month_end_date = DATE '1998-12-31'</t>
+          <t>SELECT round(avg(closing_balance), 2) AS average_month_end_balance, count(*) AS accounts_with_balance, count(*) FILTER (WHERE is_carried_forward) AS carried_forward_balances FROM ai.account_month_end_balance WHERE month_end_date = DATE '1998-12-31'</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>average_month_end_balance=43808.94 | accounts_with_balance=4500 | carried_forward_balances=76 | accounts_with_reconciliation_flag=55</t>
+          <t>average_month_end_balance=43808.94 | accounts_with_balance=4500 | carried_forward_balances=76</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
@@ -3413,11 +3413,6 @@
           <t>client_count</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>pct_of_clients</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
@@ -3428,9 +3423,6 @@
       <c r="B17" s="15" t="n">
         <v>937</v>
       </c>
-      <c r="C17" s="15" t="n">
-        <v>17.45</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
@@ -3441,9 +3433,6 @@
       <c r="B18" s="15" t="n">
         <v>920</v>
       </c>
-      <c r="C18" s="15" t="n">
-        <v>17.14</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
@@ -3454,9 +3443,6 @@
       <c r="B19" s="15" t="n">
         <v>664</v>
       </c>
-      <c r="C19" s="15" t="n">
-        <v>12.37</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
@@ -3467,9 +3453,6 @@
       <c r="B20" s="15" t="n">
         <v>663</v>
       </c>
-      <c r="C20" s="15" t="n">
-        <v>12.35</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
@@ -3480,9 +3463,6 @@
       <c r="B21" s="15" t="n">
         <v>660</v>
       </c>
-      <c r="C21" s="15" t="n">
-        <v>12.29</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
@@ -3493,9 +3473,6 @@
       <c r="B22" s="15" t="n">
         <v>561</v>
       </c>
-      <c r="C22" s="15" t="n">
-        <v>10.45</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
@@ -3506,9 +3483,6 @@
       <c r="B23" s="15" t="n">
         <v>515</v>
       </c>
-      <c r="C23" s="15" t="n">
-        <v>9.59</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
@@ -3518,9 +3492,6 @@
       </c>
       <c r="B24" s="15" t="n">
         <v>449</v>
-      </c>
-      <c r="C24" s="15" t="n">
-        <v>8.359999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -4333,22 +4304,22 @@
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>account_district_id</t>
+          <t>district_id</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>account_district_name</t>
+          <t>district_name</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>account_region</t>
+          <t>region</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>incoming_amount_czk</t>
+          <t>total_incoming_amount</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -4358,7 +4329,7 @@
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>accounts_with_credits</t>
+          <t>account_count</t>
         </is>
       </c>
     </row>
@@ -5232,25 +5203,20 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>status_code</t>
+          <t>loan_count</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>loan_count</t>
+          <t>average_age_at_loan_start</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>average_age_at_loan_start</t>
+          <t>flagged_under_15_loans</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
-        <is>
-          <t>under_15_flagged_loans</t>
-        </is>
-      </c>
-      <c r="F142" s="5" t="inlineStr">
         <is>
           <t>average_age_excluding_flagged</t>
         </is>
@@ -5262,21 +5228,16 @@
           <t>finished, paid in full</t>
         </is>
       </c>
-      <c r="B143" s="15" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+      <c r="B143" s="15" t="n">
+        <v>203</v>
       </c>
       <c r="C143" s="15" t="n">
-        <v>203</v>
+        <v>37.07</v>
       </c>
       <c r="D143" s="15" t="n">
-        <v>37.07</v>
+        <v>4</v>
       </c>
       <c r="E143" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F143" s="15" t="n">
         <v>37.53</v>
       </c>
     </row>
@@ -5286,70 +5247,55 @@
           <t>finished, unpaid (default)</t>
         </is>
       </c>
-      <c r="B144" s="15" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
+      <c r="B144" s="15" t="n">
+        <v>31</v>
       </c>
       <c r="C144" s="15" t="n">
-        <v>31</v>
+        <v>39.61</v>
       </c>
       <c r="D144" s="15" t="n">
-        <v>39.61</v>
+        <v>0</v>
       </c>
       <c r="E144" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F144" s="15" t="n">
         <v>39.61</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="15" t="inlineStr">
         <is>
-          <t>running, no problem</t>
-        </is>
-      </c>
-      <c r="B145" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
+          <t>running, client in debt</t>
+        </is>
+      </c>
+      <c r="B145" s="15" t="n">
+        <v>45</v>
       </c>
       <c r="C145" s="15" t="n">
-        <v>403</v>
+        <v>37</v>
       </c>
       <c r="D145" s="15" t="n">
-        <v>38.7</v>
+        <v>0</v>
       </c>
       <c r="E145" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="F145" s="15" t="n">
-        <v>38.82</v>
+        <v>37</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="15" t="inlineStr">
         <is>
-          <t>running, client in debt</t>
-        </is>
-      </c>
-      <c r="B146" s="15" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
+          <t>running, no problem</t>
+        </is>
+      </c>
+      <c r="B146" s="15" t="n">
+        <v>403</v>
       </c>
       <c r="C146" s="15" t="n">
-        <v>45</v>
+        <v>38.7</v>
       </c>
       <c r="D146" s="15" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="E146" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F146" s="15" t="n">
-        <v>37</v>
+        <v>38.82</v>
       </c>
     </row>
     <row r="149">
@@ -5440,12 +5386,12 @@
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>total_gold_owners</t>
+          <t>share_pct</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>share_pct</t>
+          <t>total_gold_card_owners</t>
         </is>
       </c>
     </row>
@@ -5459,10 +5405,10 @@
         <v>35</v>
       </c>
       <c r="C157" s="15" t="n">
+        <v>39.77</v>
+      </c>
+      <c r="D157" s="15" t="n">
         <v>88</v>
-      </c>
-      <c r="D157" s="15" t="n">
-        <v>39.77</v>
       </c>
     </row>
     <row r="158">
@@ -5475,10 +5421,10 @@
         <v>53</v>
       </c>
       <c r="C158" s="15" t="n">
+        <v>60.23</v>
+      </c>
+      <c r="D158" s="15" t="n">
         <v>88</v>
-      </c>
-      <c r="D158" s="15" t="n">
-        <v>60.23</v>
       </c>
     </row>
     <row r="161">
@@ -5586,11 +5532,6 @@
           <t>carried_forward_balances</t>
         </is>
       </c>
-      <c r="D167" s="5" t="inlineStr">
-        <is>
-          <t>accounts_with_reconciliation_flag</t>
-        </is>
-      </c>
     </row>
     <row r="168">
       <c r="A168" s="15" t="n">
@@ -5601,9 +5542,6 @@
       </c>
       <c r="C168" s="15" t="n">
         <v>76</v>
-      </c>
-      <c r="D168" s="15" t="n">
-        <v>55</v>
       </c>
     </row>
     <row r="171">
@@ -10916,7 +10854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11438,6 +11376,402 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>workbook</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>make workbook</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:44:08+00:00</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>make zip</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:45:18+00:00</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>{"files": 74, "size_kb": 469.7}</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>ddr</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>make ddr</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:47:20+00:00</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>{"words": 1520, "pages": 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>make zip</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:49:22+00:00</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>{"files": 79, "size_kb": 483.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>ingest</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>make ingest</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:50:34+00:00</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>{"run_id": "bd7b7fd2-e741-459c-90ed-f1ce8a1b4fc8", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>make profile</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:51:36+00:00</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>dq</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>make dq (dataset=stg)</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:51:53+00:00</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>{"run_id": "55ac5752-e529-4ad3-b3b6-2723e5a50227", "dataset": "stg", "rules_executed": 123, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 16.24, "defect_types": 14}</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>make model</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:52:04+00:00</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 27, "problems": [], "reconciliation_checks": 9}</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>entitlements</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>make entitlements</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:52:05+00:00</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>make reference</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:52:05+00:00</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>{"questions": 10, "failures": []}</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>make semantic</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:52:07+00:00</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>{"entities": 11, "columns": 100, "context_pack_chars": 27592, "problems": []}</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>entitlements</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>make entitlements</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:52:08+00:00</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>questions</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>make questions (provider=claude_cli, model=claude-sonnet-5-5)</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:54:03+00:00</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>{"answered": 10, "total": 10, "answered_first_attempt": 10, "run_as": "cro_global"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>evaluate</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>make evaluate</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:54:04+00:00</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>{"tally": {"match": 10}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>workbook</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>make workbook</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:54:55+00:00</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>ddr</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>make ddr</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:54:57+00:00</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>{"words": 1520, "pages": 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>make zip</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:54:57+00:00</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>{"files": 79, "size_kb": 482.3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>ddr</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>make ddr</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:55:21+00:00</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>{"words": 1527, "pages": 2}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/deliverables/Berka_TakeHome_Submission.xlsx
+++ b/deliverables/Berka_TakeHome_Submission.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T10:55:22+00:00</t>
+          <t>2026-10-22T21:58:03+00:00</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>b11c23f</t>
+          <t>70f19af</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>114 passing</t>
+          <t>135 passing</t>
         </is>
       </c>
     </row>
@@ -5753,7 +5753,7 @@
     <row r="2" ht="46" customHeight="1">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>88 hand-written rules, plus a completeness sweep that expands to one rule per column of every table at run time (123 executed in total). The loader refuses to run a rule that lacks a severity, a justification or the list of questions it affects. Results per run are in the dq.results table and dq/results/dq_report.md.</t>
+          <t>88 hand-written rules, plus a completeness sweep that expands to one rule per column of every table at run time (123 executed in the last run). The loader refuses to run a rule that lacks a severity, a justification or the list of questions it affects. Results per run are in the dq.results table and dq/results/dq_report.md.</t>
         </is>
       </c>
     </row>
@@ -10854,7 +10854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11772,6 +11772,116 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>workbook</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>make workbook</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:55:23+00:00</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>make zip</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:55:23+00:00</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>{"files": 79, "size_kb": 482.3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>make zip</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T12:22:41+00:00</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>{"files": 99, "size_kb": 1265.5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>workbook</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>make workbook</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T21:57:19+00:00</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>make zip</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T21:57:20+00:00</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>{"files": 123, "size_kb": 1320.7}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/deliverables/Berka_TakeHome_Submission.xlsx
+++ b/deliverables/Berka_TakeHome_Submission.xlsx
@@ -13,13 +13,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q detail" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DQ rules" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entitlements" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run log" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cleaning" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entitlements" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run log" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Defect types'!$A$1:$J$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'DQ rules'!$A$4:$H$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'DQ rules'!$A$4:$H$93</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -560,7 +561,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T21:58:03+00:00</t>
+          <t>2026-10-25T07:53:55+00:00</t>
         </is>
       </c>
     </row>
@@ -572,7 +573,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>70f19af</t>
+          <t>da3e93f</t>
         </is>
       </c>
     </row>
@@ -628,7 +629,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>123 (88 hand written + 35 generated by the completeness sweep)</t>
+          <t>124 (89 hand written + 35 generated by the completeness sweep)</t>
         </is>
       </c>
     </row>
@@ -840,7 +841,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>135 passing</t>
+          <t>145 passing</t>
         </is>
       </c>
     </row>
@@ -860,6 +861,1595 @@
   <mergeCells count="1">
     <mergeCell ref="A2:B2"/>
   </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D73"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="96" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Provenance: the command and timestamp behind every figure</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Command</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Executed at (UTC)</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>ingest</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>make ingest</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:40:30+00:00</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>{"run_id": "2ef9d717-7017-4891-b14f-70148b6a1f8d", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>make profile</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T09:49:54+00:00</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>dq</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>make dq (dataset=stg)</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:00:21+00:00</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>{"run_id": "6b7688ee-905d-44cf-915c-2eea22ef2660", "dataset": "stg", "rules_executed": 123, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "duration_sec": 14.91, "defect_types": 14}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>inject</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>python -m src.inject_defects</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:01:58+00:00</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>{"defects": 20, "rules_targeted": ["COMP_DISTRICT_REGION_MISSING", "COMP_LOAN_AMOUNT_MISSING", "COMP_LOAN_STATUS_MISSING", "CON_BALANCE_RECONCILIATION_MATERIAL", "CON_LOAN_BEFORE_ACCOUNT_OPEN", "CON_LOAN_PAYMENT_SCHEDULE", "CON_TYPE_OPERATION_DIRECTION", "REC_ROWCOUNT_RAW_TO_STG", "RI_ACCOUNT_DISTRICT", "RI_ACCOUNT_WITHOUT_OWNER", "RI_DISP_CLIENT", "UNQ_ACCOUNT_PK", "UNQ_ACCOUNT_SINGLE_OWNER", "UNQ_CLIENT_PK", "VAL_ACCOUNT_OPEN_DATE_UNPARSABLE", "VAL_CARD_TYPE_DOMAIN", "VAL_DATE_OUT_OF_RANGE", "VAL_LOAN_DURATION_DOMAIN", "VAL_LOAN_STATUS_DOMAIN", "VAL_TRANS_AMOUNT_NEGATIVE"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>dq</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>make dq (dataset=stg)</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:04:34+00:00</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>{"run_id": "861c72b9-c1c2-4902-815a-5ec9bdbbcc30", "dataset": "stg", "rules_executed": 123, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 17.22, "defect_types": 14}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>make model</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:08:06+00:00</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 76, "dim_client": 5318, "dim_account": 4457, "bridge_disposition": 5367, "dim_card": 891, "fact_loan": 676, "fact_transaction": 1056317, "fact_account_month_end_balance": 185615}, "ref_codes": 27, "problems": ["core.dim_client.district_id -&gt; core.dim_district: 61 orphan rows", "core.dim_account.district_id -&gt; core.dim_district: 55 orphan rows", "core.bridge_disposition.client_id -&gt; core.dim_client: 50 orphan rows", "core.bridge_disposition.account_id -&gt; core.dim_account: 50 orphan rows", "core.fact_loan.account_id -&gt; core.dim_account: 6 orphan rows", "core.fact_transaction.account_id -&gt; core.dim_account: 11024 orphan rows", "core.fact_account_month_end_balance.account_id -&gt; core.dim_account: 1879 orphan rows", "core.v_account_owner covers 4451 of 4457 accounts"], "reconciliation_checks": 9}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>make model</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:08:39+00:00</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 27, "problems": [], "reconciliation_checks": 9}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>make model</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:09:54+00:00</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 27, "problems": [], "reconciliation_checks": 9}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>make reference</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:12:01+00:00</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>{"questions": 10, "failures": []}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>entitlements</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>make entitlements</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:18:11+00:00</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 682, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 682, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 682, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>make model</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:18:45+00:00</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 27, "problems": [], "reconciliation_checks": 9}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>entitlements</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>make entitlements</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:18:46+00:00</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>make semantic</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:24:15+00:00</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>{"entities": 11, "columns": 100, "context_pack_chars": 27592, "problems": []}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>questions</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>make questions (provider=claude_cli, model=claude-sonnet-5-5)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:30:54+00:00</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>{"answered": 10, "total": 10, "answered_first_attempt": 10, "run_as": "cro_global"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>dq</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>make dq (dataset=stg)</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:31:52+00:00</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>{"run_id": "5571d5ad-0b9c-4db4-95d2-d2e45ab16c19", "dataset": "stg", "rules_executed": 123, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 15.15, "defect_types": 14}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>make model</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:32:03+00:00</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 27, "problems": [], "reconciliation_checks": 9}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>make reference</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:32:20+00:00</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>{"questions": 10, "failures": []}</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>questions</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>make questions (provider=claude_cli, model=claude-sonnet-5-5)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:36:04+00:00</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>{"answered": 0, "total": 10, "answered_first_attempt": 0, "run_as": "cro_global"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>entitlements</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>make entitlements</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:36:21+00:00</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>questions</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>make questions (provider=claude_cli, model=claude-sonnet-5-5)</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:38:40+00:00</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>{"answered": 10, "total": 10, "answered_first_attempt": 10, "run_as": "cro_global"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>evaluate</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>make evaluate</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:39:22+00:00</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>{"tally": {"match": 9, "mismatch": 1}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>evaluate</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>make evaluate</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:40:15+00:00</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>{"tally": {"match": 10}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>workbook</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>make workbook</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:44:08+00:00</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>make zip</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:45:18+00:00</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>{"files": 74, "size_kb": 469.7}</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>ddr</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>make ddr</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:47:20+00:00</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>{"words": 1520, "pages": 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>make zip</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:49:22+00:00</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>{"files": 79, "size_kb": 483.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>ingest</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>make ingest</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:50:34+00:00</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>{"run_id": "bd7b7fd2-e741-459c-90ed-f1ce8a1b4fc8", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>make profile</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:51:36+00:00</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>dq</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>make dq (dataset=stg)</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:51:53+00:00</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>{"run_id": "55ac5752-e529-4ad3-b3b6-2723e5a50227", "dataset": "stg", "rules_executed": 123, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 16.24, "defect_types": 14}</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>make model</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:52:04+00:00</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 27, "problems": [], "reconciliation_checks": 9}</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>entitlements</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>make entitlements</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:52:05+00:00</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>make reference</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:52:05+00:00</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>{"questions": 10, "failures": []}</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>make semantic</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:52:07+00:00</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>{"entities": 11, "columns": 100, "context_pack_chars": 27592, "problems": []}</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>entitlements</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>make entitlements</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:52:08+00:00</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>questions</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>make questions (provider=claude_cli, model=claude-sonnet-5-5)</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:54:03+00:00</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>{"answered": 10, "total": 10, "answered_first_attempt": 10, "run_as": "cro_global"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>evaluate</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>make evaluate</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:54:04+00:00</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>{"tally": {"match": 10}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>workbook</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>make workbook</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:54:55+00:00</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>ddr</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>make ddr</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:54:57+00:00</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>{"words": 1520, "pages": 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>make zip</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:54:57+00:00</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>{"files": 79, "size_kb": 482.3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>ddr</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>make ddr</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:55:21+00:00</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>{"words": 1527, "pages": 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>workbook</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>make workbook</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:55:23+00:00</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>make zip</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T10:55:23+00:00</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>{"files": 79, "size_kb": 482.3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>make zip</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T12:22:41+00:00</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>{"files": 99, "size_kb": 1265.5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>workbook</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>make workbook</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T21:57:19+00:00</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>make zip</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T21:57:20+00:00</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>{"files": 123, "size_kb": 1320.7}</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>workbook</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>make workbook</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T21:58:04+00:00</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>make zip</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T21:58:04+00:00</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>{"files": 123, "size_kb": 1321.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>make zip</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22T21:59:11+00:00</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>{"files": 124, "size_kb": 1325.4}</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>evaluate</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>make evaluate</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-24T20:50:44+00:00</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>{"tally": {"match": 10}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>make zip</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-24T20:55:43+00:00</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>{"files": 126, "size_kb": 1337.3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>make zip</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-24T20:56:09+00:00</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>{"files": 126, "size_kb": 1337.5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>make zip</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-24T21:12:20+00:00</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>{"files": 135, "size_kb": 3016.3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>make profile</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:34:31+00:00</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>dq</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>make dq (dataset=stg)</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:34:55+00:00</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>{"run_id": "6b713b33-3916-4b91-93dd-8c6d67f491b9", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 23.38, "defect_types": 14}</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>make model</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:35:19+00:00</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>entitlements</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>make entitlements</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:35:21+00:00</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>make model</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:35:38+00:00</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>entitlements</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>make entitlements</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:35:39+00:00</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>workbook</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>make workbook</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:45:15+00:00</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Cleaning", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>ddr</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>make ddr</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:46:05+00:00</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>{"words": 1780, "pages": 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>ingest</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>make ingest</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:50:02+00:00</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>{"run_id": "077de4c5-5ccb-4a88-bb1d-76a8b7714643", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>make profile</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:51:06+00:00</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>dq</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>make dq (dataset=stg)</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:51:23+00:00</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>{"run_id": "116e896d-afb0-4ddf-8119-c059382d5394", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 16.44, "defect_types": 14}</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>make model</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:51:34+00:00</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>entitlements</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>make entitlements</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:51:35+00:00</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>make reference</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:51:36+00:00</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>{"questions": 10, "failures": []}</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>make semantic</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:51:38+00:00</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>{"entities": 11, "columns": 100, "context_pack_chars": 27592, "problems": []}</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>entitlements</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>make entitlements</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:51:39+00:00</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>questions</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>make questions (provider=claude_cli, model=claude-sonnet-5-5)</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:52:57+00:00</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>{"answered": 10, "total": 10, "answered_first_attempt": 10, "run_as": "cro_global"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>evaluate</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>make evaluate</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:52:58+00:00</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>{"tally": {"match": 10}}</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1219,7 +2809,7 @@
         </is>
       </c>
       <c r="G7" s="6" t="n">
-        <v>1073727</v>
+        <v>1073386</v>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
@@ -2659,17 +4249,17 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>SELECT loan_year, count(*) AS loan_count, sum(amount) AS total_loan_amount FROM ai.loan GROUP BY loan_year ORDER BY loan_year</t>
+          <t>SELECT l.loan_year AS loan_year, SUM(l.amount) AS total_loan_amount_czk, COUNT(*) AS loan_count FROM ai.loan AS l GROUP BY l.loan_year ORDER BY l.loan_year</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>loan_year=1993 | loan_count=20 | total_loan_amount=2619276.0
-loan_year=1994 | loan_count=101 | total_loan_amount=13379904.0
-loan_year=1995 | loan_count=90 | total_loan_amount=13344372.0
-loan_year=1996 | loan_count=117 | total_loan_amount=18317676.0
-loan_year=1997 | loan_count=196 | total_loan_amount=30731364.0
-loan_year=1998 | loan_count=158 | total_loan_amount=24869148.0</t>
+          <t>loan_year=1993 | total_loan_amount_czk=2619276.0 | loan_count=20
+loan_year=1994 | total_loan_amount_czk=13379904.0 | loan_count=101
+loan_year=1995 | total_loan_amount_czk=13344372.0 | loan_count=90
+loan_year=1996 | total_loan_amount_czk=18317676.0 | loan_count=117
+loan_year=1997 | total_loan_amount_czk=30731364.0 | loan_count=196
+loan_year=1998 | total_loan_amount_czk=24869148.0 | loan_count=158</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
@@ -2859,21 +4449,21 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>SELECT account_district_id AS district_id, account_district_name AS district_name, account_region AS region, sum(amount) AS total_incoming_amount, count(*) AS credit_posting_count, count(DISTINCT account_id) AS account_count FROM ai.transaction WHERE direction = 'credit' AND trans_date &gt;= DATE '1997-01-01' AND trans_date &lt; DATE '1998-01-01' GROUP BY account_district_id, account_district_name, account_region ORDER BY sum(amount) DESC, account_district_id LIMIT 10</t>
+          <t>SELECT t.account_district_id, t.account_district_name, t.account_region, sum(t.amount) AS incoming_transaction_amount, count(*) AS credit_posting_count, count(DISTINCT t.account_id) AS accounts_with_credits FROM ai.transaction t WHERE t.direction = 'credit' AND t.trans_date &gt;= DATE '1997-01-01' AND t.trans_date &lt; DATE '1998-01-01' GROUP BY t.account_district_id, t.account_district_name, t.account_region ORDER BY incoming_transaction_amount DESC, t.account_district_name ASC LIMIT 10</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>district_id=1 | district_name=Hl.m. Praha | region=Prague | total_incoming_amount=115130200.1 | credit_posting_count=13611 | account_count=554
-district_id=70 | district_name=Karvina | region=north Moravia | total_incoming_amount=28506437.1 | credit_posting_count=3802 | account_count=152
-district_id=74 | district_name=Ostrava - mesto | region=north Moravia | total_incoming_amount=27689271.9 | credit_posting_count=3378 | account_count=135
-district_id=54 | district_name=Brno - mesto | region=south Moravia | total_incoming_amount=23095083.4 | credit_posting_count=3041 | account_count=128
-district_id=64 | district_name=Zlin | region=south Moravia | total_incoming_amount=19723168.5 | credit_posting_count=2299 | account_count=92
-district_id=68 | district_name=Frydek - Mistek | region=north Moravia | total_incoming_amount=19087598.8 | credit_posting_count=2006 | account_count=83
-district_id=72 | district_name=Olomouc | region=north Moravia | total_incoming_amount=15916397.0 | credit_posting_count=2129 | account_count=88
-district_id=5 | district_name=Kolin | region=central Bohemia | total_incoming_amount=14471603.6 | credit_posting_count=1542 | account_count=65
-district_id=52 | district_name=Usti nad Orlici | region=east Bohemia | total_incoming_amount=14085167.4 | credit_posting_count=1431 | account_count=57
-district_id=19 | district_name=Prachatice | region=south Bohemia | total_incoming_amount=12163147.0 | credit_posting_count=1359 | account_count=55</t>
+          <t>account_district_id=1 | account_district_name=Hl.m. Praha | account_region=Prague | incoming_transaction_amount=115130200.1 | credit_posting_count=13611 | accounts_with_credits=554
+account_district_id=70 | account_district_name=Karvina | account_region=north Moravia | incoming_transaction_amount=28506437.1 | credit_posting_count=3802 | accounts_with_credits=152
+account_district_id=74 | account_district_name=Ostrava - mesto | account_region=north Moravia | incoming_transaction_amount=27689271.9 | credit_posting_count=3378 | accounts_with_credits=135
+account_district_id=54 | account_district_name=Brno - mesto | account_region=south Moravia | incoming_transaction_amount=23095083.4 | credit_posting_count=3041 | accounts_with_credits=128
+account_district_id=64 | account_district_name=Zlin | account_region=south Moravia | incoming_transaction_amount=19723168.5 | credit_posting_count=2299 | accounts_with_credits=92
+account_district_id=68 | account_district_name=Frydek - Mistek | account_region=north Moravia | incoming_transaction_amount=19087598.8 | credit_posting_count=2006 | accounts_with_credits=83
+account_district_id=72 | account_district_name=Olomouc | account_region=north Moravia | incoming_transaction_amount=15916397.0 | credit_posting_count=2129 | accounts_with_credits=88
+account_district_id=5 | account_district_name=Kolin | account_region=central Bohemia | incoming_transaction_amount=14471603.6 | credit_posting_count=1542 | accounts_with_credits=65
+account_district_id=52 | account_district_name=Usti nad Orlici | account_region=east Bohemia | incoming_transaction_amount=14085167.4 | credit_posting_count=1431 | accounts_with_credits=57
+account_district_id=19 | account_district_name=Prachatice | account_region=south Bohemia | incoming_transaction_amount=12163147.0 | credit_posting_count=1359 | accounts_with_credits=55</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
@@ -2883,7 +4473,7 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>C5, C7</t>
+          <t>C5, C6, C7</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -2940,23 +4530,23 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>SELECT c.year_month AS month, c.month_start AS month_start, count(a.account_id) AS new_accounts FROM ai.calendar c LEFT JOIN ai.account a ON a.open_date = c.date_key WHERE c.year = 1996 GROUP BY c.year_month, c.month_start ORDER BY c.month_start</t>
+          <t>SELECT c.year_month AS month, COUNT(a.account_id) AS new_accounts FROM ai.calendar c LEFT JOIN ai.account a ON a.open_date = c.date_key WHERE c.year = 1996 GROUP BY c.year_month ORDER BY c.year_month</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>month=1996-01 | month_start=1996-01-01 | new_accounts=106
-month=1996-02 | month_start=1996-02-01 | new_accounts=104
-month=1996-03 | month_start=1996-03-01 | new_accounts=124
-month=1996-04 | month_start=1996-04-01 | new_accounts=101
-month=1996-05 | month_start=1996-05-01 | new_accounts=91
-month=1996-06 | month_start=1996-06-01 | new_accounts=113
-month=1996-07 | month_start=1996-07-01 | new_accounts=137
-month=1996-08 | month_start=1996-08-01 | new_accounts=133
-month=1996-09 | month_start=1996-09-01 | new_accounts=108
-month=1996-10 | month_start=1996-10-01 | new_accounts=115
-month=1996-11 | month_start=1996-11-01 | new_accounts=106
-month=1996-12 | month_start=1996-12-01 | new_accounts=125</t>
+          <t>month=1996-01 | new_accounts=106
+month=1996-02 | new_accounts=104
+month=1996-03 | new_accounts=124
+month=1996-04 | new_accounts=101
+month=1996-05 | new_accounts=91
+month=1996-06 | new_accounts=113
+month=1996-07 | new_accounts=137
+month=1996-08 | new_accounts=133
+month=1996-09 | new_accounts=108
+month=1996-10 | new_accounts=115
+month=1996-11 | new_accounts=106
+month=1996-12 | new_accounts=125</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
@@ -3015,15 +4605,15 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>SELECT loan_status, count(*) AS loan_count, round(avg(owner_age_at_loan_start), 2) AS average_age_at_loan_start, count(*) FILTER (WHERE 'val_owner_age_at_loan_start' = ANY(data_quality_flags)) AS flagged_under_15_loans, round(avg(owner_age_at_loan_start) FILTER (WHERE NOT ('val_owner_age_at_loan_start' = ANY(data_quality_flags))), 2) AS average_age_excluding_flagged FROM ai.loan GROUP BY loan_status ORDER BY loan_status</t>
+          <t>SELECT loan_status, status_code, count(*) AS loan_count, round(avg(owner_age_at_loan_start), 2) AS average_age_at_loan_start, count(*) FILTER (WHERE data_quality_flags @&gt; ARRAY['val_owner_age_at_loan_start']) AS flagged_under_15_loans, round(avg(owner_age_at_loan_start) FILTER (WHERE NOT (data_quality_flags @&gt; ARRAY['val_owner_age_at_loan_start'])), 2) AS average_age_excluding_flagged, count(*) FILTER (WHERE NOT (data_quality_flags @&gt; ARRAY['val_owner_age_at_loan_start'])) AS loan_count_excluding_flagged FROM ai.loan GROUP BY loan_status, status_code ORDER BY status_code</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>loan_status=finished, paid in full | loan_count=203 | average_age_at_loan_start=37.07 | flagged_under_15_loans=4 | average_age_excluding_flagged=37.53
-loan_status=finished, unpaid (default) | loan_count=31 | average_age_at_loan_start=39.61 | flagged_under_15_loans=0 | average_age_excluding_flagged=39.61
-loan_status=running, client in debt | loan_count=45 | average_age_at_loan_start=37.0 | flagged_under_15_loans=0 | average_age_excluding_flagged=37.0
-loan_status=running, no problem | loan_count=403 | average_age_at_loan_start=38.7 | flagged_under_15_loans=2 | average_age_excluding_flagged=38.82</t>
+          <t>loan_status=finished, paid in full | status_code=A | loan_count=203 | average_age_at_loan_start=37.07 | flagged_under_15_loans=4 | average_age_excluding_flagged=37.53 | loan_count_excluding_flagged=199
+loan_status=finished, unpaid (default) | status_code=B | loan_count=31 | average_age_at_loan_start=39.61 | flagged_under_15_loans=0 | average_age_excluding_flagged=39.61 | loan_count_excluding_flagged=31
+loan_status=running, no problem | status_code=C | loan_count=403 | average_age_at_loan_start=38.7 | flagged_under_15_loans=2 | average_age_excluding_flagged=38.82 | loan_count_excluding_flagged=401
+loan_status=running, client in debt | status_code=D | loan_count=45 | average_age_at_loan_start=37.0 | flagged_under_15_loans=0 | average_age_excluding_flagged=37.0 | loan_count_excluding_flagged=45</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
@@ -3092,7 +4682,7 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -3138,12 +4728,12 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>SELECT round(avg(closing_balance), 2) AS average_month_end_balance, count(*) AS accounts_with_balance, count(*) FILTER (WHERE is_carried_forward) AS carried_forward_balances FROM ai.account_month_end_balance WHERE month_end_date = DATE '1998-12-31'</t>
+          <t>SELECT DATE '1998-12-31' AS month_end_date, round(avg(closing_balance), 2) AS average_closing_balance, count(*) AS accounts_with_balance, count(*) FILTER (WHERE is_carried_forward) AS carried_forward_balances, count(*) FILTER (WHERE 'con_balance_reconciliation_material' = ANY(account_data_quality_flags)) AS accounts_with_reconciliation_flag FROM ai.account_month_end_balance WHERE month_end_date = DATE '1998-12-31'</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>average_month_end_balance=43808.94 | accounts_with_balance=4500 | carried_forward_balances=76</t>
+          <t>month_end_date=1998-12-31 | average_closing_balance=43808.94 | accounts_with_balance=4500 | carried_forward_balances=76 | accounts_with_reconciliation_flag=55</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
@@ -3629,12 +5219,12 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
+          <t>total_loan_amount_czk</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
           <t>loan_count</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>total_loan_amount</t>
         </is>
       </c>
     </row>
@@ -3643,10 +5233,10 @@
         <v>1993</v>
       </c>
       <c r="B39" s="15" t="n">
+        <v>2619276</v>
+      </c>
+      <c r="C39" s="15" t="n">
         <v>20</v>
-      </c>
-      <c r="C39" s="15" t="n">
-        <v>2619276</v>
       </c>
     </row>
     <row r="40">
@@ -3654,10 +5244,10 @@
         <v>1994</v>
       </c>
       <c r="B40" s="15" t="n">
+        <v>13379904</v>
+      </c>
+      <c r="C40" s="15" t="n">
         <v>101</v>
-      </c>
-      <c r="C40" s="15" t="n">
-        <v>13379904</v>
       </c>
     </row>
     <row r="41">
@@ -3665,10 +5255,10 @@
         <v>1995</v>
       </c>
       <c r="B41" s="15" t="n">
+        <v>13344372</v>
+      </c>
+      <c r="C41" s="15" t="n">
         <v>90</v>
-      </c>
-      <c r="C41" s="15" t="n">
-        <v>13344372</v>
       </c>
     </row>
     <row r="42">
@@ -3676,10 +5266,10 @@
         <v>1996</v>
       </c>
       <c r="B42" s="15" t="n">
+        <v>18317676</v>
+      </c>
+      <c r="C42" s="15" t="n">
         <v>117</v>
-      </c>
-      <c r="C42" s="15" t="n">
-        <v>18317676</v>
       </c>
     </row>
     <row r="43">
@@ -3687,10 +5277,10 @@
         <v>1997</v>
       </c>
       <c r="B43" s="15" t="n">
+        <v>30731364</v>
+      </c>
+      <c r="C43" s="15" t="n">
         <v>196</v>
-      </c>
-      <c r="C43" s="15" t="n">
-        <v>30731364</v>
       </c>
     </row>
     <row r="44">
@@ -3698,10 +5288,10 @@
         <v>1998</v>
       </c>
       <c r="B44" s="15" t="n">
+        <v>24869148</v>
+      </c>
+      <c r="C44" s="15" t="n">
         <v>158</v>
-      </c>
-      <c r="C44" s="15" t="n">
-        <v>24869148</v>
       </c>
     </row>
     <row r="47">
@@ -4304,22 +5894,22 @@
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>district_id</t>
+          <t>account_district_id</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>district_name</t>
+          <t>account_district_name</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>account_region</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>total_incoming_amount</t>
+          <t>incoming_transaction_amount</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -4329,7 +5919,7 @@
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>account_count</t>
+          <t>accounts_with_credits</t>
         </is>
       </c>
     </row>
@@ -4840,11 +6430,6 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>month_start</t>
-        </is>
-      </c>
-      <c r="C118" s="5" t="inlineStr">
-        <is>
           <t>new_accounts</t>
         </is>
       </c>
@@ -4855,12 +6440,7 @@
           <t>1996-01</t>
         </is>
       </c>
-      <c r="B119" s="15" t="inlineStr">
-        <is>
-          <t>1996-01-01</t>
-        </is>
-      </c>
-      <c r="C119" s="15" t="n">
+      <c r="B119" s="15" t="n">
         <v>106</v>
       </c>
     </row>
@@ -4870,12 +6450,7 @@
           <t>1996-02</t>
         </is>
       </c>
-      <c r="B120" s="15" t="inlineStr">
-        <is>
-          <t>1996-02-01</t>
-        </is>
-      </c>
-      <c r="C120" s="15" t="n">
+      <c r="B120" s="15" t="n">
         <v>104</v>
       </c>
     </row>
@@ -4885,12 +6460,7 @@
           <t>1996-03</t>
         </is>
       </c>
-      <c r="B121" s="15" t="inlineStr">
-        <is>
-          <t>1996-03-01</t>
-        </is>
-      </c>
-      <c r="C121" s="15" t="n">
+      <c r="B121" s="15" t="n">
         <v>124</v>
       </c>
     </row>
@@ -4900,12 +6470,7 @@
           <t>1996-04</t>
         </is>
       </c>
-      <c r="B122" s="15" t="inlineStr">
-        <is>
-          <t>1996-04-01</t>
-        </is>
-      </c>
-      <c r="C122" s="15" t="n">
+      <c r="B122" s="15" t="n">
         <v>101</v>
       </c>
     </row>
@@ -4915,12 +6480,7 @@
           <t>1996-05</t>
         </is>
       </c>
-      <c r="B123" s="15" t="inlineStr">
-        <is>
-          <t>1996-05-01</t>
-        </is>
-      </c>
-      <c r="C123" s="15" t="n">
+      <c r="B123" s="15" t="n">
         <v>91</v>
       </c>
     </row>
@@ -4930,12 +6490,7 @@
           <t>1996-06</t>
         </is>
       </c>
-      <c r="B124" s="15" t="inlineStr">
-        <is>
-          <t>1996-06-01</t>
-        </is>
-      </c>
-      <c r="C124" s="15" t="n">
+      <c r="B124" s="15" t="n">
         <v>113</v>
       </c>
     </row>
@@ -4945,12 +6500,7 @@
           <t>1996-07</t>
         </is>
       </c>
-      <c r="B125" s="15" t="inlineStr">
-        <is>
-          <t>1996-07-01</t>
-        </is>
-      </c>
-      <c r="C125" s="15" t="n">
+      <c r="B125" s="15" t="n">
         <v>137</v>
       </c>
     </row>
@@ -4960,12 +6510,7 @@
           <t>1996-08</t>
         </is>
       </c>
-      <c r="B126" s="15" t="inlineStr">
-        <is>
-          <t>1996-08-01</t>
-        </is>
-      </c>
-      <c r="C126" s="15" t="n">
+      <c r="B126" s="15" t="n">
         <v>133</v>
       </c>
     </row>
@@ -4975,12 +6520,7 @@
           <t>1996-09</t>
         </is>
       </c>
-      <c r="B127" s="15" t="inlineStr">
-        <is>
-          <t>1996-09-01</t>
-        </is>
-      </c>
-      <c r="C127" s="15" t="n">
+      <c r="B127" s="15" t="n">
         <v>108</v>
       </c>
     </row>
@@ -4990,12 +6530,7 @@
           <t>1996-10</t>
         </is>
       </c>
-      <c r="B128" s="15" t="inlineStr">
-        <is>
-          <t>1996-10-01</t>
-        </is>
-      </c>
-      <c r="C128" s="15" t="n">
+      <c r="B128" s="15" t="n">
         <v>115</v>
       </c>
     </row>
@@ -5005,12 +6540,7 @@
           <t>1996-11</t>
         </is>
       </c>
-      <c r="B129" s="15" t="inlineStr">
-        <is>
-          <t>1996-11-01</t>
-        </is>
-      </c>
-      <c r="C129" s="15" t="n">
+      <c r="B129" s="15" t="n">
         <v>106</v>
       </c>
     </row>
@@ -5020,12 +6550,7 @@
           <t>1996-12</t>
         </is>
       </c>
-      <c r="B130" s="15" t="inlineStr">
-        <is>
-          <t>1996-12-01</t>
-        </is>
-      </c>
-      <c r="C130" s="15" t="n">
+      <c r="B130" s="15" t="n">
         <v>125</v>
       </c>
     </row>
@@ -5203,22 +6728,32 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
+          <t>status_code</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
           <t>loan_count</t>
         </is>
       </c>
-      <c r="C142" s="5" t="inlineStr">
+      <c r="D142" s="5" t="inlineStr">
         <is>
           <t>average_age_at_loan_start</t>
         </is>
       </c>
-      <c r="D142" s="5" t="inlineStr">
+      <c r="E142" s="5" t="inlineStr">
         <is>
           <t>flagged_under_15_loans</t>
         </is>
       </c>
-      <c r="E142" s="5" t="inlineStr">
+      <c r="F142" s="5" t="inlineStr">
         <is>
           <t>average_age_excluding_flagged</t>
+        </is>
+      </c>
+      <c r="G142" s="5" t="inlineStr">
+        <is>
+          <t>loan_count_excluding_flagged</t>
         </is>
       </c>
     </row>
@@ -5228,17 +6763,25 @@
           <t>finished, paid in full</t>
         </is>
       </c>
-      <c r="B143" s="15" t="n">
+      <c r="B143" s="15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C143" s="15" t="n">
         <v>203</v>
       </c>
-      <c r="C143" s="15" t="n">
+      <c r="D143" s="15" t="n">
         <v>37.07</v>
       </c>
-      <c r="D143" s="15" t="n">
+      <c r="E143" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="E143" s="15" t="n">
+      <c r="F143" s="15" t="n">
         <v>37.53</v>
+      </c>
+      <c r="G143" s="15" t="n">
+        <v>199</v>
       </c>
     </row>
     <row r="144">
@@ -5247,55 +6790,79 @@
           <t>finished, unpaid (default)</t>
         </is>
       </c>
-      <c r="B144" s="15" t="n">
+      <c r="B144" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C144" s="15" t="n">
         <v>31</v>
       </c>
-      <c r="C144" s="15" t="n">
+      <c r="D144" s="15" t="n">
         <v>39.61</v>
       </c>
-      <c r="D144" s="15" t="n">
+      <c r="E144" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="E144" s="15" t="n">
+      <c r="F144" s="15" t="n">
         <v>39.61</v>
+      </c>
+      <c r="G144" s="15" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="15" t="inlineStr">
         <is>
-          <t>running, client in debt</t>
-        </is>
-      </c>
-      <c r="B145" s="15" t="n">
-        <v>45</v>
+          <t>running, no problem</t>
+        </is>
+      </c>
+      <c r="B145" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="C145" s="15" t="n">
-        <v>37</v>
+        <v>403</v>
       </c>
       <c r="D145" s="15" t="n">
-        <v>0</v>
+        <v>38.7</v>
       </c>
       <c r="E145" s="15" t="n">
-        <v>37</v>
+        <v>2</v>
+      </c>
+      <c r="F145" s="15" t="n">
+        <v>38.82</v>
+      </c>
+      <c r="G145" s="15" t="n">
+        <v>401</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="15" t="inlineStr">
         <is>
-          <t>running, no problem</t>
-        </is>
-      </c>
-      <c r="B146" s="15" t="n">
-        <v>403</v>
+          <t>running, client in debt</t>
+        </is>
+      </c>
+      <c r="B146" s="15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
       </c>
       <c r="C146" s="15" t="n">
-        <v>38.7</v>
+        <v>45</v>
       </c>
       <c r="D146" s="15" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="E146" s="15" t="n">
-        <v>38.82</v>
+        <v>0</v>
+      </c>
+      <c r="F146" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="G146" s="15" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="149">
@@ -5519,29 +7086,47 @@
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>average_month_end_balance</t>
+          <t>month_end_date</t>
         </is>
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
+          <t>average_closing_balance</t>
+        </is>
+      </c>
+      <c r="C167" s="5" t="inlineStr">
+        <is>
           <t>accounts_with_balance</t>
         </is>
       </c>
-      <c r="C167" s="5" t="inlineStr">
+      <c r="D167" s="5" t="inlineStr">
         <is>
           <t>carried_forward_balances</t>
         </is>
       </c>
+      <c r="E167" s="5" t="inlineStr">
+        <is>
+          <t>accounts_with_reconciliation_flag</t>
+        </is>
+      </c>
     </row>
     <row r="168">
-      <c r="A168" s="15" t="n">
+      <c r="A168" s="15" t="inlineStr">
+        <is>
+          <t>1998-12-31</t>
+        </is>
+      </c>
+      <c r="B168" s="15" t="n">
         <v>43808.94</v>
       </c>
-      <c r="B168" s="15" t="n">
+      <c r="C168" s="15" t="n">
         <v>4500</v>
       </c>
-      <c r="C168" s="15" t="n">
+      <c r="D168" s="15" t="n">
         <v>76</v>
+      </c>
+      <c r="E168" s="15" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="171">
@@ -5730,7 +7315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H92"/>
+  <dimension ref="A1:H93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -5753,7 +7338,7 @@
     <row r="2" ht="46" customHeight="1">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>88 hand-written rules, plus a completeness sweep that expands to one rule per column of every table at run time (123 executed in the last run). The loader refuses to run a rule that lacks a severity, a justification or the list of questions it affects. Results per run are in the dq.results table and dq/results/dq_report.md.</t>
+          <t>89 hand-written rules, plus a completeness sweep that expands to one rule per column of every table at run time (124 executed in the last run). The loader refuses to run a rule that lacks a severity, a justification or the list of questions it affects. Results per run are in the dq.results table and dq/results/dq_report.md.</t>
         </is>
       </c>
     </row>
@@ -9414,7 +10999,7 @@
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>VAL_TRANS_AMOUNT_POSITIVE</t>
+          <t>VAL_ORDER_KSYMBOL_DOMAIN</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
@@ -9424,12 +11009,12 @@
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>trans</t>
+          <t>order</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>Transaction amount is zero or negative</t>
+          <t>Standing order category (k_symbol) outside the documented set</t>
         </is>
       </c>
       <c r="E91" s="9" t="inlineStr">
@@ -9439,7 +11024,7 @@
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>14 postings have an amount of exactly zero. All of them are interest or sanction-interest runs that accrued nothing, so they are genuine events with no monetary effect: they change no sum in Q5 and no balance in Q9. The naive form of this rule ("amount must be &gt; 0") would quarantine 14 valid postings and break the balance chain of 14 accounts, which is a worked example of a defensible rule with the wrong severity doing more damage than the defect. A *negative* amount, by contrast, would be blocked: the split is in the rule below.</t>
+          <t>Same column and same code set as the transaction rule above, on the other table that carries it. It is info for the same reason: no question reads the standing orders, and an unknown category costs nothing until someone groups by it. The reason this rule exists at all is that its absence cost something: LEASING sat on 341 standing orders with no English label for the whole first build, because the catalogue check covered trans and not order. The rule is the cheap guarantee that the next unknown code is reported rather than silently unlabelled.</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
@@ -9449,54 +11034,96 @@
       </c>
       <c r="H91" s="6" t="inlineStr">
         <is>
-          <t>Logged only; the postings stay in core with amount = 0.</t>
+          <t>Logged only; the code passes through to staging with no English label.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
+          <t>VAL_TRANS_AMOUNT_POSITIVE</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>validity</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>trans</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>Transaction amount is zero or negative</t>
+        </is>
+      </c>
+      <c r="E92" s="9" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>14 postings have an amount of exactly zero. All of them are interest or sanction-interest runs that accrued nothing, so they are genuine events with no monetary effect: they change no sum in Q5 and no balance in Q9. The naive form of this rule ("amount must be &gt; 0") would quarantine 14 valid postings and break the balance chain of 14 accounts, which is a worked example of a defensible rule with the wrong severity doing more damage than the defect. A *negative* amount, by contrast, would be blocked: the split is in the rule below.</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="inlineStr">
+        <is>
+          <t>Logged only; the postings stay in core with amount = 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
           <t>VAL_TRANS_BALANCE_NEGATIVE</t>
         </is>
       </c>
-      <c r="B92" s="6" t="inlineStr">
+      <c r="B93" s="6" t="inlineStr">
         <is>
           <t>validity</t>
         </is>
       </c>
-      <c r="C92" s="6" t="inlineStr">
+      <c r="C93" s="6" t="inlineStr">
         <is>
           <t>trans</t>
         </is>
       </c>
-      <c r="D92" s="6" t="inlineStr">
+      <c r="D93" s="6" t="inlineStr">
         <is>
           <t>Balance after the transaction is negative (overdraft)</t>
         </is>
       </c>
-      <c r="E92" s="9" t="inlineStr">
+      <c r="E93" s="9" t="inlineStr">
         <is>
           <t>info</t>
         </is>
       </c>
-      <c r="F92" s="6" t="inlineStr">
+      <c r="F93" s="6" t="inlineStr">
         <is>
           <t>2,999 postings leave a negative balance. This is overdraft, which is normal banking, not a defect -- and it matters that the rule says so, because the tempting "fix" (clipping balances at zero) would bias the Q9 average upwards. Reported as info so the number is known and explicitly not acted on.</t>
         </is>
       </c>
-      <c r="G92" s="6" t="inlineStr">
+      <c r="G93" s="6" t="inlineStr">
         <is>
           <t>Q9</t>
         </is>
       </c>
-      <c r="H92" s="6" t="inlineStr">
+      <c r="H93" s="6" t="inlineStr">
         <is>
           <t>Logged only; balances are never clipped.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H92"/>
+  <autoFilter ref="A4:H93"/>
   <mergeCells count="1">
     <mergeCell ref="A2:H2"/>
   </mergeCells>
@@ -9510,7 +11137,951 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:H25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>What cleaning actually happened, from source file to product</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>One row per transformation between the .asc files and the published model. 'Measured' is produced by running a probe against the database at build time, not transcribed. 'Reversible' says where the pre-cleaning value can still be read -- a cleaning step you cannot undo is one you have to take on trust. 'Watched by' names the rule that reports whatever the step could not clean. No step repairs a value: exactly one (C14) removes a row, and C21 proves the arithmetic. Full detail in docs/CLEANING_LEDGER.md; the reasoning behind each choice is DECISIONS.md D013-D020.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>What it does</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Measured</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Reversible / watched by</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>bronze (raw)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Land every field as text, unchanged</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>all 8 tables</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>1079680</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>rows landed verbatim</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>A cast at load time destroys the evidence of the defect it trips over. Bronze is deliberately the one layer that cleans nothing.</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>reversible: the source file itself, SHA-256 in raw.load_audit
+watched by: RI_RAW_ROWCOUNT_MATCHES</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>C02</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>bronze (raw)</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Stamp every row with its file and line number</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>all 8 tables -&gt; _source_file, _source_row</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>files whose row count matched the file</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Without it no cleaned value can be traced back, and a reviewer has to take the rest of this ledger on trust.</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>reversible: -
+watched by: -</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>C03</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>silver (stg)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Trim, then map '', '?', 'NA', 'N/A', 'NULL', '-', 'unknown' to NULL</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>every text column (stg.norm_text)</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>1380</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>rows where a placeholder became NULL</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>The source spells 'missing' seven ways. Left alone, '?' counts as a value and every completeness number is wrong.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>reversible: &lt;column&gt;_raw audit column, plus _conversion_notes
+watched by: COMP_DISTRICT_1995_PLACEHOLDER, COMP_RAW_MISSING_ENCODING_INCONSISTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>C04</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>silver (stg)</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Cast to numeric, returning NULL rather than raising</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>every numeric column (stg.parse_numeric, parse_int)</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>transaction amounts that failed to cast</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>A cast that throws aborts the load and hides the bad value. Returning NULL keeps the row and lets a rule count the loss.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>reversible: amount_raw / balance_raw
+watched by: VAL_TRANS_AMOUNT_POSITIVE, VAL_LOAN_AMOUNT_POSITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>C05</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>silver (stg)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Parse YYMMDD into a real date, two-digit year read as 19xx</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>account.date, loan.date, trans.date, card.issued</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>1062394</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>dates parsed from YYMMDD text</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Six digits are not a date. The century is an assumption (A25) and it is safe only because the dataset window is 1993-1998.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>reversible: &lt;column&gt;_raw where the parse failed
+watched by: VAL_TRANS_DATE_UNPARSABLE, VAL_DATE_OUT_OF_RANGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>C06</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>silver (stg)</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Strip the trailing clock time before parsing</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>card.issued</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>892</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>card issue dates carrying a clock time</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>card.issued is '931107 00:00:00' while every other date is bare. One format rule for all four columns, applied in one function.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>reversible: raw.card.issued
+watched by: VAL_CARD_ISSUED_UNPARSABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>C07</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>silver (stg)</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Decode YYMMDD, subtracting 50 from the month for women</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>client.birth_number -&gt; birth_date</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>5369</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>birth dates decoded</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>The source packs two facts into one number. Leaving it packed means every age question has to re-implement the decoding.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>reversible: birth_number is kept in full beside it
+watched by: VAL_BIRTH_NUMBER_DECODABLE, VAL_BIRTH_DATE_PLAUSIBLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>C08</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>silver (stg)</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Derive gender from the same month offset</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>client.birth_number -&gt; gender</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>5369</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>clients whose gender was derived</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>The dataset has no gender column. It is derived, not given, which is why it is recorded here and in A26 rather than presented as fact.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>reversible: birth_number
+watched by: VAL_GENDER_DOMAIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>C09</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>silver (stg)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Decode each Czech code to an English label from one map</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>7 coded columns across 5 tables</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>2466175</v>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>coded values given an English label</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>An LLM asked for 'withdrawals' cannot know VYDAJ. The map lives in src/config.py only, and the build fails if the data holds a code it does not know.</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>reversible: the code column is kept beside every label
+watched by: VAL_KSYMBOL_DOMAIN, VAL_ORDER_KSYMBOL_DOMAIN, VAL_TRANS_TYPE_DOMAIN, VAL_TRANS_OPERATION_DOMAIN, VAL_LOAN_STATUS_DOMAIN, VAL_FREQUENCY_DOMAIN, VAL_DISP_TYPE_DOMAIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>silver (stg)</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Resolve the sign once: credits positive, debits negative</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>trans.type + trans.amount -&gt; signed_amount, direction</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>1056320</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>postings given an unambiguous sign</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>This is the single most valuable cleaning step for AI-readiness. The source states direction in a Czech word and leaves the amount unsigned, so every 'net flow' query has to encode that VYDAJ and VYBER are both outgoing. Resolved here, it cannot be got wrong there.</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>reversible: amount and trans_type_code are both kept
+watched by: VAL_TRANS_AMOUNT_NEGATIVE, CON_BALANCE_RECONCILIATION_MATERIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>silver (stg)</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Materialise the B-or-D definition as a boolean</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>loan.status -&gt; is_problematic</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>loans marked problematic (status B or D)</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Q3 and Q10 both turn on what 'problematic' means. Defining it once in the data stops the model inventing a different definition per answer.</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>reversible: status_code and status_label
+watched by: VAL_LOAN_STATUS_DOMAIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>silver (stg)</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Record every value the cleaning changed or dropped, in place</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>_conversion_notes on all 8 tables</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>1380</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>rows carrying a conversion note</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>A cleaning step with no receipt is indistinguishable from data loss.</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>reversible: -
+watched by: -</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>silver (dq)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Grade each defect block / warn / info; change no value</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>every staged table</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>124</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>rules executed against the real data</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Cleaning that silently repairs is cleaning nobody can audit. The rule layer decides what happens to a bad row; it never edits one.</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>reversible: -
+watched by: -</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>silver (dq)</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Hold back the rows that fail a block rule</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>dq.quarantine</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>rows held back from the product</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>The only step in the whole pipeline that removes a row from the product, which is why it is counted, reversible and reconciled.</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>reversible: dq.quarantine holds the row and the reason
+watched by: UNQ_TRANS_BUSINESS_KEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>C15</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>silver (dq)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Attach a warn flag to the row it concerns</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>dq.flags</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>352</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>distinct rows carrying at least one warn flag</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>A row that is suspect but usable should travel with its warning rather than be dropped or silently trusted.</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>reversible: -
+watched by: CON_BALANCE_RECONCILIATION_MATERIAL, CON_INTRADAY_ORDER_AMBIGUOUS, VAL_OWNER_AGE_AT_ACCOUNT_OPEN, VAL_OWNER_AGE_AT_LOAN_START</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>C16</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>gold (core)</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Publish staging minus the blocked rows</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>every core table</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>transactions excluded from the product</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>One subtraction, applied identically everywhere, so 'why is this row missing' always has the same answer.</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>reversible: dq.quarantine, and stg.trans still holds the row
+watched by: -</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>gold (core)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Carry the warn flags onto the published row</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>_dq_flags on 4 core tables</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>352</v>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>published rows carrying a visible caveat</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>The caveat has to reach the answer. A flag that stops at the quality schema is a flag nobody acts on.</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>reversible: -
+watched by: -</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>C18</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>gold (core)</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Re-resolve every label from one published catalogue</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>core.ref_codes</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>codes published with a label and a note</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Staging decodes inline for speed; core resolves against the catalogue and the build fails if the two disagree. Deliberate redundancy, checked rather than trusted.</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>reversible: -
+watched by: -</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>C19</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>gold (core)</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Generate a row per calendar day in the dataset window</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>core.dim_date</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>2191</v>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>calendar days generated (no source table)</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>'Per month in 1996' must report twelve months, including the quiet ones. Without a date dimension the query has to invent them.</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>reversible: -
+watched by: -</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>C20</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>gold (core)</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Derive a month-end balance per account, carried forward</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>core.fact_account_month_end_balance</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>558</v>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>month ends inherited from an earlier posting (marked as such)</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>The source has no month-end balance: it has postings. Deriving it once, with the tie-break written down, is what stops two answers to the same question.</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>reversible: is_carried_forward and balance_as_of_month_end
+watched by: CON_INTRADAY_ORDER_AMBIGUOUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>C21</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>gold (core)</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Prove core = staging - quarantine, on rows and on money</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>dq.reconciliation</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>reconciliation checks balanced (of 11; any shortfall is a cleaning leak)</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>The closing check on the whole chain: if cleaning lost a row or a koruna without a quarantine entry to explain it, this is where it shows up.</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>reversible: -
+watched by: -</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:H2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10202,12 +12773,255 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>A25</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>C03</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>The placeholder list ('', '?', 'NA', 'N/A', 'NULL', '-', 'unknown') is the complete set of ways this source writes "missing".</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Derived by profiling every text column, not assumed up front; the profiler reports the full distinct-value distribution per column and no other placeholder-shaped value appeared.</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>An eighth spelling would be counted as a real value, overstating completeness for that column. It would not corrupt anything downstream, and the profile report is where it would show up. Low risk, cheap to extend: one tuple in src/config.NULL_PLACEHOLDERS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>A26</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>C03, C09</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>A NULL after cleaning means "the source did not record this", never "the pipeline lost it".</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Every value the cleaning dropped or changed is kept in a &lt;column&gt;_raw column and listed in _conversion_notes, so the two cases are distinguishable by construction.</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>This is the assumption the whole ledger exists to make checkable. If it were false, every completeness number would be measuring the loader rather than the source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>A27</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>C09</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>operation_code IS NULL on a transaction means a bank-generated posting, not a missing value.</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Measured: all 183,114 rows with no operation carry k_symbol = UROK (interest credited), and no other category has a NULL operation. The bank books interest without a customer-facing operation.</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>If some of those NULLs were genuinely missing data, the completeness rule on that column would have to be warn rather than info, and "transactions by operation" would be understating one category. The measurement is re-run every build, so a mixed population would show up as UROK no longer being the only value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>A28</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>C09, D017</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>The code sets are open: the source may contain a code the catalogue does not know, and the right response is to fail the build rather than guess a label.</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>It already happened. LEASING appeared on 341 standing orders and was not in the map; because the catalogue check did not cover that table, nothing failed and the rows shipped unlabelled.</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>The assumption now has teeth: check_codes_against_staging covers every coded column and tests/test_dq.py::test_every_present_code_resolves_to_a_label fails if any staged row carries a code with no label. A new code stops a build, which is the intended cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>A29</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>PRIJEM is the only credit type; VYDAJ and VYBER are both debits.</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>Documented with the dataset, and consistent with the reported running balance: the balance chain reconciles for 4,364 of 4,500 accounts under this sign convention and would reconcile for almost none under any other.</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>Every monetary answer that nets or directs money (Q5, Q9) depends on it. The balance reconciliation rule is the check: a wrong sign convention would make it fail at scale rather than for 55 accounts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>A30</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>C10, C20</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>balance_after as reported by the bank is authoritative; the pipeline never recomputes it from the amounts.</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>It is the bank's own record of the account state after the posting. Recomputing would substitute this pipeline's arithmetic for the bank's ledger.</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>The 55 accounts whose chain does not reconcile beyond 100 CZK are reported as a defect rather than corrected (D013). If the bank's balances were known to be unreliable, the derived balance would become the published one and those 55 would become silent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>A31</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>C19, C20</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>The extract is a point-in-time snapshot with no history: no attribute of a client, account or district changes over time within it.</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>There is no effective-date column anywhere in the eight files, and no table carries two versions of the same key.</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>No slowly changing dimensions are needed, which is why dim_client and dim_district are plain. A feed with history would need SCD2 on at least district attributes, since the 1995/1996 socio-economic columns are already two snapshots flattened into one row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>A32</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>C19</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>The dataset window is 1993-01-01 to 1998-12-31, and dim_date is generated to exactly that span.</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>Measured from the data: the earliest and latest transaction dates are exactly those two days.</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>A date outside the window would not join to dim_date and would drop out of any date-driven aggregate. VAL_DATE_OUT_OF_RANGE is the rule that makes that fail loudly rather than quietly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>A33</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>C16</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>Row order within a source file carries no meaning; the only ordering is by the date and key columns.</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>The files are flat extracts with no sequence column beyond the surrogate ids, and trans_id is demonstrably not chronological within a day (CON_INTRADAY_ORDER_AMBIGUOUS, 183 accounts).</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>If file order were the true posting order, the Q9 tie-break would have a better answer available and those 183 accounts would stop being ambiguous. _source_row is retained on every row, so that reading could be tested without a reload.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10846,1043 +13660,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D48"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="96" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Provenance: the command and timestamp behind every figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Step</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Command</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>Executed at (UTC)</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Detail</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>ingest</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>make ingest</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T09:40:30+00:00</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>{"run_id": "2ef9d717-7017-4891-b14f-70148b6a1f8d", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>profile</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>make profile</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T09:49:54+00:00</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>dq</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>make dq (dataset=stg)</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:00:21+00:00</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>{"run_id": "6b7688ee-905d-44cf-915c-2eea22ef2660", "dataset": "stg", "rules_executed": 123, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "duration_sec": 14.91, "defect_types": 14}</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>inject</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>python -m src.inject_defects</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:01:58+00:00</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>{"defects": 20, "rules_targeted": ["COMP_DISTRICT_REGION_MISSING", "COMP_LOAN_AMOUNT_MISSING", "COMP_LOAN_STATUS_MISSING", "CON_BALANCE_RECONCILIATION_MATERIAL", "CON_LOAN_BEFORE_ACCOUNT_OPEN", "CON_LOAN_PAYMENT_SCHEDULE", "CON_TYPE_OPERATION_DIRECTION", "REC_ROWCOUNT_RAW_TO_STG", "RI_ACCOUNT_DISTRICT", "RI_ACCOUNT_WITHOUT_OWNER", "RI_DISP_CLIENT", "UNQ_ACCOUNT_PK", "UNQ_ACCOUNT_SINGLE_OWNER", "UNQ_CLIENT_PK", "VAL_ACCOUNT_OPEN_DATE_UNPARSABLE", "VAL_CARD_TYPE_DOMAIN", "VAL_DATE_OUT_OF_RANGE", "VAL_LOAN_DURATION_DOMAIN", "VAL_LOAN_STATUS_DOMAIN", "VAL_TRANS_AMOUNT_NEGATIVE"]}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>dq</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>make dq (dataset=stg)</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:04:34+00:00</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>{"run_id": "861c72b9-c1c2-4902-815a-5ec9bdbbcc30", "dataset": "stg", "rules_executed": 123, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 17.22, "defect_types": 14}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>make model</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:08:06+00:00</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>{"row_counts": {"dim_date": 2191, "dim_district": 76, "dim_client": 5318, "dim_account": 4457, "bridge_disposition": 5367, "dim_card": 891, "fact_loan": 676, "fact_transaction": 1056317, "fact_account_month_end_balance": 185615}, "ref_codes": 27, "problems": ["core.dim_client.district_id -&gt; core.dim_district: 61 orphan rows", "core.dim_account.district_id -&gt; core.dim_district: 55 orphan rows", "core.bridge_disposition.client_id -&gt; core.dim_client: 50 orphan rows", "core.bridge_disposition.account_id -&gt; core.dim_account: 50 orphan rows", "core.fact_loan.account_id -&gt; core.dim_account: 6 orphan rows", "core.fact_transaction.account_id -&gt; core.dim_account: 11024 orphan rows", "core.fact_account_month_end_balance.account_id -&gt; core.dim_account: 1879 orphan rows", "core.v_account_owner covers 4451 of 4457 accounts"], "reconciliation_checks": 9}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>make model</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:08:39+00:00</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 27, "problems": [], "reconciliation_checks": 9}</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>make model</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:09:54+00:00</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 27, "problems": [], "reconciliation_checks": 9}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>make reference</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:12:01+00:00</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>{"questions": 10, "failures": []}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>entitlements</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>make entitlements</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:18:11+00:00</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 682, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 682, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 682, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>make model</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:18:45+00:00</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 27, "problems": [], "reconciliation_checks": 9}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>entitlements</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>make entitlements</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:18:46+00:00</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>semantic</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>make semantic</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:24:15+00:00</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>{"entities": 11, "columns": 100, "context_pack_chars": 27592, "problems": []}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>questions</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>make questions (provider=claude_cli, model=claude-sonnet-5-5)</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:30:54+00:00</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>{"answered": 10, "total": 10, "answered_first_attempt": 10, "run_as": "cro_global"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>dq</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>make dq (dataset=stg)</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:31:52+00:00</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>{"run_id": "5571d5ad-0b9c-4db4-95d2-d2e45ab16c19", "dataset": "stg", "rules_executed": 123, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 15.15, "defect_types": 14}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>make model</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:32:03+00:00</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 27, "problems": [], "reconciliation_checks": 9}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>make reference</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:32:20+00:00</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>{"questions": 10, "failures": []}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>questions</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>make questions (provider=claude_cli, model=claude-sonnet-5-5)</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:36:04+00:00</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>{"answered": 0, "total": 10, "answered_first_attempt": 0, "run_as": "cro_global"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>entitlements</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>make entitlements</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:36:21+00:00</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>questions</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>make questions (provider=claude_cli, model=claude-sonnet-5-5)</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:38:40+00:00</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>{"answered": 10, "total": 10, "answered_first_attempt": 10, "run_as": "cro_global"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>evaluate</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>make evaluate</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:39:22+00:00</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>{"tally": {"match": 9, "mismatch": 1}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>evaluate</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>make evaluate</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:40:15+00:00</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>{"tally": {"match": 10}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>workbook</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>make workbook</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:44:08+00:00</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>zip</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>make zip</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:45:18+00:00</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>{"files": 74, "size_kb": 469.7}</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>ddr</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>make ddr</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:47:20+00:00</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>{"words": 1520, "pages": 2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>zip</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>make zip</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:49:22+00:00</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>{"files": 79, "size_kb": 483.0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>ingest</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>make ingest</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:50:34+00:00</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>{"run_id": "bd7b7fd2-e741-459c-90ed-f1ce8a1b4fc8", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>profile</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>make profile</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:51:36+00:00</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>dq</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>make dq (dataset=stg)</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:51:53+00:00</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>{"run_id": "55ac5752-e529-4ad3-b3b6-2723e5a50227", "dataset": "stg", "rules_executed": 123, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 16.24, "defect_types": 14}</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>make model</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:52:04+00:00</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 27, "problems": [], "reconciliation_checks": 9}</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>entitlements</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>make entitlements</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:52:05+00:00</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>make reference</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:52:05+00:00</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>{"questions": 10, "failures": []}</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>semantic</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>make semantic</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:52:07+00:00</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>{"entities": 11, "columns": 100, "context_pack_chars": 27592, "problems": []}</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>entitlements</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>make entitlements</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:52:08+00:00</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>questions</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>make questions (provider=claude_cli, model=claude-sonnet-5-5)</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:54:03+00:00</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>{"answered": 10, "total": 10, "answered_first_attempt": 10, "run_as": "cro_global"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>evaluate</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>make evaluate</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:54:04+00:00</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>{"tally": {"match": 10}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>workbook</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>make workbook</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:54:55+00:00</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>ddr</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>make ddr</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:54:57+00:00</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>{"words": 1520, "pages": 2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>zip</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>make zip</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:54:57+00:00</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>{"files": 79, "size_kb": 482.3}</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>ddr</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>make ddr</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:55:21+00:00</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>{"words": 1527, "pages": 2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>workbook</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>make workbook</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:55:23+00:00</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>zip</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>make zip</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T10:55:23+00:00</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>{"files": 79, "size_kb": 482.3}</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>zip</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>make zip</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T12:22:41+00:00</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>{"files": 99, "size_kb": 1265.5}</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>workbook</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>make workbook</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T21:57:19+00:00</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>zip</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>make zip</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-22T21:57:20+00:00</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>{"files": 123, "size_kb": 1320.7}</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/deliverables/Berka_TakeHome_Submission.xlsx
+++ b/deliverables/Berka_TakeHome_Submission.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T07:53:55+00:00</t>
+          <t>2026-10-25T09:04:07+00:00</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>da3e93f</t>
+          <t>c1e2ead</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>11 entities, 100 described columns, 12 certified metrics, 7 caveats</t>
+          <t>11 entities, 101 described columns, 12 certified metrics, 7 caveats</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>145 passing</t>
+          <t>156 passing</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2444,6 +2444,688 @@
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>{"tally": {"match": 10}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>workbook</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>make workbook</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:53:56+00:00</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Cleaning", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>ddr</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>make ddr</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:53:58+00:00</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>{"words": 1780, "pages": 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>make zip</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:53:59+00:00</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>{"files": 139, "size_kb": 3068.8}</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>make zip</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:54:28+00:00</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>{"files": 138, "size_kb": 3064.9}</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>make zip</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:54:52+00:00</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>{"files": 138, "size_kb": 3064.9}</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>make zip</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:55:16+00:00</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>{"files": 138, "size_kb": 3065.3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>entitlements</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>make entitlements</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:48:18+00:00</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": null}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": null}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subject_client_id": n</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>entitlements</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>make entitlements</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:48:47+00:00</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subjec</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>entitlements</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>make entitlements</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:49:59+00:00</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subjec</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>make demo</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:53:18+00:00</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>{"principals": 6, "attempts": 13, "leaks": 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>make demo</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:53:37+00:00</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>{"principals": 6, "attempts": 13, "leaks": 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>make demo</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:54:03+00:00</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>{"principals": 6, "attempts": 13, "leaks": 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>ingest</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>make ingest</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:57:30+00:00</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>{"run_id": "9333367e-c3a2-4e61-91ff-605c39dc7d82", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>make profile</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:58:46+00:00</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>dq</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>make dq (dataset=stg)</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:59:10+00:00</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>{"run_id": "1e4ca221-e5cc-4fd2-8ca5-92a40b0e0728", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 22.96, "defect_types": 14}</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>make model</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:59:22+00:00</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>entitlements</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>make entitlements</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:59:25+00:00</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subjec</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>make reference</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:59:26+00:00</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>{"questions": 10, "failures": []}</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>make semantic</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:59:29+00:00</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>{"entities": 11, "columns": 100, "context_pack_chars": 27592, "problems": ["ai.my_entitlement.principal_type: present in the view but not described (an undocumented column is one the model will guess at)"]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>make semantic</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:59:52+00:00</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>{"entities": 11, "columns": 101, "context_pack_chars": 28453, "problems": []}</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>ingest</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>make ingest</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:00:01+00:00</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>{"run_id": "6f2cd8a4-fb2b-469b-9e44-707c900bd0f0", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>make profile</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:01:08+00:00</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>dq</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>make dq (dataset=stg)</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:01:28+00:00</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>{"run_id": "7fa1b4a2-c790-4d4a-8d0d-cd91f82b3331", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 19.21, "defect_types": 14}</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>make model</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:01:39+00:00</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>entitlements</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>make entitlements</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:01:42+00:00</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subjec</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>make reference</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:01:44+00:00</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>{"questions": 10, "failures": []}</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>make semantic</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:01:45+00:00</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>{"entities": 11, "columns": 101, "context_pack_chars": 28453, "problems": []}</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>entitlements</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>make entitlements</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:01:47+00:00</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subjec</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>make demo</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:01:48+00:00</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>{"principals": 6, "attempts": 13, "leaks": 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>questions</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>make questions (provider=claude_cli, model=claude-sonnet-5-5)</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:03:10+00:00</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>{"answered": 10, "total": 10, "answered_first_attempt": 10, "run_as": "cro_global"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>evaluate</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>make evaluate</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T09:03:10+00:00</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
         <is>
           <t>{"tally": {"match": 10}}</t>
         </is>
@@ -4249,17 +4931,17 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>SELECT l.loan_year AS loan_year, SUM(l.amount) AS total_loan_amount_czk, COUNT(*) AS loan_count FROM ai.loan AS l GROUP BY l.loan_year ORDER BY l.loan_year</t>
+          <t>SELECT loan_year, count(*) AS loan_count, sum(amount) AS total_loan_amount FROM ai.loan GROUP BY loan_year ORDER BY loan_year</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>loan_year=1993 | total_loan_amount_czk=2619276.0 | loan_count=20
-loan_year=1994 | total_loan_amount_czk=13379904.0 | loan_count=101
-loan_year=1995 | total_loan_amount_czk=13344372.0 | loan_count=90
-loan_year=1996 | total_loan_amount_czk=18317676.0 | loan_count=117
-loan_year=1997 | total_loan_amount_czk=30731364.0 | loan_count=196
-loan_year=1998 | total_loan_amount_czk=24869148.0 | loan_count=158</t>
+          <t>loan_year=1993 | loan_count=20 | total_loan_amount=2619276.0
+loan_year=1994 | loan_count=101 | total_loan_amount=13379904.0
+loan_year=1995 | loan_count=90 | total_loan_amount=13344372.0
+loan_year=1996 | loan_count=117 | total_loan_amount=18317676.0
+loan_year=1997 | loan_count=196 | total_loan_amount=30731364.0
+loan_year=1998 | loan_count=158 | total_loan_amount=24869148.0</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
@@ -4365,15 +5047,15 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>SELECT owner_card_type, count(*) AS loan_count, round(avg(amount), 2) AS average_loan_amount FROM ai.loan GROUP BY owner_card_type ORDER BY average_loan_amount DESC</t>
+          <t>SELECT owner_card_type, count(*) AS loan_count, sum(amount) AS total_loan_amount, round(avg(amount), 2) AS average_loan_amount FROM ai.loan GROUP BY owner_card_type ORDER BY average_loan_amount DESC</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>owner_card_type=junior | loan_count=21 | average_loan_amount=221970.29
-owner_card_type=gold | loan_count=16 | average_loan_amount=161880.75
-owner_card_type=no card | loan_count=512 | average_loan_amount=148864.71
-owner_card_type=classic | loan_count=133 | average_loan_amount=148808.57</t>
+          <t>owner_card_type=junior | loan_count=21 | total_loan_amount=4661376.0 | average_loan_amount=221970.29
+owner_card_type=gold | loan_count=16 | total_loan_amount=2590092.0 | average_loan_amount=161880.75
+owner_card_type=no card | loan_count=512 | total_loan_amount=76218732.0 | average_loan_amount=148864.71
+owner_card_type=classic | loan_count=133 | total_loan_amount=19791540.0 | average_loan_amount=148808.57</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
@@ -4449,21 +5131,21 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>SELECT t.account_district_id, t.account_district_name, t.account_region, sum(t.amount) AS incoming_transaction_amount, count(*) AS credit_posting_count, count(DISTINCT t.account_id) AS accounts_with_credits FROM ai.transaction t WHERE t.direction = 'credit' AND t.trans_date &gt;= DATE '1997-01-01' AND t.trans_date &lt; DATE '1998-01-01' GROUP BY t.account_district_id, t.account_district_name, t.account_region ORDER BY incoming_transaction_amount DESC, t.account_district_name ASC LIMIT 10</t>
+          <t>SELECT t.account_district_id, t.account_district_name, t.account_region, sum(t.amount) AS incoming_transaction_amount_czk, count(*) AS credit_posting_count, count(DISTINCT t.account_id) AS accounts_with_credits FROM ai.transaction t WHERE t.direction = 'credit' AND t.trans_date &gt;= DATE '1997-01-01' AND t.trans_date &lt; DATE '1998-01-01' GROUP BY t.account_district_id, t.account_district_name, t.account_region ORDER BY sum(t.amount) DESC, t.account_district_id LIMIT 10</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>account_district_id=1 | account_district_name=Hl.m. Praha | account_region=Prague | incoming_transaction_amount=115130200.1 | credit_posting_count=13611 | accounts_with_credits=554
-account_district_id=70 | account_district_name=Karvina | account_region=north Moravia | incoming_transaction_amount=28506437.1 | credit_posting_count=3802 | accounts_with_credits=152
-account_district_id=74 | account_district_name=Ostrava - mesto | account_region=north Moravia | incoming_transaction_amount=27689271.9 | credit_posting_count=3378 | accounts_with_credits=135
-account_district_id=54 | account_district_name=Brno - mesto | account_region=south Moravia | incoming_transaction_amount=23095083.4 | credit_posting_count=3041 | accounts_with_credits=128
-account_district_id=64 | account_district_name=Zlin | account_region=south Moravia | incoming_transaction_amount=19723168.5 | credit_posting_count=2299 | accounts_with_credits=92
-account_district_id=68 | account_district_name=Frydek - Mistek | account_region=north Moravia | incoming_transaction_amount=19087598.8 | credit_posting_count=2006 | accounts_with_credits=83
-account_district_id=72 | account_district_name=Olomouc | account_region=north Moravia | incoming_transaction_amount=15916397.0 | credit_posting_count=2129 | accounts_with_credits=88
-account_district_id=5 | account_district_name=Kolin | account_region=central Bohemia | incoming_transaction_amount=14471603.6 | credit_posting_count=1542 | accounts_with_credits=65
-account_district_id=52 | account_district_name=Usti nad Orlici | account_region=east Bohemia | incoming_transaction_amount=14085167.4 | credit_posting_count=1431 | accounts_with_credits=57
-account_district_id=19 | account_district_name=Prachatice | account_region=south Bohemia | incoming_transaction_amount=12163147.0 | credit_posting_count=1359 | accounts_with_credits=55</t>
+          <t>account_district_id=1 | account_district_name=Hl.m. Praha | account_region=Prague | incoming_transaction_amount_czk=115130200.1 | credit_posting_count=13611 | accounts_with_credits=554
+account_district_id=70 | account_district_name=Karvina | account_region=north Moravia | incoming_transaction_amount_czk=28506437.1 | credit_posting_count=3802 | accounts_with_credits=152
+account_district_id=74 | account_district_name=Ostrava - mesto | account_region=north Moravia | incoming_transaction_amount_czk=27689271.9 | credit_posting_count=3378 | accounts_with_credits=135
+account_district_id=54 | account_district_name=Brno - mesto | account_region=south Moravia | incoming_transaction_amount_czk=23095083.4 | credit_posting_count=3041 | accounts_with_credits=128
+account_district_id=64 | account_district_name=Zlin | account_region=south Moravia | incoming_transaction_amount_czk=19723168.5 | credit_posting_count=2299 | accounts_with_credits=92
+account_district_id=68 | account_district_name=Frydek - Mistek | account_region=north Moravia | incoming_transaction_amount_czk=19087598.8 | credit_posting_count=2006 | accounts_with_credits=83
+account_district_id=72 | account_district_name=Olomouc | account_region=north Moravia | incoming_transaction_amount_czk=15916397.0 | credit_posting_count=2129 | accounts_with_credits=88
+account_district_id=5 | account_district_name=Kolin | account_region=central Bohemia | incoming_transaction_amount_czk=14471603.6 | credit_posting_count=1542 | accounts_with_credits=65
+account_district_id=52 | account_district_name=Usti nad Orlici | account_region=east Bohemia | incoming_transaction_amount_czk=14085167.4 | credit_posting_count=1431 | accounts_with_credits=57
+account_district_id=19 | account_district_name=Prachatice | account_region=south Bohemia | incoming_transaction_amount_czk=12163147.0 | credit_posting_count=1359 | accounts_with_credits=55</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
@@ -4473,7 +5155,7 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>C5, C6, C7</t>
+          <t>C5, C7</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -4605,15 +5287,15 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>SELECT loan_status, status_code, count(*) AS loan_count, round(avg(owner_age_at_loan_start), 2) AS average_age_at_loan_start, count(*) FILTER (WHERE data_quality_flags @&gt; ARRAY['val_owner_age_at_loan_start']) AS flagged_under_15_loans, round(avg(owner_age_at_loan_start) FILTER (WHERE NOT (data_quality_flags @&gt; ARRAY['val_owner_age_at_loan_start'])), 2) AS average_age_excluding_flagged, count(*) FILTER (WHERE NOT (data_quality_flags @&gt; ARRAY['val_owner_age_at_loan_start'])) AS loan_count_excluding_flagged FROM ai.loan GROUP BY loan_status, status_code ORDER BY status_code</t>
+          <t>SELECT loan_status, status_code, count(*) AS loan_count, round(avg(owner_age_at_loan_start), 2) AS average_age_at_loan_start, count(*) FILTER (WHERE data_quality_flags @&gt; ARRAY['val_owner_age_at_loan_start']) AS under_15_owner_loans, round(avg(owner_age_at_loan_start) FILTER (WHERE NOT (data_quality_flags @&gt; ARRAY['val_owner_age_at_loan_start'])), 2) AS average_age_excluding_flagged FROM ai.loan GROUP BY loan_status, status_code ORDER BY status_code</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>loan_status=finished, paid in full | status_code=A | loan_count=203 | average_age_at_loan_start=37.07 | flagged_under_15_loans=4 | average_age_excluding_flagged=37.53 | loan_count_excluding_flagged=199
-loan_status=finished, unpaid (default) | status_code=B | loan_count=31 | average_age_at_loan_start=39.61 | flagged_under_15_loans=0 | average_age_excluding_flagged=39.61 | loan_count_excluding_flagged=31
-loan_status=running, no problem | status_code=C | loan_count=403 | average_age_at_loan_start=38.7 | flagged_under_15_loans=2 | average_age_excluding_flagged=38.82 | loan_count_excluding_flagged=401
-loan_status=running, client in debt | status_code=D | loan_count=45 | average_age_at_loan_start=37.0 | flagged_under_15_loans=0 | average_age_excluding_flagged=37.0 | loan_count_excluding_flagged=45</t>
+          <t>loan_status=finished, paid in full | status_code=A | loan_count=203 | average_age_at_loan_start=37.07 | under_15_owner_loans=4 | average_age_excluding_flagged=37.53
+loan_status=finished, unpaid (default) | status_code=B | loan_count=31 | average_age_at_loan_start=39.61 | under_15_owner_loans=0 | average_age_excluding_flagged=39.61
+loan_status=running, no problem | status_code=C | loan_count=403 | average_age_at_loan_start=38.7 | under_15_owner_loans=2 | average_age_excluding_flagged=38.82
+loan_status=running, client in debt | status_code=D | loan_count=45 | average_age_at_loan_start=37.0 | under_15_owner_loans=0 | average_age_excluding_flagged=37.0</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
@@ -4682,7 +5364,7 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -4728,12 +5410,12 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>SELECT DATE '1998-12-31' AS month_end_date, round(avg(closing_balance), 2) AS average_closing_balance, count(*) AS accounts_with_balance, count(*) FILTER (WHERE is_carried_forward) AS carried_forward_balances, count(*) FILTER (WHERE 'con_balance_reconciliation_material' = ANY(account_data_quality_flags)) AS accounts_with_reconciliation_flag FROM ai.account_month_end_balance WHERE month_end_date = DATE '1998-12-31'</t>
+          <t>SELECT round(avg(closing_balance), 2) AS average_month_end_balance, count(*) AS accounts_with_balance, count(*) FILTER (WHERE is_carried_forward) AS carried_forward_balances, count(*) FILTER (WHERE 'con_balance_reconciliation_material' = ANY(account_data_quality_flags)) AS accounts_with_reconciliation_flag FROM ai.account_month_end_balance WHERE month_end_date = DATE '1998-12-31'</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>month_end_date=1998-12-31 | average_closing_balance=43808.94 | accounts_with_balance=4500 | carried_forward_balances=76 | accounts_with_reconciliation_flag=55</t>
+          <t>average_month_end_balance=43808.94 | accounts_with_balance=4500 | carried_forward_balances=76 | accounts_with_reconciliation_flag=55</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
@@ -4790,14 +5472,14 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>SELECT statement_frequency, count(*) AS loan_count, count(*) FILTER (WHERE is_problematic) AS problematic_loan_count, round(100.0 * count(*) FILTER (WHERE is_problematic) / count(*), 2) AS problematic_loan_share FROM ai.loan GROUP BY statement_frequency ORDER BY problematic_loan_share DESC, statement_frequency</t>
+          <t>SELECT statement_frequency, count(*) AS loan_count, count(*) FILTER (WHERE is_problematic) AS problematic_loan_count, round(100.0 * count(*) FILTER (WHERE is_problematic) / count(*), 2) AS problematic_loan_share_pct FROM ai.loan GROUP BY statement_frequency ORDER BY problematic_loan_share_pct DESC, statement_frequency</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>statement_frequency=after transaction | loan_count=32 | problematic_loan_count=6 | problematic_loan_share=18.75
-statement_frequency=weekly | loan_count=91 | problematic_loan_count=11 | problematic_loan_share=12.09
-statement_frequency=monthly | loan_count=559 | problematic_loan_count=59 | problematic_loan_share=10.55</t>
+          <t>statement_frequency=after transaction | loan_count=32 | problematic_loan_count=6 | problematic_loan_share_pct=18.75
+statement_frequency=weekly | loan_count=91 | problematic_loan_count=11 | problematic_loan_share_pct=12.09
+statement_frequency=monthly | loan_count=559 | problematic_loan_count=59 | problematic_loan_share_pct=10.55</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
@@ -5219,12 +5901,12 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>total_loan_amount_czk</t>
+          <t>loan_count</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>loan_count</t>
+          <t>total_loan_amount</t>
         </is>
       </c>
     </row>
@@ -5233,10 +5915,10 @@
         <v>1993</v>
       </c>
       <c r="B39" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="C39" s="15" t="n">
         <v>2619276</v>
-      </c>
-      <c r="C39" s="15" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="40">
@@ -5244,10 +5926,10 @@
         <v>1994</v>
       </c>
       <c r="B40" s="15" t="n">
+        <v>101</v>
+      </c>
+      <c r="C40" s="15" t="n">
         <v>13379904</v>
-      </c>
-      <c r="C40" s="15" t="n">
-        <v>101</v>
       </c>
     </row>
     <row r="41">
@@ -5255,10 +5937,10 @@
         <v>1995</v>
       </c>
       <c r="B41" s="15" t="n">
+        <v>90</v>
+      </c>
+      <c r="C41" s="15" t="n">
         <v>13344372</v>
-      </c>
-      <c r="C41" s="15" t="n">
-        <v>90</v>
       </c>
     </row>
     <row r="42">
@@ -5266,10 +5948,10 @@
         <v>1996</v>
       </c>
       <c r="B42" s="15" t="n">
+        <v>117</v>
+      </c>
+      <c r="C42" s="15" t="n">
         <v>18317676</v>
-      </c>
-      <c r="C42" s="15" t="n">
-        <v>117</v>
       </c>
     </row>
     <row r="43">
@@ -5277,10 +5959,10 @@
         <v>1997</v>
       </c>
       <c r="B43" s="15" t="n">
+        <v>196</v>
+      </c>
+      <c r="C43" s="15" t="n">
         <v>30731364</v>
-      </c>
-      <c r="C43" s="15" t="n">
-        <v>196</v>
       </c>
     </row>
     <row r="44">
@@ -5288,10 +5970,10 @@
         <v>1998</v>
       </c>
       <c r="B44" s="15" t="n">
+        <v>158</v>
+      </c>
+      <c r="C44" s="15" t="n">
         <v>24869148</v>
-      </c>
-      <c r="C44" s="15" t="n">
-        <v>158</v>
       </c>
     </row>
     <row r="47">
@@ -5507,6 +6189,11 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
+          <t>total_loan_amount</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
           <t>average_loan_amount</t>
         </is>
       </c>
@@ -5521,6 +6208,9 @@
         <v>21</v>
       </c>
       <c r="C67" s="15" t="n">
+        <v>4661376</v>
+      </c>
+      <c r="D67" s="15" t="n">
         <v>221970.29</v>
       </c>
     </row>
@@ -5534,6 +6224,9 @@
         <v>16</v>
       </c>
       <c r="C68" s="15" t="n">
+        <v>2590092</v>
+      </c>
+      <c r="D68" s="15" t="n">
         <v>161880.75</v>
       </c>
     </row>
@@ -5547,6 +6240,9 @@
         <v>512</v>
       </c>
       <c r="C69" s="15" t="n">
+        <v>76218732</v>
+      </c>
+      <c r="D69" s="15" t="n">
         <v>148864.71</v>
       </c>
     </row>
@@ -5560,6 +6256,9 @@
         <v>133</v>
       </c>
       <c r="C70" s="15" t="n">
+        <v>19791540</v>
+      </c>
+      <c r="D70" s="15" t="n">
         <v>148808.57</v>
       </c>
     </row>
@@ -5909,7 +6608,7 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>incoming_transaction_amount</t>
+          <t>incoming_transaction_amount_czk</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -6743,17 +7442,12 @@
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>flagged_under_15_loans</t>
+          <t>under_15_owner_loans</t>
         </is>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
           <t>average_age_excluding_flagged</t>
-        </is>
-      </c>
-      <c r="G142" s="5" t="inlineStr">
-        <is>
-          <t>loan_count_excluding_flagged</t>
         </is>
       </c>
     </row>
@@ -6780,9 +7474,6 @@
       <c r="F143" s="15" t="n">
         <v>37.53</v>
       </c>
-      <c r="G143" s="15" t="n">
-        <v>199</v>
-      </c>
     </row>
     <row r="144">
       <c r="A144" s="15" t="inlineStr">
@@ -6807,9 +7498,6 @@
       <c r="F144" s="15" t="n">
         <v>39.61</v>
       </c>
-      <c r="G144" s="15" t="n">
-        <v>31</v>
-      </c>
     </row>
     <row r="145">
       <c r="A145" s="15" t="inlineStr">
@@ -6834,9 +7522,6 @@
       <c r="F145" s="15" t="n">
         <v>38.82</v>
       </c>
-      <c r="G145" s="15" t="n">
-        <v>401</v>
-      </c>
     </row>
     <row r="146">
       <c r="A146" s="15" t="inlineStr">
@@ -6860,9 +7545,6 @@
       </c>
       <c r="F146" s="15" t="n">
         <v>37</v>
-      </c>
-      <c r="G146" s="15" t="n">
-        <v>45</v>
       </c>
     </row>
     <row r="149">
@@ -7086,46 +7768,36 @@
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>month_end_date</t>
+          <t>average_month_end_balance</t>
         </is>
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>average_closing_balance</t>
+          <t>accounts_with_balance</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>accounts_with_balance</t>
+          <t>carried_forward_balances</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>carried_forward_balances</t>
-        </is>
-      </c>
-      <c r="E167" s="5" t="inlineStr">
-        <is>
           <t>accounts_with_reconciliation_flag</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="15" t="inlineStr">
-        <is>
-          <t>1998-12-31</t>
-        </is>
+      <c r="A168" s="15" t="n">
+        <v>43808.94</v>
       </c>
       <c r="B168" s="15" t="n">
-        <v>43808.94</v>
+        <v>4500</v>
       </c>
       <c r="C168" s="15" t="n">
-        <v>4500</v>
+        <v>76</v>
       </c>
       <c r="D168" s="15" t="n">
-        <v>76</v>
-      </c>
-      <c r="E168" s="15" t="n">
         <v>55</v>
       </c>
     </row>
@@ -7252,7 +7924,7 @@
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>problematic_loan_share</t>
+          <t>problematic_loan_share_pct</t>
         </is>
       </c>
     </row>
@@ -12081,7 +12753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -13016,6 +13688,141 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>A34</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Identity</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>A self-service customer authenticates as their own database login role, and that role is never shared, pooled or re-pointed.</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Same reasoning as A21/D009 for staff: session_user cannot be changed by any statement the caller or an LLM emits, because changing it needs a password neither ever sees.</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>This is the load-bearing assumption of the whole privacy claim. If customer logins were pooled behind one shared role, the entitlement would resolve to that shared role and every customer would see every other customer's data. Connection pooling is therefore named in the DDR as the first thing that must be redesigned, not quietly added.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>A35</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Identity</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>A customer is entitled to exactly the client record that sec.app_user.subject_client_id names, and the mapping from a real person to that client id is correct and is made outside this system.</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>This dataset has no identity documents, no logins and no names; the mapping from "the person at the counter" to client_id is the bank's KYC process, not a data-product concern.</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>The product enforces the mapping it is given. A wrong mapping shows the wrong person's data with the full force of a correct-looking entitlement, and nothing in this build could detect it. In a real deployment the insert into sec.app_user is the output of an identity-proofing process and should be auditable on that basis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>A36</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Identity</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>A customer sees the accounts they own, not the accounts they may merely operate as a disponent.</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>Consistency with A21 and the safer default for a privacy boundary (D022).</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>869 clients hold a disponent relationship. Under the other reading each of them would additionally see that account and its postings. It is one predicate in sec.v_my_accounts and it is a business decision, not a technical one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>A37</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>Privacy</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Reference data (districts, calendar, code catalogue) is not sensitive, so a customer may read all 77 districts even though they belong to one.</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>Same as A22: filtering it would break every group-by, and a district list reveals nothing about any client.</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>If district-level data were considered identifying in combination with other attributes, the policy would extend to it. Nothing else in the design changes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>A38</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Privacy</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>No read audit is required for this submission.</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>The brief asks who *can* see what, not what was actually read.</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>For a real bank this is a regulatory gap, not a simplification. It is listed in the worked example's limits and in the build review as the largest missing control.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13027,7 +13834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -13099,236 +13906,300 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>cro_global</t>
+          <t>client_11409</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Group risk, bank-wide reporting</t>
+          <t>Self-service customer (client 11409)</t>
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>5369</v>
+        <v>1</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>4500</v>
+        <v>1</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>682</v>
+        <v>1</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>1056319</v>
+        <v>643</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>77</v>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>ALL_CLIENTS</t>
+          <t>SELF:11409</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>rm_north</t>
+          <t>client_3763</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Relationship manager, northern book</t>
+          <t>Self-service customer (client 3763)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>1481</v>
+        <v>1</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>1241</v>
+        <v>1</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>179</v>
+        <v>1</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>294622</v>
+        <v>439</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>77</v>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>NORTH_BOOK</t>
+          <t>SELF:3763</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>rm_south</t>
+          <t>cro_global</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Relationship manager, southern book</t>
+          <t>Group risk, bank-wide reporting</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>1386</v>
+        <v>5369</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1157</v>
+        <v>4500</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>194</v>
+        <v>682</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>272331</v>
+        <v>1056319</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>77</v>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>SOUTH_BOOK</t>
+          <t>ALL_CLIENTS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>rm_unassigned</t>
+          <t>rm_north</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Newly created user with no portfolio yet</t>
+          <t>Relationship manager, northern book</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>0</v>
+        <v>1481</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0</v>
+        <v>1241</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0</v>
+        <v>294622</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>77</v>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
+          <t>NORTH_BOOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>rm_south</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Relationship manager, southern book</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>1386</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>1157</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>194</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>272331</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>SOUTH_BOOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>rm_unassigned</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Newly created user with no portfolio yet</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
           <t>(none)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>Row level security policies in force</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Table</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Policy</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Granted to</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Predicate</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>core.bridge_disposition</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>entitled_dispositions</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>{ai_consumer}</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>((client_id IN ( SELECT v_my_clients.client_id
    FROM sec.v_my_clients)) OR (account_id IN ( SELECT v_my_accounts.account_id
    FROM sec.v_my_accounts)))</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr"/>
-      <c r="F12" s="6" t="inlineStr"/>
-      <c r="G12" s="6" t="inlineStr"/>
-      <c r="H12" s="6" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>core.dim_account</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>entitled_accounts</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>{ai_consumer}</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>(account_id IN ( SELECT v_my_accounts.account_id
    FROM sec.v_my_accounts))</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>core.dim_card</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>entitled_cards</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>{ai_consumer}</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>(disp_id IN ( SELECT d.disp_id
    FROM core.bridge_disposition d
@@ -13336,60 +14207,6 @@
            FROM sec.v_my_accounts))))</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>core.dim_client</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>entitled_clients</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>{ai_consumer}</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>(client_id IN ( SELECT v_my_clients.client_id
-   FROM sec.v_my_clients))</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>core.fact_account_month_end_balance</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>entitled_balances</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>{ai_consumer}</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>(account_id IN ( SELECT v_my_accounts.account_id
-   FROM sec.v_my_accounts))</t>
-        </is>
-      </c>
       <c r="E16" s="6" t="inlineStr"/>
       <c r="F16" s="6" t="inlineStr"/>
       <c r="G16" s="6" t="inlineStr"/>
@@ -13398,12 +14215,12 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>core.fact_loan</t>
+          <t>core.dim_client</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>entitled_loans</t>
+          <t>entitled_clients</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -13413,8 +14230,8 @@
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>(account_id IN ( SELECT v_my_accounts.account_id
-   FROM sec.v_my_accounts))</t>
+          <t>(client_id IN ( SELECT v_my_clients.client_id
+   FROM sec.v_my_clients))</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr"/>
@@ -13425,12 +14242,12 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>core.fact_transaction</t>
+          <t>core.fact_account_month_end_balance</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>entitled_transactions</t>
+          <t>entitled_balances</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -13449,76 +14266,94 @@
       <c r="G18" s="6" t="inlineStr"/>
       <c r="H18" s="6" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>core.fact_loan</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>entitled_loans</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>{ai_consumer}</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>(account_id IN ( SELECT v_my_accounts.account_id
+   FROM sec.v_my_accounts))</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr"/>
+      <c r="F19" s="6" t="inlineStr"/>
+      <c r="G19" s="6" t="inlineStr"/>
+      <c r="H19" s="6" t="inlineStr"/>
+    </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>core.fact_transaction</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>entitled_transactions</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>{ai_consumer}</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>(account_id IN ( SELECT v_my_accounts.account_id
+   FROM sec.v_my_accounts))</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>Bypass attempts, and what happened</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>Attempt</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr"/>
-      <c r="D21" s="5" t="inlineStr"/>
-      <c r="E21" s="5" t="inlineStr"/>
-      <c r="F21" s="5" t="inlineStr"/>
-      <c r="G21" s="5" t="inlineStr"/>
-      <c r="H21" s="5" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>SET ROLE to another relationship manager</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>refused: no membership in that role</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr"/>
-      <c r="D22" s="6" t="inlineStr"/>
-      <c r="E22" s="6" t="inlineStr"/>
-      <c r="F22" s="6" t="inlineStr"/>
-      <c r="G22" s="6" t="inlineStr"/>
-      <c r="H22" s="6" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>SET ROLE to the pipeline owner (which bypasses RLS)</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>refused: no membership</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr"/>
-      <c r="D23" s="6" t="inlineStr"/>
-      <c r="E23" s="6" t="inlineStr"/>
-      <c r="F23" s="6" t="inlineStr"/>
-      <c r="G23" s="6" t="inlineStr"/>
-      <c r="H23" s="6" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Query the core base tables directly, around the ai views</t>
+          <t>SET ROLE to another relationship manager</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>allowed, and still filtered: the policy is on the table, so reaching the table reaches the policy</t>
+          <t>refused: no membership in that role</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr"/>
@@ -13531,12 +14366,12 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Read raw / stg / dq / inject</t>
+          <t>SET ROLE to the pipeline owner (which bypasses RLS)</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>refused: no privilege on those schemas</t>
+          <t>refused: no membership</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr"/>
@@ -13549,12 +14384,12 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>set_config('app.end_user', &lt;other user&gt;)</t>
+          <t>Query the core base tables directly, around the ai views</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>no effect: identity is session_user, not a session variable</t>
+          <t>allowed, and still filtered: the policy is on the table, so reaching the table reaches the policy</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr"/>
@@ -13567,12 +14402,12 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>INSERT into sec.portfolio_client to self-grant a portfolio</t>
+          <t>Read raw / stg / dq / inject</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>refused: no privilege</t>
+          <t>refused: no privilege on those schemas</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr"/>
@@ -13585,12 +14420,12 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>ALTER TABLE ... DISABLE ROW LEVEL SECURITY</t>
+          <t>set_config('app.end_user', &lt;other user&gt;)</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>refused: not the table owner</t>
+          <t>no effect: identity is session_user, not a session variable</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr"/>
@@ -13603,12 +14438,12 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>DROP POLICY</t>
+          <t>INSERT into sec.portfolio_client to self-grant a portfolio</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>refused: not the table owner</t>
+          <t>refused: no privilege</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr"/>
@@ -13621,12 +14456,12 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>UPDATE / DELETE / TRUNCATE anything in core</t>
+          <t>ALTER TABLE ... DISABLE ROW LEVEL SECURITY</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>refused: consumers hold SELECT only</t>
+          <t>refused: not the table owner</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr"/>
@@ -13639,12 +14474,12 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>FULL OUTER JOIN to widen the result</t>
+          <t>DROP POLICY</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>no leak: each table carries its own policy, so the result is the intersection</t>
+          <t>refused: not the table owner</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr"/>
@@ -13653,6 +14488,42 @@
       <c r="F31" s="6" t="inlineStr"/>
       <c r="G31" s="6" t="inlineStr"/>
       <c r="H31" s="6" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>UPDATE / DELETE / TRUNCATE anything in core</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>refused: consumers hold SELECT only</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr"/>
+      <c r="D32" s="6" t="inlineStr"/>
+      <c r="E32" s="6" t="inlineStr"/>
+      <c r="F32" s="6" t="inlineStr"/>
+      <c r="G32" s="6" t="inlineStr"/>
+      <c r="H32" s="6" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>FULL OUTER JOIN to widen the result</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>no leak: each table carries its own policy, so the result is the intersection</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr"/>
+      <c r="D33" s="6" t="inlineStr"/>
+      <c r="E33" s="6" t="inlineStr"/>
+      <c r="F33" s="6" t="inlineStr"/>
+      <c r="G33" s="6" t="inlineStr"/>
+      <c r="H33" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/deliverables/Berka_TakeHome_Submission.xlsx
+++ b/deliverables/Berka_TakeHome_Submission.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T09:04:07+00:00</t>
+          <t>2026-10-25T11:34:43+00:00</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>c1e2ead</t>
+          <t>a7da25a</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>11 entities, 101 described columns, 12 certified metrics, 7 caveats</t>
+          <t>11 entities, 106 described columns, 12 certified metrics, 7 caveats</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>156 passing</t>
+          <t>202 passing</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D104"/>
+  <dimension ref="A1:D123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -912,550 +912,550 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>ingest</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>make ingest</t>
+          <t>make zip</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T09:40:30+00:00</t>
+          <t>2026-10-22T10:49:22+00:00</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "2ef9d717-7017-4891-b14f-70148b6a1f8d", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
+          <t>{"files": 79, "size_kb": 483.0}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>ingest</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>make profile</t>
+          <t>make ingest</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T09:49:54+00:00</t>
+          <t>2026-10-22T10:50:34+00:00</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
+          <t>{"run_id": "bd7b7fd2-e741-459c-90ed-f1ce8a1b4fc8", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>dq</t>
+          <t>profile</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>make dq (dataset=stg)</t>
+          <t>make profile</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:00:21+00:00</t>
+          <t>2026-10-22T10:51:36+00:00</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "6b7688ee-905d-44cf-915c-2eea22ef2660", "dataset": "stg", "rules_executed": 123, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "duration_sec": 14.91, "defect_types": 14}</t>
+          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>inject</t>
+          <t>dq</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>python -m src.inject_defects</t>
+          <t>make dq (dataset=stg)</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:01:58+00:00</t>
+          <t>2026-10-22T10:51:53+00:00</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>{"defects": 20, "rules_targeted": ["COMP_DISTRICT_REGION_MISSING", "COMP_LOAN_AMOUNT_MISSING", "COMP_LOAN_STATUS_MISSING", "CON_BALANCE_RECONCILIATION_MATERIAL", "CON_LOAN_BEFORE_ACCOUNT_OPEN", "CON_LOAN_PAYMENT_SCHEDULE", "CON_TYPE_OPERATION_DIRECTION", "REC_ROWCOUNT_RAW_TO_STG", "RI_ACCOUNT_DISTRICT", "RI_ACCOUNT_WITHOUT_OWNER", "RI_DISP_CLIENT", "UNQ_ACCOUNT_PK", "UNQ_ACCOUNT_SINGLE_OWNER", "UNQ_CLIENT_PK", "VAL_ACCOUNT_OPEN_DATE_UNPARSABLE", "VAL_CARD_TYPE_DOMAIN", "VAL_DATE_OUT_OF_RANGE", "VAL_LOAN_DURATION_DOMAIN", "VAL_LOAN_STATUS_DOMAIN", "VAL_TRANS_AMOUNT_NEGATIVE"]}</t>
+          <t>{"run_id": "55ac5752-e529-4ad3-b3b6-2723e5a50227", "dataset": "stg", "rules_executed": 123, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 16.24, "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>dq</t>
+          <t>model</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>make dq (dataset=stg)</t>
+          <t>make model</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:04:34+00:00</t>
+          <t>2026-10-22T10:52:04+00:00</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "861c72b9-c1c2-4902-815a-5ec9bdbbcc30", "dataset": "stg", "rules_executed": 123, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 17.22, "defect_types": 14}</t>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 27, "problems": [], "reconciliation_checks": 9}</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>make model</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:08:06+00:00</t>
+          <t>2026-10-22T10:52:05+00:00</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>{"row_counts": {"dim_date": 2191, "dim_district": 76, "dim_client": 5318, "dim_account": 4457, "bridge_disposition": 5367, "dim_card": 891, "fact_loan": 676, "fact_transaction": 1056317, "fact_account_month_end_balance": 185615}, "ref_codes": 27, "problems": ["core.dim_client.district_id -&gt; core.dim_district: 61 orphan rows", "core.dim_account.district_id -&gt; core.dim_district: 55 orphan rows", "core.bridge_disposition.client_id -&gt; core.dim_client: 50 orphan rows", "core.bridge_disposition.account_id -&gt; core.dim_account: 50 orphan rows", "core.fact_loan.account_id -&gt; core.dim_account: 6 orphan rows", "core.fact_transaction.account_id -&gt; core.dim_account: 11024 orphan rows", "core.fact_account_month_end_balance.account_id -&gt; core.dim_account: 1879 orphan rows", "core.v_account_owner covers 4451 of 4457 accounts"], "reconciliation_checks": 9}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>make model</t>
+          <t>make reference</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:08:39+00:00</t>
+          <t>2026-10-22T10:52:05+00:00</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 27, "problems": [], "reconciliation_checks": 9}</t>
+          <t>{"questions": 10, "failures": []}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>semantic</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>make model</t>
+          <t>make semantic</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:09:54+00:00</t>
+          <t>2026-10-22T10:52:07+00:00</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 27, "problems": [], "reconciliation_checks": 9}</t>
+          <t>{"entities": 11, "columns": 100, "context_pack_chars": 27592, "problems": []}</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>make reference</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:12:01+00:00</t>
+          <t>2026-10-22T10:52:08+00:00</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>{"questions": 10, "failures": []}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>questions</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make questions (provider=claude_cli, model=claude-sonnet-5-5)</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:18:11+00:00</t>
+          <t>2026-10-22T10:54:03+00:00</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 682, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 682, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 682, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
+          <t>{"answered": 10, "total": 10, "answered_first_attempt": 10, "run_as": "cro_global"}</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>evaluate</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>make model</t>
+          <t>make evaluate</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:18:45+00:00</t>
+          <t>2026-10-22T10:54:04+00:00</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 27, "problems": [], "reconciliation_checks": 9}</t>
+          <t>{"tally": {"match": 10}}</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>workbook</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make workbook</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:18:46+00:00</t>
+          <t>2026-10-22T10:54:55+00:00</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
+          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>ddr</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>make semantic</t>
+          <t>make ddr</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:24:15+00:00</t>
+          <t>2026-10-22T10:54:57+00:00</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>{"entities": 11, "columns": 100, "context_pack_chars": 27592, "problems": []}</t>
+          <t>{"words": 1520, "pages": 2}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>questions</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>make questions (provider=claude_cli, model=claude-sonnet-5-5)</t>
+          <t>make zip</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:30:54+00:00</t>
+          <t>2026-10-22T10:54:57+00:00</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>{"answered": 10, "total": 10, "answered_first_attempt": 10, "run_as": "cro_global"}</t>
+          <t>{"files": 79, "size_kb": 482.3}</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>dq</t>
+          <t>ddr</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>make dq (dataset=stg)</t>
+          <t>make ddr</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:31:52+00:00</t>
+          <t>2026-10-22T10:55:21+00:00</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "5571d5ad-0b9c-4db4-95d2-d2e45ab16c19", "dataset": "stg", "rules_executed": 123, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 15.15, "defect_types": 14}</t>
+          <t>{"words": 1527, "pages": 2}</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>workbook</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>make model</t>
+          <t>make workbook</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:32:03+00:00</t>
+          <t>2026-10-22T10:55:23+00:00</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 27, "problems": [], "reconciliation_checks": 9}</t>
+          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>make reference</t>
+          <t>make zip</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:32:20+00:00</t>
+          <t>2026-10-22T10:55:23+00:00</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>{"questions": 10, "failures": []}</t>
+          <t>{"files": 79, "size_kb": 482.3}</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>questions</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>make questions (provider=claude_cli, model=claude-sonnet-5-5)</t>
+          <t>make zip</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:36:04+00:00</t>
+          <t>2026-10-22T12:22:41+00:00</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>{"answered": 0, "total": 10, "answered_first_attempt": 0, "run_as": "cro_global"}</t>
+          <t>{"files": 99, "size_kb": 1265.5}</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>workbook</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make workbook</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:36:21+00:00</t>
+          <t>2026-10-22T21:57:19+00:00</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
+          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>questions</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>make questions (provider=claude_cli, model=claude-sonnet-5-5)</t>
+          <t>make zip</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:38:40+00:00</t>
+          <t>2026-10-22T21:57:20+00:00</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>{"answered": 10, "total": 10, "answered_first_attempt": 10, "run_as": "cro_global"}</t>
+          <t>{"files": 123, "size_kb": 1320.7}</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>evaluate</t>
+          <t>workbook</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>make evaluate</t>
+          <t>make workbook</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:39:22+00:00</t>
+          <t>2026-10-22T21:58:04+00:00</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>{"tally": {"match": 9, "mismatch": 1}}</t>
+          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>evaluate</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>make evaluate</t>
+          <t>make zip</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:40:15+00:00</t>
+          <t>2026-10-22T21:58:04+00:00</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>{"tally": {"match": 10}}</t>
+          <t>{"files": 123, "size_kb": 1321.0}</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>workbook</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>make workbook</t>
+          <t>make zip</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:44:08+00:00</t>
+          <t>2026-10-22T21:59:11+00:00</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
+          <t>{"files": 124, "size_kb": 1325.4}</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>evaluate</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>make zip</t>
+          <t>make evaluate</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:45:18+00:00</t>
+          <t>2026-10-24T20:50:44+00:00</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>{"files": 74, "size_kb": 469.7}</t>
+          <t>{"tally": {"match": 10}}</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>ddr</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>make ddr</t>
+          <t>make zip</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:47:20+00:00</t>
+          <t>2026-10-24T20:55:43+00:00</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>{"words": 1520, "pages": 2}</t>
+          <t>{"files": 126, "size_kb": 1337.3}</t>
         </is>
       </c>
     </row>
@@ -1472,34 +1472,34 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:49:22+00:00</t>
+          <t>2026-10-24T20:56:09+00:00</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>{"files": 79, "size_kb": 483.0}</t>
+          <t>{"files": 126, "size_kb": 1337.5}</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>ingest</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>make ingest</t>
+          <t>make zip</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:50:34+00:00</t>
+          <t>2026-10-24T21:12:20+00:00</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "bd7b7fd2-e741-459c-90ed-f1ce8a1b4fc8", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
+          <t>{"files": 135, "size_kb": 3016.3}</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:51:36+00:00</t>
+          <t>2026-10-25T07:34:31+00:00</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:51:53+00:00</t>
+          <t>2026-10-25T07:34:55+00:00</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "55ac5752-e529-4ad3-b3b6-2723e5a50227", "dataset": "stg", "rules_executed": 123, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 16.24, "defect_types": 14}</t>
+          <t>{"run_id": "6b713b33-3916-4b91-93dd-8c6d67f491b9", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 23.38, "defect_types": 14}</t>
         </is>
       </c>
     </row>
@@ -1560,12 +1560,12 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:52:04+00:00</t>
+          <t>2026-10-25T07:35:19+00:00</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 27, "problems": [], "reconciliation_checks": 9}</t>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:52:05+00:00</t>
+          <t>2026-10-25T07:35:21+00:00</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -1594,308 +1594,308 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>model</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>make reference</t>
+          <t>make model</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:52:05+00:00</t>
+          <t>2026-10-25T07:35:38+00:00</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>{"questions": 10, "failures": []}</t>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>make semantic</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:52:07+00:00</t>
+          <t>2026-10-25T07:35:39+00:00</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>{"entities": 11, "columns": 100, "context_pack_chars": 27592, "problems": []}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>workbook</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make workbook</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:52:08+00:00</t>
+          <t>2026-10-25T07:45:15+00:00</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
+          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Cleaning", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>questions</t>
+          <t>ddr</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>make questions (provider=claude_cli, model=claude-sonnet-5-5)</t>
+          <t>make ddr</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:54:03+00:00</t>
+          <t>2026-10-25T07:46:05+00:00</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>{"answered": 10, "total": 10, "answered_first_attempt": 10, "run_as": "cro_global"}</t>
+          <t>{"words": 1780, "pages": 2}</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>evaluate</t>
+          <t>ingest</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>make evaluate</t>
+          <t>make ingest</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:54:04+00:00</t>
+          <t>2026-10-25T07:50:02+00:00</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>{"tally": {"match": 10}}</t>
+          <t>{"run_id": "077de4c5-5ccb-4a88-bb1d-76a8b7714643", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>workbook</t>
+          <t>profile</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>make workbook</t>
+          <t>make profile</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:54:55+00:00</t>
+          <t>2026-10-25T07:51:06+00:00</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
+          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>ddr</t>
+          <t>dq</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>make ddr</t>
+          <t>make dq (dataset=stg)</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:54:57+00:00</t>
+          <t>2026-10-25T07:51:23+00:00</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>{"words": 1520, "pages": 2}</t>
+          <t>{"run_id": "116e896d-afb0-4ddf-8119-c059382d5394", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 16.44, "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>model</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>make zip</t>
+          <t>make model</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:54:57+00:00</t>
+          <t>2026-10-25T07:51:34+00:00</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>{"files": 79, "size_kb": 482.3}</t>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>ddr</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>make ddr</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:55:21+00:00</t>
+          <t>2026-10-25T07:51:35+00:00</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>{"words": 1527, "pages": 2}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>workbook</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>make workbook</t>
+          <t>make reference</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:55:23+00:00</t>
+          <t>2026-10-25T07:51:36+00:00</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
+          <t>{"questions": 10, "failures": []}</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>semantic</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>make zip</t>
+          <t>make semantic</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:55:23+00:00</t>
+          <t>2026-10-25T07:51:38+00:00</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>{"files": 79, "size_kb": 482.3}</t>
+          <t>{"entities": 11, "columns": 100, "context_pack_chars": 27592, "problems": []}</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>make zip</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T12:22:41+00:00</t>
+          <t>2026-10-25T07:51:39+00:00</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>{"files": 99, "size_kb": 1265.5}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>workbook</t>
+          <t>questions</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>make workbook</t>
+          <t>make questions (provider=claude_cli, model=claude-sonnet-5-5)</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T21:57:19+00:00</t>
+          <t>2026-10-25T07:52:57+00:00</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
+          <t>{"answered": 10, "total": 10, "answered_first_attempt": 10, "run_as": "cro_global"}</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>evaluate</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>make zip</t>
+          <t>make evaluate</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T21:57:20+00:00</t>
+          <t>2026-10-25T07:52:58+00:00</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>{"files": 123, "size_kb": 1320.7}</t>
+          <t>{"tally": {"match": 10}}</t>
         </is>
       </c>
     </row>
@@ -1912,34 +1912,34 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T21:58:04+00:00</t>
+          <t>2026-10-25T07:53:56+00:00</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
+          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Cleaning", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>ddr</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>make zip</t>
+          <t>make ddr</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T21:58:04+00:00</t>
+          <t>2026-10-25T07:53:58+00:00</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>{"files": 123, "size_kb": 1321.0}</t>
+          <t>{"words": 1780, "pages": 2}</t>
         </is>
       </c>
     </row>
@@ -1956,34 +1956,34 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T21:59:11+00:00</t>
+          <t>2026-10-25T07:53:59+00:00</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>{"files": 124, "size_kb": 1325.4}</t>
+          <t>{"files": 139, "size_kb": 3068.8}</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>evaluate</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>make evaluate</t>
+          <t>make zip</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>2026-10-24T20:50:44+00:00</t>
+          <t>2026-10-25T07:54:28+00:00</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>{"tally": {"match": 10}}</t>
+          <t>{"files": 138, "size_kb": 3064.9}</t>
         </is>
       </c>
     </row>
@@ -2000,12 +2000,12 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>2026-10-24T20:55:43+00:00</t>
+          <t>2026-10-25T07:54:52+00:00</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>{"files": 126, "size_kb": 1337.3}</t>
+          <t>{"files": 138, "size_kb": 3064.9}</t>
         </is>
       </c>
     </row>
@@ -2022,782 +2022,782 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>2026-10-24T20:56:09+00:00</t>
+          <t>2026-10-25T07:55:16+00:00</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>{"files": 126, "size_kb": 1337.5}</t>
+          <t>{"files": 138, "size_kb": 3065.3}</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>make zip</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>2026-10-24T21:12:20+00:00</t>
+          <t>2026-10-25T08:48:18+00:00</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>{"files": 135, "size_kb": 3016.3}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": null}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": null}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subject_client_id": n</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>make profile</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:34:31+00:00</t>
+          <t>2026-10-25T08:48:47+00:00</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subjec</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>dq</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>make dq (dataset=stg)</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:34:55+00:00</t>
+          <t>2026-10-25T08:49:59+00:00</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "6b713b33-3916-4b91-93dd-8c6d67f491b9", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 23.38, "defect_types": 14}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subjec</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>make model</t>
+          <t>make demo</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:35:19+00:00</t>
+          <t>2026-10-25T08:53:18+00:00</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
+          <t>{"principals": 6, "attempts": 13, "leaks": 0}</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make demo</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:35:21+00:00</t>
+          <t>2026-10-25T08:53:37+00:00</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
+          <t>{"principals": 6, "attempts": 13, "leaks": 0}</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>make model</t>
+          <t>make demo</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:35:38+00:00</t>
+          <t>2026-10-25T08:54:03+00:00</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
+          <t>{"principals": 6, "attempts": 13, "leaks": 0}</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>ingest</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make ingest</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:35:39+00:00</t>
+          <t>2026-10-25T08:57:30+00:00</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
+          <t>{"run_id": "9333367e-c3a2-4e61-91ff-605c39dc7d82", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>workbook</t>
+          <t>profile</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>make workbook</t>
+          <t>make profile</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:45:15+00:00</t>
+          <t>2026-10-25T08:58:46+00:00</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Cleaning", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
+          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>ddr</t>
+          <t>dq</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>make ddr</t>
+          <t>make dq (dataset=stg)</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:46:05+00:00</t>
+          <t>2026-10-25T08:59:10+00:00</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>{"words": 1780, "pages": 2}</t>
+          <t>{"run_id": "1e4ca221-e5cc-4fd2-8ca5-92a40b0e0728", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 22.96, "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>ingest</t>
+          <t>model</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>make ingest</t>
+          <t>make model</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:50:02+00:00</t>
+          <t>2026-10-25T08:59:22+00:00</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "077de4c5-5ccb-4a88-bb1d-76a8b7714643", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>make profile</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:51:06+00:00</t>
+          <t>2026-10-25T08:59:25+00:00</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subjec</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>dq</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>make dq (dataset=stg)</t>
+          <t>make reference</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:51:23+00:00</t>
+          <t>2026-10-25T08:59:26+00:00</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "116e896d-afb0-4ddf-8119-c059382d5394", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 16.44, "defect_types": 14}</t>
+          <t>{"questions": 10, "failures": []}</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>semantic</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>make model</t>
+          <t>make semantic</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:51:34+00:00</t>
+          <t>2026-10-25T08:59:29+00:00</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
+          <t>{"entities": 11, "columns": 100, "context_pack_chars": 27592, "problems": ["ai.my_entitlement.principal_type: present in the view but not described (an undocumented column is one the model will guess at)"]}</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>semantic</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make semantic</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:51:35+00:00</t>
+          <t>2026-10-25T08:59:52+00:00</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
+          <t>{"entities": 11, "columns": 101, "context_pack_chars": 28453, "problems": []}</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>ingest</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>make reference</t>
+          <t>make ingest</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:51:36+00:00</t>
+          <t>2026-10-25T09:00:01+00:00</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>{"questions": 10, "failures": []}</t>
+          <t>{"run_id": "6f2cd8a4-fb2b-469b-9e44-707c900bd0f0", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>profile</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>make semantic</t>
+          <t>make profile</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:51:38+00:00</t>
+          <t>2026-10-25T09:01:08+00:00</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>{"entities": 11, "columns": 100, "context_pack_chars": 27592, "problems": []}</t>
+          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>dq</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make dq (dataset=stg)</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:51:39+00:00</t>
+          <t>2026-10-25T09:01:28+00:00</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
+          <t>{"run_id": "7fa1b4a2-c790-4d4a-8d0d-cd91f82b3331", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 19.21, "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>questions</t>
+          <t>model</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>make questions (provider=claude_cli, model=claude-sonnet-5-5)</t>
+          <t>make model</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:52:57+00:00</t>
+          <t>2026-10-25T09:01:39+00:00</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>{"answered": 10, "total": 10, "answered_first_attempt": 10, "run_as": "cro_global"}</t>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>evaluate</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>make evaluate</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:52:58+00:00</t>
+          <t>2026-10-25T09:01:42+00:00</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>{"tally": {"match": 10}}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subjec</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>workbook</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>make workbook</t>
+          <t>make reference</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:53:56+00:00</t>
+          <t>2026-10-25T09:01:44+00:00</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Cleaning", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
+          <t>{"questions": 10, "failures": []}</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>ddr</t>
+          <t>semantic</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>make ddr</t>
+          <t>make semantic</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:53:58+00:00</t>
+          <t>2026-10-25T09:01:45+00:00</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>{"words": 1780, "pages": 2}</t>
+          <t>{"entities": 11, "columns": 101, "context_pack_chars": 28453, "problems": []}</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>make zip</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:53:59+00:00</t>
+          <t>2026-10-25T09:01:47+00:00</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>{"files": 139, "size_kb": 3068.8}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subjec</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>make zip</t>
+          <t>make demo</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:54:28+00:00</t>
+          <t>2026-10-25T09:01:48+00:00</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>{"files": 138, "size_kb": 3064.9}</t>
+          <t>{"principals": 6, "attempts": 13, "leaks": 0}</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>questions</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>make zip</t>
+          <t>make questions (provider=claude_cli, model=claude-sonnet-5-5)</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:54:52+00:00</t>
+          <t>2026-10-25T09:03:10+00:00</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>{"files": 138, "size_kb": 3064.9}</t>
+          <t>{"answered": 10, "total": 10, "answered_first_attempt": 10, "run_as": "cro_global"}</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>evaluate</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>make zip</t>
+          <t>make evaluate</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:55:16+00:00</t>
+          <t>2026-10-25T09:03:10+00:00</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>{"files": 138, "size_kb": 3065.3}</t>
+          <t>{"tally": {"match": 10}}</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>workbook</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make workbook</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:48:18+00:00</t>
+          <t>2026-10-25T09:04:08+00:00</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": null}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": null}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subject_client_id": n</t>
+          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Cleaning", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>ddr</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make ddr</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:48:47+00:00</t>
+          <t>2026-10-25T09:04:10+00:00</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subjec</t>
+          <t>{"words": 1780, "pages": 2}</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make zip</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:49:59+00:00</t>
+          <t>2026-10-25T09:04:11+00:00</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subjec</t>
+          <t>{"files": 140, "size_kb": 3098.2}</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>ddr</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>make demo</t>
+          <t>make ddr</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:53:18+00:00</t>
+          <t>2026-10-25T09:04:28+00:00</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>{"principals": 6, "attempts": 13, "leaks": 0}</t>
+          <t>{"words": 1900, "pages": 2}</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>make demo</t>
+          <t>make zip</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:53:37+00:00</t>
+          <t>2026-10-25T09:05:52+00:00</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>{"principals": 6, "attempts": 13, "leaks": 0}</t>
+          <t>{"files": 141, "size_kb": 3103.3}</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>model</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>make demo</t>
+          <t>make model</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:54:03+00:00</t>
+          <t>2026-10-25T09:42:15+00:00</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>{"principals": 6, "attempts": 13, "leaks": 0}</t>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>ingest</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>make ingest</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:57:30+00:00</t>
+          <t>2026-10-25T09:42:17+00:00</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "9333367e-c3a2-4e61-91ff-605c39dc7d82", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "subject_client_id": 3764, "clients": 1, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": "SELF:3764"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clie</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>make profile</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:58:46+00:00</t>
+          <t>2026-10-25T09:47:55+00:00</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>dq</t>
+          <t>model</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>make dq (dataset=stg)</t>
+          <t>make model</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:59:10+00:00</t>
+          <t>2026-10-25T09:48:55+00:00</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "1e4ca221-e5cc-4fd2-8ca5-92a40b0e0728", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 22.96, "defect_types": 14}</t>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>make model</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:59:22+00:00</t>
+          <t>2026-10-25T09:48:59+00:00</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
         </is>
       </c>
     </row>
@@ -2814,320 +2814,738 @@
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:59:25+00:00</t>
+          <t>2026-10-25T11:00:47+00:00</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subjec</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>make reference</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:59:26+00:00</t>
+          <t>2026-10-25T11:03:42+00:00</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>{"questions": 10, "failures": []}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>ingest</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>make semantic</t>
+          <t>make ingest</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:59:29+00:00</t>
+          <t>2026-10-25T11:05:45+00:00</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>{"entities": 11, "columns": 100, "context_pack_chars": 27592, "problems": ["ai.my_entitlement.principal_type: present in the view but not described (an undocumented column is one the model will guess at)"]}</t>
+          <t>{"run_id": "768f6d57-1008-4ba7-a1a1-7995e12504a9", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>profile</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>make semantic</t>
+          <t>make profile</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:59:52+00:00</t>
+          <t>2026-10-25T11:06:54+00:00</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>{"entities": 11, "columns": 101, "context_pack_chars": 28453, "problems": []}</t>
+          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>ingest</t>
+          <t>dq</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>make ingest</t>
+          <t>make dq (dataset=stg)</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:00:01+00:00</t>
+          <t>2026-10-25T11:07:14+00:00</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "6f2cd8a4-fb2b-469b-9e44-707c900bd0f0", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
+          <t>{"run_id": "8bc261dd-5837-4eaf-8864-bf398749cfcb", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 18.74, "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>model</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>make profile</t>
+          <t>make model</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:08+00:00</t>
+          <t>2026-10-25T11:07:27+00:00</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>dq</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>make dq (dataset=stg)</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:28+00:00</t>
+          <t>2026-10-25T11:07:31+00:00</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "7fa1b4a2-c790-4d4a-8d0d-cd91f82b3331", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 19.21, "defect_types": 14}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>make model</t>
+          <t>make reference</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:39+00:00</t>
+          <t>2026-10-25T11:07:33+00:00</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
+          <t>{"questions": 10, "failures": []}</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>semantic</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make semantic</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:42+00:00</t>
+          <t>2026-10-25T11:07:34+00:00</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subjec</t>
+          <t>{"entities": 11, "columns": 101, "context_pack_chars": 28453, "problems": ["ai.client.client_ref: present in the view but not described (an undocumented column is one the model will guess at)", "ai.account.account_ref: present in the view but not described (an undocumented column is one the model will guess at)", "ai.account_owner.account_ref: present in the view but not described (an undocumented column is one the model will guess at)", "ai.account_owner.owner_client_ref: present in the view but not described (an undocumented column is one the model will guess at)"]}</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>semantic</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>make reference</t>
+          <t>make semantic</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:44+00:00</t>
+          <t>2026-10-25T11:07:58+00:00</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>{"questions": 10, "failures": []}</t>
+          <t>{"entities": 11, "columns": 106, "context_pack_chars": 29500, "problems": []}</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>ingest</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>make semantic</t>
+          <t>make ingest</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:45+00:00</t>
+          <t>2026-10-25T11:08:07+00:00</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>{"entities": 11, "columns": 101, "context_pack_chars": 28453, "problems": []}</t>
+          <t>{"run_id": "64293db3-d4d0-429e-a99d-74d6a0aa3959", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>profile</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make profile</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:47+00:00</t>
+          <t>2026-10-25T11:09:15+00:00</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subjec</t>
+          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>dq</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>make demo</t>
+          <t>make dq (dataset=stg)</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:48+00:00</t>
+          <t>2026-10-25T11:09:40+00:00</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>{"principals": 6, "attempts": 13, "leaks": 0}</t>
+          <t>{"run_id": "313199cc-62d3-4583-ae3d-70a1b1bc1750", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 24.2, "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>questions</t>
+          <t>model</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>make questions (provider=claude_cli, model=claude-sonnet-5-5)</t>
+          <t>make model</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:03:10+00:00</t>
+          <t>2026-10-25T11:09:56+00:00</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>{"answered": 10, "total": 10, "answered_first_attempt": 10, "run_as": "cro_global"}</t>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
+          <t>entitlements</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>make entitlements</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T11:10:01+00:00</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>make reference</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T11:10:03+00:00</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>{"questions": 10, "failures": []}</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>make semantic</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T11:10:04+00:00</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>{"entities": 11, "columns": 106, "context_pack_chars": 29500, "problems": []}</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>entitlements</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>make entitlements</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T11:10:09+00:00</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>make demo</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T11:13:30+00:00</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>{"principals": 8, "attempts": 13, "leaks": 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>ingest</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>make ingest</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T11:13:40+00:00</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>{"run_id": "126fe0e9-fd23-4ca4-96ab-2c2c6d16d0af", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>make profile</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T11:14:52+00:00</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>dq</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>make dq (dataset=stg)</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T11:15:12+00:00</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>{"run_id": "bd005a32-4474-4779-b235-1cd6a8d91e0b", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 19.75, "defect_types": 14}</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>make model</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T11:15:25+00:00</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>entitlements</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>make entitlements</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T11:15:30+00:00</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>make reference</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T11:15:32+00:00</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>{"questions": 10, "failures": []}</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>make semantic</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T11:15:34+00:00</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>{"entities": 11, "columns": 106, "context_pack_chars": 29500, "problems": []}</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>entitlements</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>make entitlements</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T11:15:38+00:00</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>make demo</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T11:17:00+00:00</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>{"principals": 8, "attempts": 13, "leaks": 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>questions</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>make questions (provider=claude_cli, model=claude-sonnet-5-5)</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T11:21:30+00:00</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>{"answered": 10, "total": 10, "answered_first_attempt": 10, "run_as": "cro_global"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
           <t>evaluate</t>
         </is>
       </c>
-      <c r="B104" s="6" t="inlineStr">
+      <c r="B119" s="6" t="inlineStr">
         <is>
           <t>make evaluate</t>
         </is>
       </c>
-      <c r="C104" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-25T09:03:10+00:00</t>
-        </is>
-      </c>
-      <c r="D104" s="6" t="inlineStr">
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T11:21:30+00:00</t>
+        </is>
+      </c>
+      <c r="D119" s="6" t="inlineStr">
         <is>
           <t>{"tally": {"match": 10}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>workbook</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>make workbook</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T11:24:05+00:00</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Cleaning", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>ddr</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>make ddr</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T11:24:11+00:00</t>
+        </is>
+      </c>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>{"words": 1900, "pages": 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>make zip</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T11:24:14+00:00</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>{"files": 148, "size_kb": 3139.3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>make zip</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25T11:31:24+00:00</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>{"files": 154, "size_kb": 4029.9}</t>
         </is>
       </c>
     </row>
@@ -4931,7 +5349,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>SELECT loan_year, count(*) AS loan_count, sum(amount) AS total_loan_amount FROM ai.loan GROUP BY loan_year ORDER BY loan_year</t>
+          <t>SELECT l.loan_year, count(*) AS loan_count, sum(l.amount) AS total_loan_amount FROM ai.loan AS l GROUP BY l.loan_year ORDER BY l.loan_year</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -5047,15 +5465,15 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>SELECT owner_card_type, count(*) AS loan_count, sum(amount) AS total_loan_amount, round(avg(amount), 2) AS average_loan_amount FROM ai.loan GROUP BY owner_card_type ORDER BY average_loan_amount DESC</t>
+          <t>SELECT owner_card_type, count(*) AS loan_count, round(avg(amount), 2) AS average_loan_amount FROM ai.loan GROUP BY owner_card_type ORDER BY owner_card_type</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>owner_card_type=junior | loan_count=21 | total_loan_amount=4661376.0 | average_loan_amount=221970.29
-owner_card_type=gold | loan_count=16 | total_loan_amount=2590092.0 | average_loan_amount=161880.75
-owner_card_type=no card | loan_count=512 | total_loan_amount=76218732.0 | average_loan_amount=148864.71
-owner_card_type=classic | loan_count=133 | total_loan_amount=19791540.0 | average_loan_amount=148808.57</t>
+          <t>owner_card_type=classic | loan_count=133 | average_loan_amount=148808.57
+owner_card_type=gold | loan_count=16 | average_loan_amount=161880.75
+owner_card_type=junior | loan_count=21 | average_loan_amount=221970.29
+owner_card_type=no card | loan_count=512 | average_loan_amount=148864.71</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
@@ -5131,21 +5549,21 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>SELECT t.account_district_id, t.account_district_name, t.account_region, sum(t.amount) AS incoming_transaction_amount_czk, count(*) AS credit_posting_count, count(DISTINCT t.account_id) AS accounts_with_credits FROM ai.transaction t WHERE t.direction = 'credit' AND t.trans_date &gt;= DATE '1997-01-01' AND t.trans_date &lt; DATE '1998-01-01' GROUP BY t.account_district_id, t.account_district_name, t.account_region ORDER BY sum(t.amount) DESC, t.account_district_id LIMIT 10</t>
+          <t>SELECT t.account_district_id, t.account_district_name, t.account_region, sum(t.amount) AS incoming_amount_czk, count(*) AS credit_postings, count(DISTINCT t.account_id) AS accounts_with_credits FROM ai.transaction t WHERE t.direction = 'credit' AND t.trans_date &gt;= DATE '1997-01-01' AND t.trans_date &lt; DATE '1998-01-01' GROUP BY t.account_district_id, t.account_district_name, t.account_region ORDER BY sum(t.amount) DESC, t.account_district_name ASC LIMIT 10</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>account_district_id=1 | account_district_name=Hl.m. Praha | account_region=Prague | incoming_transaction_amount_czk=115130200.1 | credit_posting_count=13611 | accounts_with_credits=554
-account_district_id=70 | account_district_name=Karvina | account_region=north Moravia | incoming_transaction_amount_czk=28506437.1 | credit_posting_count=3802 | accounts_with_credits=152
-account_district_id=74 | account_district_name=Ostrava - mesto | account_region=north Moravia | incoming_transaction_amount_czk=27689271.9 | credit_posting_count=3378 | accounts_with_credits=135
-account_district_id=54 | account_district_name=Brno - mesto | account_region=south Moravia | incoming_transaction_amount_czk=23095083.4 | credit_posting_count=3041 | accounts_with_credits=128
-account_district_id=64 | account_district_name=Zlin | account_region=south Moravia | incoming_transaction_amount_czk=19723168.5 | credit_posting_count=2299 | accounts_with_credits=92
-account_district_id=68 | account_district_name=Frydek - Mistek | account_region=north Moravia | incoming_transaction_amount_czk=19087598.8 | credit_posting_count=2006 | accounts_with_credits=83
-account_district_id=72 | account_district_name=Olomouc | account_region=north Moravia | incoming_transaction_amount_czk=15916397.0 | credit_posting_count=2129 | accounts_with_credits=88
-account_district_id=5 | account_district_name=Kolin | account_region=central Bohemia | incoming_transaction_amount_czk=14471603.6 | credit_posting_count=1542 | accounts_with_credits=65
-account_district_id=52 | account_district_name=Usti nad Orlici | account_region=east Bohemia | incoming_transaction_amount_czk=14085167.4 | credit_posting_count=1431 | accounts_with_credits=57
-account_district_id=19 | account_district_name=Prachatice | account_region=south Bohemia | incoming_transaction_amount_czk=12163147.0 | credit_posting_count=1359 | accounts_with_credits=55</t>
+          <t>account_district_id=1 | account_district_name=Hl.m. Praha | account_region=Prague | incoming_amount_czk=115130200.1 | credit_postings=13611 | accounts_with_credits=554
+account_district_id=70 | account_district_name=Karvina | account_region=north Moravia | incoming_amount_czk=28506437.1 | credit_postings=3802 | accounts_with_credits=152
+account_district_id=74 | account_district_name=Ostrava - mesto | account_region=north Moravia | incoming_amount_czk=27689271.9 | credit_postings=3378 | accounts_with_credits=135
+account_district_id=54 | account_district_name=Brno - mesto | account_region=south Moravia | incoming_amount_czk=23095083.4 | credit_postings=3041 | accounts_with_credits=128
+account_district_id=64 | account_district_name=Zlin | account_region=south Moravia | incoming_amount_czk=19723168.5 | credit_postings=2299 | accounts_with_credits=92
+account_district_id=68 | account_district_name=Frydek - Mistek | account_region=north Moravia | incoming_amount_czk=19087598.8 | credit_postings=2006 | accounts_with_credits=83
+account_district_id=72 | account_district_name=Olomouc | account_region=north Moravia | incoming_amount_czk=15916397.0 | credit_postings=2129 | accounts_with_credits=88
+account_district_id=5 | account_district_name=Kolin | account_region=central Bohemia | incoming_amount_czk=14471603.6 | credit_postings=1542 | accounts_with_credits=65
+account_district_id=52 | account_district_name=Usti nad Orlici | account_region=east Bohemia | incoming_amount_czk=14085167.4 | credit_postings=1431 | accounts_with_credits=57
+account_district_id=19 | account_district_name=Prachatice | account_region=south Bohemia | incoming_amount_czk=12163147.0 | credit_postings=1359 | accounts_with_credits=55</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
@@ -5212,23 +5630,23 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>SELECT c.year_month AS month, COUNT(a.account_id) AS new_accounts FROM ai.calendar c LEFT JOIN ai.account a ON a.open_date = c.date_key WHERE c.year = 1996 GROUP BY c.year_month ORDER BY c.year_month</t>
+          <t>SELECT c.year_month AS month, c.month_start, COUNT(a.account_id) AS new_accounts FROM (SELECT DISTINCT year_month, month_start FROM ai.calendar WHERE year = 1996) AS c LEFT JOIN ai.account AS a ON a.open_date &gt;= c.month_start AND a.open_date &lt; (c.month_start + INTERVAL '1 month') GROUP BY c.year_month, c.month_start ORDER BY c.month_start</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>month=1996-01 | new_accounts=106
-month=1996-02 | new_accounts=104
-month=1996-03 | new_accounts=124
-month=1996-04 | new_accounts=101
-month=1996-05 | new_accounts=91
-month=1996-06 | new_accounts=113
-month=1996-07 | new_accounts=137
-month=1996-08 | new_accounts=133
-month=1996-09 | new_accounts=108
-month=1996-10 | new_accounts=115
-month=1996-11 | new_accounts=106
-month=1996-12 | new_accounts=125</t>
+          <t>month=1996-01 | month_start=1996-01-01 | new_accounts=106
+month=1996-02 | month_start=1996-02-01 | new_accounts=104
+month=1996-03 | month_start=1996-03-01 | new_accounts=124
+month=1996-04 | month_start=1996-04-01 | new_accounts=101
+month=1996-05 | month_start=1996-05-01 | new_accounts=91
+month=1996-06 | month_start=1996-06-01 | new_accounts=113
+month=1996-07 | month_start=1996-07-01 | new_accounts=137
+month=1996-08 | month_start=1996-08-01 | new_accounts=133
+month=1996-09 | month_start=1996-09-01 | new_accounts=108
+month=1996-10 | month_start=1996-10-01 | new_accounts=115
+month=1996-11 | month_start=1996-11-01 | new_accounts=106
+month=1996-12 | month_start=1996-12-01 | new_accounts=125</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
@@ -5287,15 +5705,15 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>SELECT loan_status, status_code, count(*) AS loan_count, round(avg(owner_age_at_loan_start), 2) AS average_age_at_loan_start, count(*) FILTER (WHERE data_quality_flags @&gt; ARRAY['val_owner_age_at_loan_start']) AS under_15_owner_loans, round(avg(owner_age_at_loan_start) FILTER (WHERE NOT (data_quality_flags @&gt; ARRAY['val_owner_age_at_loan_start'])), 2) AS average_age_excluding_flagged FROM ai.loan GROUP BY loan_status, status_code ORDER BY status_code</t>
+          <t>SELECT loan_status, status_code, count(*) AS loan_count, round(avg(owner_age_at_loan_start), 2) AS average_age_at_loan_start, count(*) FILTER (WHERE 'val_owner_age_at_loan_start' = ANY(data_quality_flags)) AS flagged_under_15_loans, round(avg(owner_age_at_loan_start) FILTER (WHERE NOT ('val_owner_age_at_loan_start' = ANY(data_quality_flags))), 2) AS average_age_excluding_flagged FROM ai.loan GROUP BY loan_status, status_code ORDER BY status_code</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>loan_status=finished, paid in full | status_code=A | loan_count=203 | average_age_at_loan_start=37.07 | under_15_owner_loans=4 | average_age_excluding_flagged=37.53
-loan_status=finished, unpaid (default) | status_code=B | loan_count=31 | average_age_at_loan_start=39.61 | under_15_owner_loans=0 | average_age_excluding_flagged=39.61
-loan_status=running, no problem | status_code=C | loan_count=403 | average_age_at_loan_start=38.7 | under_15_owner_loans=2 | average_age_excluding_flagged=38.82
-loan_status=running, client in debt | status_code=D | loan_count=45 | average_age_at_loan_start=37.0 | under_15_owner_loans=0 | average_age_excluding_flagged=37.0</t>
+          <t>loan_status=finished, paid in full | status_code=A | loan_count=203 | average_age_at_loan_start=37.07 | flagged_under_15_loans=4 | average_age_excluding_flagged=37.53
+loan_status=finished, unpaid (default) | status_code=B | loan_count=31 | average_age_at_loan_start=39.61 | flagged_under_15_loans=0 | average_age_excluding_flagged=39.61
+loan_status=running, no problem | status_code=C | loan_count=403 | average_age_at_loan_start=38.7 | flagged_under_15_loans=2 | average_age_excluding_flagged=38.82
+loan_status=running, client in debt | status_code=D | loan_count=45 | average_age_at_loan_start=37.0 | flagged_under_15_loans=0 | average_age_excluding_flagged=37.0</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
@@ -5364,7 +5782,7 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -5410,12 +5828,12 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>SELECT round(avg(closing_balance), 2) AS average_month_end_balance, count(*) AS accounts_with_balance, count(*) FILTER (WHERE is_carried_forward) AS carried_forward_balances, count(*) FILTER (WHERE 'con_balance_reconciliation_material' = ANY(account_data_quality_flags)) AS accounts_with_reconciliation_flag FROM ai.account_month_end_balance WHERE month_end_date = DATE '1998-12-31'</t>
+          <t>SELECT DATE '1998-12-31' AS month_end_date, round(avg(closing_balance), 2) AS average_month_end_balance, count(*) AS accounts_with_balance, count(*) FILTER (WHERE is_carried_forward) AS carried_forward_balances, count(*) FILTER (WHERE 'con_balance_reconciliation_material' = ANY(account_data_quality_flags)) AS accounts_with_reconciliation_flag FROM ai.account_month_end_balance WHERE month_end_date = DATE '1998-12-31'</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>average_month_end_balance=43808.94 | accounts_with_balance=4500 | carried_forward_balances=76 | accounts_with_reconciliation_flag=55</t>
+          <t>month_end_date=1998-12-31 | average_month_end_balance=43808.94 | accounts_with_balance=4500 | carried_forward_balances=76 | accounts_with_reconciliation_flag=55</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
@@ -6189,11 +6607,6 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>total_loan_amount</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="inlineStr">
-        <is>
           <t>average_loan_amount</t>
         </is>
       </c>
@@ -6201,17 +6614,14 @@
     <row r="67">
       <c r="A67" s="15" t="inlineStr">
         <is>
-          <t>junior</t>
+          <t>classic</t>
         </is>
       </c>
       <c r="B67" s="15" t="n">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="C67" s="15" t="n">
-        <v>4661376</v>
-      </c>
-      <c r="D67" s="15" t="n">
-        <v>221970.29</v>
+        <v>148808.57</v>
       </c>
     </row>
     <row r="68">
@@ -6224,42 +6634,33 @@
         <v>16</v>
       </c>
       <c r="C68" s="15" t="n">
-        <v>2590092</v>
-      </c>
-      <c r="D68" s="15" t="n">
         <v>161880.75</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="15" t="inlineStr">
         <is>
-          <t>no card</t>
+          <t>junior</t>
         </is>
       </c>
       <c r="B69" s="15" t="n">
-        <v>512</v>
+        <v>21</v>
       </c>
       <c r="C69" s="15" t="n">
-        <v>76218732</v>
-      </c>
-      <c r="D69" s="15" t="n">
-        <v>148864.71</v>
+        <v>221970.29</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="15" t="inlineStr">
         <is>
-          <t>classic</t>
+          <t>no card</t>
         </is>
       </c>
       <c r="B70" s="15" t="n">
-        <v>133</v>
+        <v>512</v>
       </c>
       <c r="C70" s="15" t="n">
-        <v>19791540</v>
-      </c>
-      <c r="D70" s="15" t="n">
-        <v>148808.57</v>
+        <v>148864.71</v>
       </c>
     </row>
     <row r="73">
@@ -6608,12 +7009,12 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>incoming_transaction_amount_czk</t>
+          <t>incoming_amount_czk</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>credit_posting_count</t>
+          <t>credit_postings</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
@@ -7129,6 +7530,11 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
+          <t>month_start</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
           <t>new_accounts</t>
         </is>
       </c>
@@ -7139,7 +7545,12 @@
           <t>1996-01</t>
         </is>
       </c>
-      <c r="B119" s="15" t="n">
+      <c r="B119" s="15" t="inlineStr">
+        <is>
+          <t>1996-01-01</t>
+        </is>
+      </c>
+      <c r="C119" s="15" t="n">
         <v>106</v>
       </c>
     </row>
@@ -7149,7 +7560,12 @@
           <t>1996-02</t>
         </is>
       </c>
-      <c r="B120" s="15" t="n">
+      <c r="B120" s="15" t="inlineStr">
+        <is>
+          <t>1996-02-01</t>
+        </is>
+      </c>
+      <c r="C120" s="15" t="n">
         <v>104</v>
       </c>
     </row>
@@ -7159,7 +7575,12 @@
           <t>1996-03</t>
         </is>
       </c>
-      <c r="B121" s="15" t="n">
+      <c r="B121" s="15" t="inlineStr">
+        <is>
+          <t>1996-03-01</t>
+        </is>
+      </c>
+      <c r="C121" s="15" t="n">
         <v>124</v>
       </c>
     </row>
@@ -7169,7 +7590,12 @@
           <t>1996-04</t>
         </is>
       </c>
-      <c r="B122" s="15" t="n">
+      <c r="B122" s="15" t="inlineStr">
+        <is>
+          <t>1996-04-01</t>
+        </is>
+      </c>
+      <c r="C122" s="15" t="n">
         <v>101</v>
       </c>
     </row>
@@ -7179,7 +7605,12 @@
           <t>1996-05</t>
         </is>
       </c>
-      <c r="B123" s="15" t="n">
+      <c r="B123" s="15" t="inlineStr">
+        <is>
+          <t>1996-05-01</t>
+        </is>
+      </c>
+      <c r="C123" s="15" t="n">
         <v>91</v>
       </c>
     </row>
@@ -7189,7 +7620,12 @@
           <t>1996-06</t>
         </is>
       </c>
-      <c r="B124" s="15" t="n">
+      <c r="B124" s="15" t="inlineStr">
+        <is>
+          <t>1996-06-01</t>
+        </is>
+      </c>
+      <c r="C124" s="15" t="n">
         <v>113</v>
       </c>
     </row>
@@ -7199,7 +7635,12 @@
           <t>1996-07</t>
         </is>
       </c>
-      <c r="B125" s="15" t="n">
+      <c r="B125" s="15" t="inlineStr">
+        <is>
+          <t>1996-07-01</t>
+        </is>
+      </c>
+      <c r="C125" s="15" t="n">
         <v>137</v>
       </c>
     </row>
@@ -7209,7 +7650,12 @@
           <t>1996-08</t>
         </is>
       </c>
-      <c r="B126" s="15" t="n">
+      <c r="B126" s="15" t="inlineStr">
+        <is>
+          <t>1996-08-01</t>
+        </is>
+      </c>
+      <c r="C126" s="15" t="n">
         <v>133</v>
       </c>
     </row>
@@ -7219,7 +7665,12 @@
           <t>1996-09</t>
         </is>
       </c>
-      <c r="B127" s="15" t="n">
+      <c r="B127" s="15" t="inlineStr">
+        <is>
+          <t>1996-09-01</t>
+        </is>
+      </c>
+      <c r="C127" s="15" t="n">
         <v>108</v>
       </c>
     </row>
@@ -7229,7 +7680,12 @@
           <t>1996-10</t>
         </is>
       </c>
-      <c r="B128" s="15" t="n">
+      <c r="B128" s="15" t="inlineStr">
+        <is>
+          <t>1996-10-01</t>
+        </is>
+      </c>
+      <c r="C128" s="15" t="n">
         <v>115</v>
       </c>
     </row>
@@ -7239,7 +7695,12 @@
           <t>1996-11</t>
         </is>
       </c>
-      <c r="B129" s="15" t="n">
+      <c r="B129" s="15" t="inlineStr">
+        <is>
+          <t>1996-11-01</t>
+        </is>
+      </c>
+      <c r="C129" s="15" t="n">
         <v>106</v>
       </c>
     </row>
@@ -7249,7 +7710,12 @@
           <t>1996-12</t>
         </is>
       </c>
-      <c r="B130" s="15" t="n">
+      <c r="B130" s="15" t="inlineStr">
+        <is>
+          <t>1996-12-01</t>
+        </is>
+      </c>
+      <c r="C130" s="15" t="n">
         <v>125</v>
       </c>
     </row>
@@ -7442,7 +7908,7 @@
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>under_15_owner_loans</t>
+          <t>flagged_under_15_loans</t>
         </is>
       </c>
       <c r="F142" s="5" t="inlineStr">
@@ -7768,36 +8234,46 @@
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
+          <t>month_end_date</t>
+        </is>
+      </c>
+      <c r="B167" s="5" t="inlineStr">
+        <is>
           <t>average_month_end_balance</t>
         </is>
       </c>
-      <c r="B167" s="5" t="inlineStr">
+      <c r="C167" s="5" t="inlineStr">
         <is>
           <t>accounts_with_balance</t>
         </is>
       </c>
-      <c r="C167" s="5" t="inlineStr">
+      <c r="D167" s="5" t="inlineStr">
         <is>
           <t>carried_forward_balances</t>
         </is>
       </c>
-      <c r="D167" s="5" t="inlineStr">
+      <c r="E167" s="5" t="inlineStr">
         <is>
           <t>accounts_with_reconciliation_flag</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="15" t="n">
+      <c r="A168" s="15" t="inlineStr">
+        <is>
+          <t>1998-12-31</t>
+        </is>
+      </c>
+      <c r="B168" s="15" t="n">
         <v>43808.94</v>
       </c>
-      <c r="B168" s="15" t="n">
+      <c r="C168" s="15" t="n">
         <v>4500</v>
       </c>
-      <c r="C168" s="15" t="n">
+      <c r="D168" s="15" t="n">
         <v>76</v>
       </c>
-      <c r="D168" s="15" t="n">
+      <c r="E168" s="15" t="n">
         <v>55</v>
       </c>
     </row>
@@ -12753,7 +13229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -13823,6 +14299,222 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>A39</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>Access</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>A customer may see every account they are authorised to OPERATE, including accounts they do not own.</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>What the bank tells its customers their app will show. Supersedes A36, which narrowed them to ownership; the decision was taken to the business reading and settled (D023).</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>869 clients hold a disposition on an account they do not own. Under the narrow reading each of them sees one fewer account. It is one branch in sec.v_access_grant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>A40</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>Access</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>A disposition grants the ACCOUNT and nothing else -- not the owner's client record, not their other accounts.</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>Authorising someone to pay a bill from your account is not authorising them to read you. Nobody signing that arrangement would expect otherwise.</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>If a disposition granted the owning client instead, every disponent would see their co-holder's full customer record. This is the single most consequential line in the access model, and it is tested by name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>A41</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>Access</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>A staff portfolio grants view and never operate.</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>Being accountable for a client is not authority to move their money.</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>Nothing acts on operate in this read-only product, so the distinction costs nothing today and cannot be recovered later if it is dropped now. A test pins it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>A42</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>Identity</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>An opaque client_ref is sufficient protection for an identifier that appears in a URL or on a statement; it does not need to be rotated per session.</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>It is unguessable without the salt, and row level security stops access regardless. The reference prevents enumeration and correlation, not access.</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>If a reference leaked in bulk, rebuilding under a new salt reissues all of them. Per-session identifiers would be stronger and would make every support conversation impossible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>A43</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>A time-based one-time code is an adequate second factor for this demonstration.</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>It is the standard most people already have an app for, and it is verifiable offline against RFC 6238.</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>TOTP is phishable in real time: a victim relaying a live code to an attacker defeats it. A deployment handling real money should prefer a phishing-resistant factor (WebAuthn/passkeys). The session model here would not change; only the factor would.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>A44</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Storing TOTP shared secrets in a recoverable form is acceptable here.</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>Verification requires the secret, so it cannot be hashed.</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>sec.auth_factor.secret is the most sensitive column in the schema. A real deployment encrypts it with a key held outside the database, so that a dump of the data is not a dump of everyone's second factor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>A45</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Binding a session to (db_role, pg_backend_pid) is sufficient to stop replay.</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>A stolen session id is useless on a different connection, and the holder cannot forge session_user either.</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>Backend pids are reused after wraparound. A replay would need the same pid, the same role and the session still inside its 30-minute window; the combination is thin but not impossible, and a production system would add the backend start time to the binding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>A46</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>Printing the one-time code in the demo console does not weaken the claims being demonstrated.</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>The control being shown is what the second factor *stops*, not where the code comes from; every other part of the path is the production one.</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>A system that can display your own second factor has one factor. It is marked as a demo affordance at every call site and is the first thing a deployment removes.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13834,7 +14526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -13906,44 +14598,44 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>client_11409</t>
+          <t>admin_demo</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Self-service customer (client 11409)</t>
+          <t>Demo administrator (data owner's view, via a portfolio)</t>
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>1</v>
+        <v>5369</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>1</v>
+        <v>4500</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>1</v>
+        <v>682</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>643</v>
+        <v>1056319</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>77</v>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>SELF:11409</t>
+          <t>ALL_CLIENTS</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>client_3763</t>
+          <t>client_11409</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Self-service customer (client 3763)</t>
+          <t>Self-service customer (client 11409)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
@@ -13956,250 +14648,314 @@
         <v>1</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>439</v>
+        <v>643</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>77</v>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>SELF:3763</t>
+          <t>SELF:11409</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>cro_global</t>
+          <t>client_3763</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Group risk, bank-wide reporting</t>
+          <t>Self-service customer (client 3763)</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>5369</v>
+        <v>1</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>4500</v>
+        <v>1</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>682</v>
+        <v>1</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>1056319</v>
+        <v>439</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>77</v>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>ALL_CLIENTS</t>
+          <t>SELF:3763</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>rm_north</t>
+          <t>client_3764</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Relationship manager, northern book</t>
+          <t>Self-service customer (client 3764)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>1481</v>
+        <v>1</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1241</v>
+        <v>1</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>179</v>
+        <v>1</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>294622</v>
+        <v>439</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>77</v>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>NORTH_BOOK</t>
+          <t>SELF:3764</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>rm_south</t>
+          <t>cro_global</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Relationship manager, southern book</t>
+          <t>Group risk, bank-wide reporting</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>1386</v>
+        <v>5369</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1157</v>
+        <v>4500</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>194</v>
+        <v>682</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>272331</v>
+        <v>1056319</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>77</v>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>SOUTH_BOOK</t>
+          <t>ALL_CLIENTS</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>rm_unassigned</t>
+          <t>rm_north</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Newly created user with no portfolio yet</t>
+          <t>Relationship manager, northern book</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>0</v>
+        <v>1481</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0</v>
+        <v>1241</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0</v>
+        <v>294622</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>77</v>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
+          <t>NORTH_BOOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>rm_south</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Relationship manager, southern book</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>1387</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>1158</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>195</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>272770</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>SOUTH_BOOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>rm_unassigned</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Newly created user with no portfolio yet</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
           <t>(none)</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>Row level security policies in force</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Table</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Policy</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Granted to</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Predicate</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr"/>
-      <c r="F13" s="5" t="inlineStr"/>
-      <c r="G13" s="5" t="inlineStr"/>
-      <c r="H13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>core.bridge_disposition</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>entitled_dispositions</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>{ai_consumer}</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>((client_id IN ( SELECT v_my_clients.client_id
    FROM sec.v_my_clients)) OR (account_id IN ( SELECT v_my_accounts.account_id
    FROM sec.v_my_accounts)))</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr"/>
+      <c r="F16" s="6" t="inlineStr"/>
+      <c r="G16" s="6" t="inlineStr"/>
+      <c r="H16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>core.dim_account</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>entitled_accounts</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>{ai_consumer}</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>(account_id IN ( SELECT v_my_accounts.account_id
    FROM sec.v_my_accounts))</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr"/>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>core.dim_card</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>entitled_cards</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>{ai_consumer}</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>(disp_id IN ( SELECT d.disp_id
    FROM core.bridge_disposition d
@@ -14207,60 +14963,6 @@
            FROM sec.v_my_accounts))))</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr"/>
-      <c r="F16" s="6" t="inlineStr"/>
-      <c r="G16" s="6" t="inlineStr"/>
-      <c r="H16" s="6" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>core.dim_client</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>entitled_clients</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>{ai_consumer}</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>(client_id IN ( SELECT v_my_clients.client_id
-   FROM sec.v_my_clients))</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr"/>
-      <c r="F17" s="6" t="inlineStr"/>
-      <c r="G17" s="6" t="inlineStr"/>
-      <c r="H17" s="6" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>core.fact_account_month_end_balance</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>entitled_balances</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>{ai_consumer}</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>(account_id IN ( SELECT v_my_accounts.account_id
-   FROM sec.v_my_accounts))</t>
-        </is>
-      </c>
       <c r="E18" s="6" t="inlineStr"/>
       <c r="F18" s="6" t="inlineStr"/>
       <c r="G18" s="6" t="inlineStr"/>
@@ -14269,12 +14971,12 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>core.fact_loan</t>
+          <t>core.dim_client</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>entitled_loans</t>
+          <t>entitled_clients</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -14284,8 +14986,8 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>(account_id IN ( SELECT v_my_accounts.account_id
-   FROM sec.v_my_accounts))</t>
+          <t>(client_id IN ( SELECT v_my_clients.client_id
+   FROM sec.v_my_clients))</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr"/>
@@ -14296,12 +14998,12 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>core.fact_transaction</t>
+          <t>core.fact_account_month_end_balance</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>entitled_transactions</t>
+          <t>entitled_balances</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -14320,76 +15022,94 @@
       <c r="G20" s="6" t="inlineStr"/>
       <c r="H20" s="6" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>core.fact_loan</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>entitled_loans</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>{ai_consumer}</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>(account_id IN ( SELECT v_my_accounts.account_id
+   FROM sec.v_my_accounts))</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+    </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>core.fact_transaction</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>entitled_transactions</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>{ai_consumer}</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>(account_id IN ( SELECT v_my_accounts.account_id
+   FROM sec.v_my_accounts))</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr"/>
+      <c r="F22" s="6" t="inlineStr"/>
+      <c r="G22" s="6" t="inlineStr"/>
+      <c r="H22" s="6" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>Bypass attempts, and what happened</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Attempt</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>SET ROLE to another relationship manager</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>refused: no membership in that role</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr"/>
-      <c r="D24" s="6" t="inlineStr"/>
-      <c r="E24" s="6" t="inlineStr"/>
-      <c r="F24" s="6" t="inlineStr"/>
-      <c r="G24" s="6" t="inlineStr"/>
-      <c r="H24" s="6" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>SET ROLE to the pipeline owner (which bypasses RLS)</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>refused: no membership</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Query the core base tables directly, around the ai views</t>
+          <t>SET ROLE to another relationship manager</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>allowed, and still filtered: the policy is on the table, so reaching the table reaches the policy</t>
+          <t>refused: no membership in that role</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr"/>
@@ -14402,12 +15122,12 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Read raw / stg / dq / inject</t>
+          <t>SET ROLE to the pipeline owner (which bypasses RLS)</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>refused: no privilege on those schemas</t>
+          <t>refused: no membership</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr"/>
@@ -14420,12 +15140,12 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>set_config('app.end_user', &lt;other user&gt;)</t>
+          <t>Query the core base tables directly, around the ai views</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>no effect: identity is session_user, not a session variable</t>
+          <t>allowed, and still filtered: the policy is on the table, so reaching the table reaches the policy</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr"/>
@@ -14438,12 +15158,12 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>INSERT into sec.portfolio_client to self-grant a portfolio</t>
+          <t>Read raw / stg / dq / inject</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>refused: no privilege</t>
+          <t>refused: no privilege on those schemas</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr"/>
@@ -14456,12 +15176,12 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>ALTER TABLE ... DISABLE ROW LEVEL SECURITY</t>
+          <t>set_config('app.end_user', &lt;other user&gt;)</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>refused: not the table owner</t>
+          <t>no effect: identity is session_user, not a session variable</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr"/>
@@ -14474,12 +15194,12 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>DROP POLICY</t>
+          <t>INSERT into sec.portfolio_client to self-grant a portfolio</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>refused: not the table owner</t>
+          <t>refused: no privilege</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr"/>
@@ -14492,12 +15212,12 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>UPDATE / DELETE / TRUNCATE anything in core</t>
+          <t>ALTER TABLE ... DISABLE ROW LEVEL SECURITY</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>refused: consumers hold SELECT only</t>
+          <t>refused: not the table owner</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr"/>
@@ -14510,12 +15230,12 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>FULL OUTER JOIN to widen the result</t>
+          <t>DROP POLICY</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>no leak: each table carries its own policy, so the result is the intersection</t>
+          <t>refused: not the table owner</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr"/>
@@ -14524,6 +15244,42 @@
       <c r="F33" s="6" t="inlineStr"/>
       <c r="G33" s="6" t="inlineStr"/>
       <c r="H33" s="6" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>UPDATE / DELETE / TRUNCATE anything in core</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>refused: consumers hold SELECT only</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr"/>
+      <c r="D34" s="6" t="inlineStr"/>
+      <c r="E34" s="6" t="inlineStr"/>
+      <c r="F34" s="6" t="inlineStr"/>
+      <c r="G34" s="6" t="inlineStr"/>
+      <c r="H34" s="6" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>FULL OUTER JOIN to widen the result</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>no leak: each table carries its own policy, so the result is the intersection</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr"/>
+      <c r="D35" s="6" t="inlineStr"/>
+      <c r="E35" s="6" t="inlineStr"/>
+      <c r="F35" s="6" t="inlineStr"/>
+      <c r="G35" s="6" t="inlineStr"/>
+      <c r="H35" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/deliverables/Berka_TakeHome_Submission.xlsx
+++ b/deliverables/Berka_TakeHome_Submission.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T11:34:43+00:00</t>
+          <t>2026-10-25T21:26:04+00:00</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>a7da25a</t>
+          <t>a9c9f38</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>202 passing</t>
+          <t>204 passing</t>
         </is>
       </c>
     </row>
@@ -922,452 +922,452 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:49:22+00:00</t>
+          <t>2026-10-24T21:12:20+00:00</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>{"files": 79, "size_kb": 483.0}</t>
+          <t>{"files": 135, "size_kb": 3016.3}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>ingest</t>
+          <t>profile</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>make ingest</t>
+          <t>make profile</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:50:34+00:00</t>
+          <t>2026-10-25T07:34:31+00:00</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "bd7b7fd2-e741-459c-90ed-f1ce8a1b4fc8", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
+          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>dq</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>make profile</t>
+          <t>make dq (dataset=stg)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:51:36+00:00</t>
+          <t>2026-10-25T07:34:55+00:00</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
+          <t>{"run_id": "6b713b33-3916-4b91-93dd-8c6d67f491b9", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 23.38, "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>dq</t>
+          <t>model</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>make dq (dataset=stg)</t>
+          <t>make model</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:51:53+00:00</t>
+          <t>2026-10-25T07:35:19+00:00</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "55ac5752-e529-4ad3-b3b6-2723e5a50227", "dataset": "stg", "rules_executed": 123, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 16.24, "defect_types": 14}</t>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>make model</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:52:04+00:00</t>
+          <t>2026-10-25T07:35:21+00:00</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 27, "problems": [], "reconciliation_checks": 9}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>model</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make model</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:52:05+00:00</t>
+          <t>2026-10-25T07:35:38+00:00</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>make reference</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:52:05+00:00</t>
+          <t>2026-10-25T07:35:39+00:00</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>{"questions": 10, "failures": []}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>workbook</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>make semantic</t>
+          <t>make workbook</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:52:07+00:00</t>
+          <t>2026-10-25T07:45:15+00:00</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>{"entities": 11, "columns": 100, "context_pack_chars": 27592, "problems": []}</t>
+          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Cleaning", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>ddr</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make ddr</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:52:08+00:00</t>
+          <t>2026-10-25T07:46:05+00:00</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
+          <t>{"words": 1780, "pages": 2}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>questions</t>
+          <t>ingest</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>make questions (provider=claude_cli, model=claude-sonnet-5-5)</t>
+          <t>make ingest</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:54:03+00:00</t>
+          <t>2026-10-25T07:50:02+00:00</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>{"answered": 10, "total": 10, "answered_first_attempt": 10, "run_as": "cro_global"}</t>
+          <t>{"run_id": "077de4c5-5ccb-4a88-bb1d-76a8b7714643", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>evaluate</t>
+          <t>profile</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>make evaluate</t>
+          <t>make profile</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:54:04+00:00</t>
+          <t>2026-10-25T07:51:06+00:00</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>{"tally": {"match": 10}}</t>
+          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>workbook</t>
+          <t>dq</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>make workbook</t>
+          <t>make dq (dataset=stg)</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:54:55+00:00</t>
+          <t>2026-10-25T07:51:23+00:00</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
+          <t>{"run_id": "116e896d-afb0-4ddf-8119-c059382d5394", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 16.44, "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>ddr</t>
+          <t>model</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>make ddr</t>
+          <t>make model</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:54:57+00:00</t>
+          <t>2026-10-25T07:51:34+00:00</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>{"words": 1520, "pages": 2}</t>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>make zip</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:54:57+00:00</t>
+          <t>2026-10-25T07:51:35+00:00</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>{"files": 79, "size_kb": 482.3}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>ddr</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>make ddr</t>
+          <t>make reference</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:55:21+00:00</t>
+          <t>2026-10-25T07:51:36+00:00</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>{"words": 1527, "pages": 2}</t>
+          <t>{"questions": 10, "failures": []}</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>workbook</t>
+          <t>semantic</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>make workbook</t>
+          <t>make semantic</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:55:23+00:00</t>
+          <t>2026-10-25T07:51:38+00:00</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
+          <t>{"entities": 11, "columns": 100, "context_pack_chars": 27592, "problems": []}</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>make zip</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T10:55:23+00:00</t>
+          <t>2026-10-25T07:51:39+00:00</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>{"files": 79, "size_kb": 482.3}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>questions</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>make zip</t>
+          <t>make questions (provider=claude_cli, model=claude-sonnet-5-5)</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T12:22:41+00:00</t>
+          <t>2026-10-25T07:52:57+00:00</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>{"files": 99, "size_kb": 1265.5}</t>
+          <t>{"answered": 10, "total": 10, "answered_first_attempt": 10, "run_as": "cro_global"}</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>workbook</t>
+          <t>evaluate</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>make workbook</t>
+          <t>make evaluate</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T21:57:19+00:00</t>
+          <t>2026-10-25T07:52:58+00:00</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
+          <t>{"tally": {"match": 10}}</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>workbook</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>make zip</t>
+          <t>make workbook</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T21:57:20+00:00</t>
+          <t>2026-10-25T07:53:56+00:00</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>{"files": 123, "size_kb": 1320.7}</t>
+          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Cleaning", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>workbook</t>
+          <t>ddr</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>make workbook</t>
+          <t>make ddr</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T21:58:04+00:00</t>
+          <t>2026-10-25T07:53:58+00:00</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
+          <t>{"words": 1780, "pages": 2}</t>
         </is>
       </c>
     </row>
@@ -1384,12 +1384,12 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T21:58:04+00:00</t>
+          <t>2026-10-25T07:53:59+00:00</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>{"files": 123, "size_kb": 1321.0}</t>
+          <t>{"files": 139, "size_kb": 3068.8}</t>
         </is>
       </c>
     </row>
@@ -1406,34 +1406,34 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22T21:59:11+00:00</t>
+          <t>2026-10-25T07:54:28+00:00</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>{"files": 124, "size_kb": 1325.4}</t>
+          <t>{"files": 138, "size_kb": 3064.9}</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>evaluate</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>make evaluate</t>
+          <t>make zip</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>2026-10-24T20:50:44+00:00</t>
+          <t>2026-10-25T07:54:52+00:00</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>{"tally": {"match": 10}}</t>
+          <t>{"files": 138, "size_kb": 3064.9}</t>
         </is>
       </c>
     </row>
@@ -1450,804 +1450,804 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>2026-10-24T20:55:43+00:00</t>
+          <t>2026-10-25T07:55:16+00:00</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>{"files": 126, "size_kb": 1337.3}</t>
+          <t>{"files": 138, "size_kb": 3065.3}</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>make zip</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>2026-10-24T20:56:09+00:00</t>
+          <t>2026-10-25T08:48:18+00:00</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>{"files": 126, "size_kb": 1337.5}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": null}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": null}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subject_client_id": n</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>make zip</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>2026-10-24T21:12:20+00:00</t>
+          <t>2026-10-25T08:48:47+00:00</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>{"files": 135, "size_kb": 3016.3}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subjec</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>make profile</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:34:31+00:00</t>
+          <t>2026-10-25T08:49:59+00:00</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subjec</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>dq</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>make dq (dataset=stg)</t>
+          <t>make demo</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:34:55+00:00</t>
+          <t>2026-10-25T08:53:18+00:00</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "6b713b33-3916-4b91-93dd-8c6d67f491b9", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 23.38, "defect_types": 14}</t>
+          <t>{"principals": 6, "attempts": 13, "leaks": 0}</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>make model</t>
+          <t>make demo</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:35:19+00:00</t>
+          <t>2026-10-25T08:53:37+00:00</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
+          <t>{"principals": 6, "attempts": 13, "leaks": 0}</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make demo</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:35:21+00:00</t>
+          <t>2026-10-25T08:54:03+00:00</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
+          <t>{"principals": 6, "attempts": 13, "leaks": 0}</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>ingest</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>make model</t>
+          <t>make ingest</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:35:38+00:00</t>
+          <t>2026-10-25T08:57:30+00:00</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
+          <t>{"run_id": "9333367e-c3a2-4e61-91ff-605c39dc7d82", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>profile</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make profile</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:35:39+00:00</t>
+          <t>2026-10-25T08:58:46+00:00</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
+          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>workbook</t>
+          <t>dq</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>make workbook</t>
+          <t>make dq (dataset=stg)</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:45:15+00:00</t>
+          <t>2026-10-25T08:59:10+00:00</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Cleaning", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
+          <t>{"run_id": "1e4ca221-e5cc-4fd2-8ca5-92a40b0e0728", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 22.96, "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>ddr</t>
+          <t>model</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>make ddr</t>
+          <t>make model</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:46:05+00:00</t>
+          <t>2026-10-25T08:59:22+00:00</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>{"words": 1780, "pages": 2}</t>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>ingest</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>make ingest</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:50:02+00:00</t>
+          <t>2026-10-25T08:59:25+00:00</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "077de4c5-5ccb-4a88-bb1d-76a8b7714643", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subjec</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>make profile</t>
+          <t>make reference</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:51:06+00:00</t>
+          <t>2026-10-25T08:59:26+00:00</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
+          <t>{"questions": 10, "failures": []}</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>dq</t>
+          <t>semantic</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>make dq (dataset=stg)</t>
+          <t>make semantic</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:51:23+00:00</t>
+          <t>2026-10-25T08:59:29+00:00</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "116e896d-afb0-4ddf-8119-c059382d5394", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 16.44, "defect_types": 14}</t>
+          <t>{"entities": 11, "columns": 100, "context_pack_chars": 27592, "problems": ["ai.my_entitlement.principal_type: present in the view but not described (an undocumented column is one the model will guess at)"]}</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>semantic</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>make model</t>
+          <t>make semantic</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:51:34+00:00</t>
+          <t>2026-10-25T08:59:52+00:00</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
+          <t>{"entities": 11, "columns": 101, "context_pack_chars": 28453, "problems": []}</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>ingest</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make ingest</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:51:35+00:00</t>
+          <t>2026-10-25T09:00:01+00:00</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
+          <t>{"run_id": "6f2cd8a4-fb2b-469b-9e44-707c900bd0f0", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>profile</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>make reference</t>
+          <t>make profile</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:51:36+00:00</t>
+          <t>2026-10-25T09:01:08+00:00</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>{"questions": 10, "failures": []}</t>
+          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>dq</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>make semantic</t>
+          <t>make dq (dataset=stg)</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:51:38+00:00</t>
+          <t>2026-10-25T09:01:28+00:00</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>{"entities": 11, "columns": 100, "context_pack_chars": 27592, "problems": []}</t>
+          <t>{"run_id": "7fa1b4a2-c790-4d4a-8d0d-cd91f82b3331", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 19.21, "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>model</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make model</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:51:39+00:00</t>
+          <t>2026-10-25T09:01:39+00:00</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>questions</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>make questions (provider=claude_cli, model=claude-sonnet-5-5)</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:52:57+00:00</t>
+          <t>2026-10-25T09:01:42+00:00</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>{"answered": 10, "total": 10, "answered_first_attempt": 10, "run_as": "cro_global"}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subjec</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>evaluate</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>make evaluate</t>
+          <t>make reference</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:52:58+00:00</t>
+          <t>2026-10-25T09:01:44+00:00</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>{"tally": {"match": 10}}</t>
+          <t>{"questions": 10, "failures": []}</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>workbook</t>
+          <t>semantic</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>make workbook</t>
+          <t>make semantic</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:53:56+00:00</t>
+          <t>2026-10-25T09:01:45+00:00</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Cleaning", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
+          <t>{"entities": 11, "columns": 101, "context_pack_chars": 28453, "problems": []}</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>ddr</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>make ddr</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:53:58+00:00</t>
+          <t>2026-10-25T09:01:47+00:00</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>{"words": 1780, "pages": 2}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subjec</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>make zip</t>
+          <t>make demo</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:53:59+00:00</t>
+          <t>2026-10-25T09:01:48+00:00</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>{"files": 139, "size_kb": 3068.8}</t>
+          <t>{"principals": 6, "attempts": 13, "leaks": 0}</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>questions</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>make zip</t>
+          <t>make questions (provider=claude_cli, model=claude-sonnet-5-5)</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:54:28+00:00</t>
+          <t>2026-10-25T09:03:10+00:00</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>{"files": 138, "size_kb": 3064.9}</t>
+          <t>{"answered": 10, "total": 10, "answered_first_attempt": 10, "run_as": "cro_global"}</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>evaluate</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>make zip</t>
+          <t>make evaluate</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:54:52+00:00</t>
+          <t>2026-10-25T09:03:10+00:00</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>{"files": 138, "size_kb": 3064.9}</t>
+          <t>{"tally": {"match": 10}}</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>workbook</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>make zip</t>
+          <t>make workbook</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:55:16+00:00</t>
+          <t>2026-10-25T09:04:08+00:00</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>{"files": 138, "size_kb": 3065.3}</t>
+          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Cleaning", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>ddr</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make ddr</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:48:18+00:00</t>
+          <t>2026-10-25T09:04:10+00:00</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": null}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": null}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subject_client_id": n</t>
+          <t>{"words": 1780, "pages": 2}</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make zip</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:48:47+00:00</t>
+          <t>2026-10-25T09:04:11+00:00</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subjec</t>
+          <t>{"files": 140, "size_kb": 3098.2}</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>ddr</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make ddr</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:49:59+00:00</t>
+          <t>2026-10-25T09:04:28+00:00</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subjec</t>
+          <t>{"words": 1900, "pages": 2}</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>make demo</t>
+          <t>make zip</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:53:18+00:00</t>
+          <t>2026-10-25T09:05:52+00:00</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>{"principals": 6, "attempts": 13, "leaks": 0}</t>
+          <t>{"files": 141, "size_kb": 3103.3}</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>model</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>make demo</t>
+          <t>make model</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:53:37+00:00</t>
+          <t>2026-10-25T09:42:15+00:00</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>{"principals": 6, "attempts": 13, "leaks": 0}</t>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>make demo</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:54:03+00:00</t>
+          <t>2026-10-25T09:42:17+00:00</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>{"principals": 6, "attempts": 13, "leaks": 0}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "subject_client_id": 3764, "clients": 1, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": "SELF:3764"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clie</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>ingest</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>make ingest</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:57:30+00:00</t>
+          <t>2026-10-25T09:47:55+00:00</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "9333367e-c3a2-4e61-91ff-605c39dc7d82", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>model</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>make profile</t>
+          <t>make model</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:58:46+00:00</t>
+          <t>2026-10-25T09:48:55+00:00</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>dq</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>make dq (dataset=stg)</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:59:10+00:00</t>
+          <t>2026-10-25T09:48:59+00:00</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "1e4ca221-e5cc-4fd2-8ca5-92a40b0e0728", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 22.96, "defect_types": 14}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>make model</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:59:22+00:00</t>
+          <t>2026-10-25T11:00:47+00:00</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
         </is>
       </c>
     </row>
@@ -2264,474 +2264,474 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:59:25+00:00</t>
+          <t>2026-10-25T11:03:42+00:00</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subjec</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>ingest</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>make reference</t>
+          <t>make ingest</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:59:26+00:00</t>
+          <t>2026-10-25T11:05:45+00:00</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>{"questions": 10, "failures": []}</t>
+          <t>{"run_id": "768f6d57-1008-4ba7-a1a1-7995e12504a9", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>profile</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>make semantic</t>
+          <t>make profile</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:59:29+00:00</t>
+          <t>2026-10-25T11:06:54+00:00</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>{"entities": 11, "columns": 100, "context_pack_chars": 27592, "problems": ["ai.my_entitlement.principal_type: present in the view but not described (an undocumented column is one the model will guess at)"]}</t>
+          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>dq</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>make semantic</t>
+          <t>make dq (dataset=stg)</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:59:52+00:00</t>
+          <t>2026-10-25T11:07:14+00:00</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>{"entities": 11, "columns": 101, "context_pack_chars": 28453, "problems": []}</t>
+          <t>{"run_id": "8bc261dd-5837-4eaf-8864-bf398749cfcb", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 18.74, "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>ingest</t>
+          <t>model</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>make ingest</t>
+          <t>make model</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:00:01+00:00</t>
+          <t>2026-10-25T11:07:27+00:00</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "6f2cd8a4-fb2b-469b-9e44-707c900bd0f0", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>make profile</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:08+00:00</t>
+          <t>2026-10-25T11:07:31+00:00</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>dq</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>make dq (dataset=stg)</t>
+          <t>make reference</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:28+00:00</t>
+          <t>2026-10-25T11:07:33+00:00</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "7fa1b4a2-c790-4d4a-8d0d-cd91f82b3331", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 19.21, "defect_types": 14}</t>
+          <t>{"questions": 10, "failures": []}</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>semantic</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>make model</t>
+          <t>make semantic</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:39+00:00</t>
+          <t>2026-10-25T11:07:34+00:00</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
+          <t>{"entities": 11, "columns": 101, "context_pack_chars": 28453, "problems": ["ai.client.client_ref: present in the view but not described (an undocumented column is one the model will guess at)", "ai.account.account_ref: present in the view but not described (an undocumented column is one the model will guess at)", "ai.account_owner.account_ref: present in the view but not described (an undocumented column is one the model will guess at)", "ai.account_owner.owner_client_ref: present in the view but not described (an undocumented column is one the model will guess at)"]}</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>semantic</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make semantic</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:42+00:00</t>
+          <t>2026-10-25T11:07:58+00:00</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subjec</t>
+          <t>{"entities": 11, "columns": 106, "context_pack_chars": 29500, "problems": []}</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>ingest</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>make reference</t>
+          <t>make ingest</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:44+00:00</t>
+          <t>2026-10-25T11:08:07+00:00</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>{"questions": 10, "failures": []}</t>
+          <t>{"run_id": "64293db3-d4d0-429e-a99d-74d6a0aa3959", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>profile</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>make semantic</t>
+          <t>make profile</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:45+00:00</t>
+          <t>2026-10-25T11:09:15+00:00</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>{"entities": 11, "columns": 101, "context_pack_chars": 28453, "problems": []}</t>
+          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>dq</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make dq (dataset=stg)</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:47+00:00</t>
+          <t>2026-10-25T11:09:40+00:00</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subjec</t>
+          <t>{"run_id": "313199cc-62d3-4583-ae3d-70a1b1bc1750", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 24.2, "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>model</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>make demo</t>
+          <t>make model</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:48+00:00</t>
+          <t>2026-10-25T11:09:56+00:00</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>{"principals": 6, "attempts": 13, "leaks": 0}</t>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>questions</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>make questions (provider=claude_cli, model=claude-sonnet-5-5)</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:03:10+00:00</t>
+          <t>2026-10-25T11:10:01+00:00</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>{"answered": 10, "total": 10, "answered_first_attempt": 10, "run_as": "cro_global"}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>evaluate</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>make evaluate</t>
+          <t>make reference</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:03:10+00:00</t>
+          <t>2026-10-25T11:10:03+00:00</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>{"tally": {"match": 10}}</t>
+          <t>{"questions": 10, "failures": []}</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>workbook</t>
+          <t>semantic</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>make workbook</t>
+          <t>make semantic</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:04:08+00:00</t>
+          <t>2026-10-25T11:10:04+00:00</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Cleaning", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
+          <t>{"entities": 11, "columns": 106, "context_pack_chars": 29500, "problems": []}</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>ddr</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>make ddr</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:04:10+00:00</t>
+          <t>2026-10-25T11:10:09+00:00</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>{"words": 1780, "pages": 2}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>make zip</t>
+          <t>make demo</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:04:11+00:00</t>
+          <t>2026-10-25T11:13:30+00:00</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>{"files": 140, "size_kb": 3098.2}</t>
+          <t>{"principals": 8, "attempts": 13, "leaks": 0}</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>ddr</t>
+          <t>ingest</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>make ddr</t>
+          <t>make ingest</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:04:28+00:00</t>
+          <t>2026-10-25T11:13:40+00:00</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>{"words": 1900, "pages": 2}</t>
+          <t>{"run_id": "126fe0e9-fd23-4ca4-96ab-2c2c6d16d0af", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>profile</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>make zip</t>
+          <t>make profile</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:05:52+00:00</t>
+          <t>2026-10-25T11:14:52+00:00</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>{"files": 141, "size_kb": 3103.3}</t>
+          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>dq</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>make model</t>
+          <t>make dq (dataset=stg)</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:42:15+00:00</t>
+          <t>2026-10-25T11:15:12+00:00</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
+          <t>{"run_id": "bd005a32-4474-4779-b235-1cd6a8d91e0b", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 19.75, "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>model</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make model</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:42:17+00:00</t>
+          <t>2026-10-25T11:15:25+00:00</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "subject_client_id": 3764, "clients": 1, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": "SELF:3764"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clie</t>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
         </is>
       </c>
     </row>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:47:55+00:00</t>
+          <t>2026-10-25T11:15:30+00:00</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
@@ -2760,44 +2760,44 @@
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>make model</t>
+          <t>make reference</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:48:55+00:00</t>
+          <t>2026-10-25T11:15:32+00:00</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
+          <t>{"questions": 10, "failures": []}</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>semantic</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make semantic</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:48:59+00:00</t>
+          <t>2026-10-25T11:15:34+00:00</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
+          <t>{"entities": 11, "columns": 106, "context_pack_chars": 29500, "problems": []}</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:00:47+00:00</t>
+          <t>2026-10-25T11:15:38+00:00</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
@@ -2826,726 +2826,726 @@
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make demo</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:03:42+00:00</t>
+          <t>2026-10-25T11:17:00+00:00</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
+          <t>{"principals": 8, "attempts": 13, "leaks": 0}</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>ingest</t>
+          <t>questions</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>make ingest</t>
+          <t>make questions (provider=claude_cli, model=claude-sonnet-5-5)</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:05:45+00:00</t>
+          <t>2026-10-25T11:21:30+00:00</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "768f6d57-1008-4ba7-a1a1-7995e12504a9", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
+          <t>{"answered": 10, "total": 10, "answered_first_attempt": 10, "run_as": "cro_global"}</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>evaluate</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>make profile</t>
+          <t>make evaluate</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:06:54+00:00</t>
+          <t>2026-10-25T11:21:30+00:00</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
+          <t>{"tally": {"match": 10}}</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>dq</t>
+          <t>workbook</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>make dq (dataset=stg)</t>
+          <t>make workbook</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:07:14+00:00</t>
+          <t>2026-10-25T11:24:05+00:00</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "8bc261dd-5837-4eaf-8864-bf398749cfcb", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 18.74, "defect_types": 14}</t>
+          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Cleaning", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>ddr</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>make model</t>
+          <t>make ddr</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:07:27+00:00</t>
+          <t>2026-10-25T11:24:11+00:00</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
+          <t>{"words": 1900, "pages": 2}</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make zip</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:07:31+00:00</t>
+          <t>2026-10-25T11:24:14+00:00</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
+          <t>{"files": 148, "size_kb": 3139.3}</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>make reference</t>
+          <t>make zip</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:07:33+00:00</t>
+          <t>2026-10-25T11:31:24+00:00</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>{"questions": 10, "failures": []}</t>
+          <t>{"files": 154, "size_kb": 4029.9}</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>workbook</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>make semantic</t>
+          <t>make workbook</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:07:34+00:00</t>
+          <t>2026-10-25T11:34:44+00:00</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>{"entities": 11, "columns": 101, "context_pack_chars": 28453, "problems": ["ai.client.client_ref: present in the view but not described (an undocumented column is one the model will guess at)", "ai.account.account_ref: present in the view but not described (an undocumented column is one the model will guess at)", "ai.account_owner.account_ref: present in the view but not described (an undocumented column is one the model will guess at)", "ai.account_owner.owner_client_ref: present in the view but not described (an undocumented column is one the model will guess at)"]}</t>
+          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Cleaning", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>ddr</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>make semantic</t>
+          <t>make ddr</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:07:58+00:00</t>
+          <t>2026-10-25T11:34:46+00:00</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>{"entities": 11, "columns": 106, "context_pack_chars": 29500, "problems": []}</t>
+          <t>{"words": 1900, "pages": 2}</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>ingest</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>make ingest</t>
+          <t>make zip</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:08:07+00:00</t>
+          <t>2026-10-25T11:34:47+00:00</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "64293db3-d4d0-429e-a99d-74d6a0aa3959", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
+          <t>{"files": 155, "size_kb": 4038.5}</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>make profile</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:09:15+00:00</t>
+          <t>2026-10-25T20:49:19+00:00</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>dq</t>
+          <t>ingest</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>make dq (dataset=stg)</t>
+          <t>make ingest</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:09:40+00:00</t>
+          <t>2026-10-25T20:50:32+00:00</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "313199cc-62d3-4583-ae3d-70a1b1bc1750", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 24.2, "defect_types": 14}</t>
+          <t>{"run_id": "aa7fd23a-28e9-4a31-b699-5fc876ca60d8", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>profile</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>make model</t>
+          <t>make profile</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:09:56+00:00</t>
+          <t>2026-10-25T20:52:04+00:00</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
+          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>dq</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make dq (dataset=stg)</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:10:01+00:00</t>
+          <t>2026-10-25T20:52:29+00:00</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
+          <t>{"run_id": "92e26d58-e139-4e07-a394-36542d070828", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 23.73, "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>model</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>make reference</t>
+          <t>make model</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:10:03+00:00</t>
+          <t>2026-10-25T20:52:45+00:00</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>{"questions": 10, "failures": []}</t>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>make semantic</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:10:04+00:00</t>
+          <t>2026-10-25T20:52:49+00:00</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>{"entities": 11, "columns": 106, "context_pack_chars": 29500, "problems": []}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make reference</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:10:09+00:00</t>
+          <t>2026-10-25T20:52:51+00:00</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
+          <t>{"questions": 10, "failures": []}</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>semantic</t>
         </is>
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>make demo</t>
+          <t>make semantic</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:13:30+00:00</t>
+          <t>2026-10-25T20:52:54+00:00</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>{"principals": 8, "attempts": 13, "leaks": 0}</t>
+          <t>{"entities": 11, "columns": 106, "context_pack_chars": 29500, "problems": []}</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>ingest</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>make ingest</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:13:40+00:00</t>
+          <t>2026-10-25T20:52:58+00:00</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "126fe0e9-fd23-4ca4-96ab-2c2c6d16d0af", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>make profile</t>
+          <t>make demo</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:14:52+00:00</t>
+          <t>2026-10-25T20:54:00+00:00</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
+          <t>{"principals": 8, "attempts": 13, "leaks": 0}</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>dq</t>
+          <t>questions</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>make dq (dataset=stg)</t>
+          <t>make questions (provider=none, model=claude-sonnet-5-5)</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:15:12+00:00</t>
+          <t>2026-10-25T21:00:32+00:00</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "bd005a32-4474-4779-b235-1cd6a8d91e0b", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 19.75, "defect_types": 14}</t>
+          <t>{"answered": 0, "total": 10, "answered_first_attempt": 0, "run_as": "cro_global"}</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>evaluate</t>
         </is>
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>make model</t>
+          <t>make evaluate</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:15:25+00:00</t>
+          <t>2026-10-25T21:00:47+00:00</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
+          <t>{"tally": {"match": 10}}</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make zip</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:15:30+00:00</t>
+          <t>2026-10-25T21:03:34+00:00</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
+          <t>{"files": 157, "size_kb": 4049.3}</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>ingest</t>
         </is>
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>make reference</t>
+          <t>make ingest</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:15:32+00:00</t>
+          <t>2026-10-25T21:12:55+00:00</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>{"questions": 10, "failures": []}</t>
+          <t>{"run_id": "9a0380cf-ad55-474f-8fb3-3889e3a75adb", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="6" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>profile</t>
         </is>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>make semantic</t>
+          <t>make profile</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:15:34+00:00</t>
+          <t>2026-10-25T21:14:14+00:00</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>{"entities": 11, "columns": 106, "context_pack_chars": 29500, "problems": []}</t>
+          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>dq</t>
         </is>
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make dq (dataset=stg)</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:15:38+00:00</t>
+          <t>2026-10-25T21:14:40+00:00</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
+          <t>{"run_id": "08db5c80-bb78-4ac9-9ba0-336249b231e1", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 25.5, "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="6" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>model</t>
         </is>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>make demo</t>
+          <t>make model</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:17:00+00:00</t>
+          <t>2026-10-25T21:14:56+00:00</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>{"principals": 8, "attempts": 13, "leaks": 0}</t>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>questions</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>make questions (provider=claude_cli, model=claude-sonnet-5-5)</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:21:30+00:00</t>
+          <t>2026-10-25T21:15:00+00:00</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>{"answered": 10, "total": 10, "answered_first_attempt": 10, "run_as": "cro_global"}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
         <is>
-          <t>evaluate</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>make evaluate</t>
+          <t>make reference</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:21:30+00:00</t>
+          <t>2026-10-25T21:15:02+00:00</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>{"tally": {"match": 10}}</t>
+          <t>{"questions": 10, "failures": []}</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>workbook</t>
+          <t>semantic</t>
         </is>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>make workbook</t>
+          <t>make semantic</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:24:05+00:00</t>
+          <t>2026-10-25T21:15:05+00:00</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Cleaning", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
+          <t>{"entities": 11, "columns": 106, "context_pack_chars": 29500, "problems": []}</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
         <is>
-          <t>ddr</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>make ddr</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:24:11+00:00</t>
+          <t>2026-10-25T21:15:10+00:00</t>
         </is>
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>{"words": 1900, "pages": 2}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>make zip</t>
+          <t>make demo</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:24:14+00:00</t>
+          <t>2026-10-25T21:16:30+00:00</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>{"files": 148, "size_kb": 3139.3}</t>
+          <t>{"principals": 8, "attempts": 13, "leaks": 0}</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="6" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>make zip</t>
+          <t>make demo</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:31:24+00:00</t>
+          <t>2026-10-25T21:21:30+00:00</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>{"files": 154, "size_kb": 4029.9}</t>
+          <t>{"principals": 8, "attempts": 13, "leaks": 0}</t>
         </is>
       </c>
     </row>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>balance_after = -13466.40</t>
+          <t>balance_after = -1142.60</t>
         </is>
       </c>
     </row>

--- a/deliverables/Berka_TakeHome_Submission.xlsx
+++ b/deliverables/Berka_TakeHome_Submission.xlsx
@@ -532,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -561,7 +561,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T21:26:04+00:00</t>
+          <t>2026-10-28T11:54:33+00:00</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>a9c9f38</t>
+          <t>a308fc1</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>440</v>
+        <v>388</v>
       </c>
     </row>
     <row r="17">
@@ -761,7 +761,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>10 of 10</t>
+          <t>10 of 10, each verified against the intent the model declared (D029)</t>
         </is>
       </c>
     </row>
@@ -777,81 +777,93 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>TASK 3 -- entitlements</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr"/>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Additional questions (gender, quarters)</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>4 of 4 answered, 4 matching the hand-written reference (Questions tab, below the ten)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Where the filter sits</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Row level security policies on the core tables; the ai views are security_invoker</t>
-        </is>
-      </c>
+          <t>TASK 3 -- entitlements</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Identity</t>
+          <t>Where the filter sits</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>session_user (the authenticated database role), not a session variable</t>
+          <t>Row level security policies on the core tables; the ai views are security_invoker</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Bypass attempts tested</t>
+          <t>Identity</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>9, all refused (tests/test_rls.py)</t>
+          <t>session_user (the authenticated database role), not a session variable</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
+          <t>Bypass attempts tested</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>9, all refused (tests/test_rls.py)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
           <t>Onboarding</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>4 inserts and one credential; no policy, view or query change</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Tests</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>204 passing</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>321 passing</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
           <t>Full pipeline</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>make up &amp;&amp; make all -- 4m28s end to end from an empty database</t>
         </is>
@@ -922,78 +934,78 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>2026-10-24T21:12:20+00:00</t>
+          <t>2026-10-25T07:54:52+00:00</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>{"files": 135, "size_kb": 3016.3}</t>
+          <t>{"files": 138, "size_kb": 3064.9}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>make profile</t>
+          <t>make zip</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:34:31+00:00</t>
+          <t>2026-10-25T07:55:16+00:00</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
+          <t>{"files": 138, "size_kb": 3065.3}</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>dq</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>make dq (dataset=stg)</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:34:55+00:00</t>
+          <t>2026-10-25T08:48:18+00:00</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "6b713b33-3916-4b91-93dd-8c6d67f491b9", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 23.38, "defect_types": 14}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": null}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": null}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subject_client_id": n</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>make model</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:35:19+00:00</t>
+          <t>2026-10-25T08:48:47+00:00</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subjec</t>
         </is>
       </c>
     </row>
@@ -1010,232 +1022,232 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:35:21+00:00</t>
+          <t>2026-10-25T08:49:59+00:00</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subjec</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>make model</t>
+          <t>make demo</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:35:38+00:00</t>
+          <t>2026-10-25T08:53:18+00:00</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
+          <t>{"principals": 6, "attempts": 13, "leaks": 0}</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make demo</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:35:39+00:00</t>
+          <t>2026-10-25T08:53:37+00:00</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
+          <t>{"principals": 6, "attempts": 13, "leaks": 0}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>workbook</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>make workbook</t>
+          <t>make demo</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:45:15+00:00</t>
+          <t>2026-10-25T08:54:03+00:00</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Cleaning", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
+          <t>{"principals": 6, "attempts": 13, "leaks": 0}</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>ddr</t>
+          <t>ingest</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>make ddr</t>
+          <t>make ingest</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:46:05+00:00</t>
+          <t>2026-10-25T08:57:30+00:00</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>{"words": 1780, "pages": 2}</t>
+          <t>{"run_id": "9333367e-c3a2-4e61-91ff-605c39dc7d82", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>ingest</t>
+          <t>profile</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>make ingest</t>
+          <t>make profile</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:50:02+00:00</t>
+          <t>2026-10-25T08:58:46+00:00</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "077de4c5-5ccb-4a88-bb1d-76a8b7714643", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
+          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>dq</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>make profile</t>
+          <t>make dq (dataset=stg)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:51:06+00:00</t>
+          <t>2026-10-25T08:59:10+00:00</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
+          <t>{"run_id": "1e4ca221-e5cc-4fd2-8ca5-92a40b0e0728", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 22.96, "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>dq</t>
+          <t>model</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>make dq (dataset=stg)</t>
+          <t>make model</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:51:23+00:00</t>
+          <t>2026-10-25T08:59:22+00:00</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "116e896d-afb0-4ddf-8119-c059382d5394", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 16.44, "defect_types": 14}</t>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>make model</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:51:34+00:00</t>
+          <t>2026-10-25T08:59:25+00:00</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subjec</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make reference</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:51:35+00:00</t>
+          <t>2026-10-25T08:59:26+00:00</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
+          <t>{"questions": 10, "failures": []}</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>semantic</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>make reference</t>
+          <t>make semantic</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:51:36+00:00</t>
+          <t>2026-10-25T08:59:29+00:00</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>{"questions": 10, "failures": []}</t>
+          <t>{"entities": 11, "columns": 100, "context_pack_chars": 27592, "problems": ["ai.my_entitlement.principal_type: present in the view but not described (an undocumented column is one the model will guess at)"]}</t>
         </is>
       </c>
     </row>
@@ -1252,518 +1264,518 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:51:38+00:00</t>
+          <t>2026-10-25T08:59:52+00:00</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>{"entities": 11, "columns": 100, "context_pack_chars": 27592, "problems": []}</t>
+          <t>{"entities": 11, "columns": 101, "context_pack_chars": 28453, "problems": []}</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>ingest</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make ingest</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:51:39+00:00</t>
+          <t>2026-10-25T09:00:01+00:00</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "cro_global", "display_name": "Group risk, bank-wide reporting", "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "clients": 1386, "accounts": 1157, "loans": 194, "transactions": 272331, "districts": 77, "portfolios": "SOUTH_BOOK"}, {"db_role": "rm_unassigned", "display_name": "Newly created user with no portfolio yet", "clients": 0, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": null}]}</t>
+          <t>{"run_id": "6f2cd8a4-fb2b-469b-9e44-707c900bd0f0", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>questions</t>
+          <t>profile</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>make questions (provider=claude_cli, model=claude-sonnet-5-5)</t>
+          <t>make profile</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:52:57+00:00</t>
+          <t>2026-10-25T09:01:08+00:00</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>{"answered": 10, "total": 10, "answered_first_attempt": 10, "run_as": "cro_global"}</t>
+          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>evaluate</t>
+          <t>dq</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>make evaluate</t>
+          <t>make dq (dataset=stg)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:52:58+00:00</t>
+          <t>2026-10-25T09:01:28+00:00</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>{"tally": {"match": 10}}</t>
+          <t>{"run_id": "7fa1b4a2-c790-4d4a-8d0d-cd91f82b3331", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 19.21, "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>workbook</t>
+          <t>model</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>make workbook</t>
+          <t>make model</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:53:56+00:00</t>
+          <t>2026-10-25T09:01:39+00:00</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Cleaning", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>ddr</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>make ddr</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:53:58+00:00</t>
+          <t>2026-10-25T09:01:42+00:00</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>{"words": 1780, "pages": 2}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subjec</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>make zip</t>
+          <t>make reference</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:53:59+00:00</t>
+          <t>2026-10-25T09:01:44+00:00</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>{"files": 139, "size_kb": 3068.8}</t>
+          <t>{"questions": 10, "failures": []}</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>semantic</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>make zip</t>
+          <t>make semantic</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:54:28+00:00</t>
+          <t>2026-10-25T09:01:45+00:00</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>{"files": 138, "size_kb": 3064.9}</t>
+          <t>{"entities": 11, "columns": 101, "context_pack_chars": 28453, "problems": []}</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>make zip</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:54:52+00:00</t>
+          <t>2026-10-25T09:01:47+00:00</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>{"files": 138, "size_kb": 3064.9}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subjec</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>make zip</t>
+          <t>make demo</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T07:55:16+00:00</t>
+          <t>2026-10-25T09:01:48+00:00</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>{"files": 138, "size_kb": 3065.3}</t>
+          <t>{"principals": 6, "attempts": 13, "leaks": 0}</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>questions</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make questions (provider=claude_cli, model=claude-sonnet-5-5)</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:48:18+00:00</t>
+          <t>2026-10-25T09:03:10+00:00</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": null}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": null}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subject_client_id": n</t>
+          <t>{"answered": 10, "total": 10, "answered_first_attempt": 10, "run_as": "cro_global"}</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>evaluate</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make evaluate</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:48:47+00:00</t>
+          <t>2026-10-25T09:03:10+00:00</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subjec</t>
+          <t>{"tally": {"match": 10}}</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>workbook</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make workbook</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:49:59+00:00</t>
+          <t>2026-10-25T09:04:08+00:00</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subjec</t>
+          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Cleaning", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>ddr</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>make demo</t>
+          <t>make ddr</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:53:18+00:00</t>
+          <t>2026-10-25T09:04:10+00:00</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>{"principals": 6, "attempts": 13, "leaks": 0}</t>
+          <t>{"words": 1780, "pages": 2}</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>make demo</t>
+          <t>make zip</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:53:37+00:00</t>
+          <t>2026-10-25T09:04:11+00:00</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>{"principals": 6, "attempts": 13, "leaks": 0}</t>
+          <t>{"files": 140, "size_kb": 3098.2}</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>ddr</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>make demo</t>
+          <t>make ddr</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:54:03+00:00</t>
+          <t>2026-10-25T09:04:28+00:00</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>{"principals": 6, "attempts": 13, "leaks": 0}</t>
+          <t>{"words": 1900, "pages": 2}</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>ingest</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>make ingest</t>
+          <t>make zip</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:57:30+00:00</t>
+          <t>2026-10-25T09:05:52+00:00</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "9333367e-c3a2-4e61-91ff-605c39dc7d82", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
+          <t>{"files": 141, "size_kb": 3103.3}</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>model</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>make profile</t>
+          <t>make model</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:58:46+00:00</t>
+          <t>2026-10-25T09:42:15+00:00</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>dq</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>make dq (dataset=stg)</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:59:10+00:00</t>
+          <t>2026-10-25T09:42:17+00:00</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "1e4ca221-e5cc-4fd2-8ca5-92a40b0e0728", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 22.96, "defect_types": 14}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "subject_client_id": 3764, "clients": 1, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": "SELF:3764"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clie</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>make model</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:59:22+00:00</t>
+          <t>2026-10-25T09:47:55+00:00</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>model</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make model</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:59:25+00:00</t>
+          <t>2026-10-25T09:48:55+00:00</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subjec</t>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>make reference</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:59:26+00:00</t>
+          <t>2026-10-25T09:48:59+00:00</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>{"questions": 10, "failures": []}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>make semantic</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:59:29+00:00</t>
+          <t>2026-10-25T11:00:47+00:00</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>{"entities": 11, "columns": 100, "context_pack_chars": 27592, "problems": ["ai.my_entitlement.principal_type: present in the view but not described (an undocumented column is one the model will guess at)"]}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>make semantic</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T08:59:52+00:00</t>
+          <t>2026-10-25T11:03:42+00:00</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>{"entities": 11, "columns": 101, "context_pack_chars": 28453, "problems": []}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
         </is>
       </c>
     </row>
@@ -1780,12 +1792,12 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:00:01+00:00</t>
+          <t>2026-10-25T11:05:45+00:00</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "6f2cd8a4-fb2b-469b-9e44-707c900bd0f0", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
+          <t>{"run_id": "768f6d57-1008-4ba7-a1a1-7995e12504a9", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1814,7 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:08+00:00</t>
+          <t>2026-10-25T11:06:54+00:00</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
@@ -1824,12 +1836,12 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:28+00:00</t>
+          <t>2026-10-25T11:07:14+00:00</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "7fa1b4a2-c790-4d4a-8d0d-cd91f82b3331", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 19.21, "defect_types": 14}</t>
+          <t>{"run_id": "8bc261dd-5837-4eaf-8864-bf398749cfcb", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 18.74, "defect_types": 14}</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1858,7 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:39+00:00</t>
+          <t>2026-10-25T11:07:27+00:00</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -1868,12 +1880,12 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:42+00:00</t>
+          <t>2026-10-25T11:07:31+00:00</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subjec</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1902,7 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:44+00:00</t>
+          <t>2026-10-25T11:07:33+00:00</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
@@ -1912,320 +1924,320 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:45+00:00</t>
+          <t>2026-10-25T11:07:34+00:00</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>{"entities": 11, "columns": 101, "context_pack_chars": 28453, "problems": []}</t>
+          <t>{"entities": 11, "columns": 101, "context_pack_chars": 28453, "problems": ["ai.client.client_ref: present in the view but not described (an undocumented column is one the model will guess at)", "ai.account.account_ref: present in the view but not described (an undocumented column is one the model will guess at)", "ai.account_owner.account_ref: present in the view but not described (an undocumented column is one the model will guess at)", "ai.account_owner.owner_client_ref: present in the view but not described (an undocumented column is one the model will guess at)"]}</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>semantic</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make semantic</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:47+00:00</t>
+          <t>2026-10-25T11:07:58+00:00</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clients": 1481, "accounts": 1241, "loans": 179, "transactions": 294622, "districts": 77, "portfolios": "NORTH_BOOK"}, {"db_role": "rm_south", "display_name": "Relationship manager, southern book", "user_type": "relationship_manager", "subjec</t>
+          <t>{"entities": 11, "columns": 106, "context_pack_chars": 29500, "problems": []}</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>ingest</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>make demo</t>
+          <t>make ingest</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:48+00:00</t>
+          <t>2026-10-25T11:08:07+00:00</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>{"principals": 6, "attempts": 13, "leaks": 0}</t>
+          <t>{"run_id": "64293db3-d4d0-429e-a99d-74d6a0aa3959", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>questions</t>
+          <t>profile</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>make questions (provider=claude_cli, model=claude-sonnet-5-5)</t>
+          <t>make profile</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:03:10+00:00</t>
+          <t>2026-10-25T11:09:15+00:00</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>{"answered": 10, "total": 10, "answered_first_attempt": 10, "run_as": "cro_global"}</t>
+          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>evaluate</t>
+          <t>dq</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>make evaluate</t>
+          <t>make dq (dataset=stg)</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:03:10+00:00</t>
+          <t>2026-10-25T11:09:40+00:00</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>{"tally": {"match": 10}}</t>
+          <t>{"run_id": "313199cc-62d3-4583-ae3d-70a1b1bc1750", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 24.2, "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>workbook</t>
+          <t>model</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>make workbook</t>
+          <t>make model</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:04:08+00:00</t>
+          <t>2026-10-25T11:09:56+00:00</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Cleaning", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>ddr</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>make ddr</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:04:10+00:00</t>
+          <t>2026-10-25T11:10:01+00:00</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>{"words": 1780, "pages": 2}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>make zip</t>
+          <t>make reference</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:04:11+00:00</t>
+          <t>2026-10-25T11:10:03+00:00</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>{"files": 140, "size_kb": 3098.2}</t>
+          <t>{"questions": 10, "failures": []}</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>ddr</t>
+          <t>semantic</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>make ddr</t>
+          <t>make semantic</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:04:28+00:00</t>
+          <t>2026-10-25T11:10:04+00:00</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>{"words": 1900, "pages": 2}</t>
+          <t>{"entities": 11, "columns": 106, "context_pack_chars": 29500, "problems": []}</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>make zip</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:05:52+00:00</t>
+          <t>2026-10-25T11:10:09+00:00</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>{"files": 141, "size_kb": 3103.3}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>make model</t>
+          <t>make demo</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:42:15+00:00</t>
+          <t>2026-10-25T11:13:30+00:00</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
+          <t>{"principals": 8, "attempts": 13, "leaks": 0}</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>ingest</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make ingest</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:42:17+00:00</t>
+          <t>2026-10-25T11:13:40+00:00</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "subject_client_id": 3764, "clients": 1, "accounts": 0, "loans": 0, "transactions": 0, "districts": 77, "portfolios": "SELF:3764"}, {"db_role": "rm_north", "display_name": "Relationship manager, northern book", "user_type": "relationship_manager", "subject_client_id": null, "clie</t>
+          <t>{"run_id": "126fe0e9-fd23-4ca4-96ab-2c2c6d16d0af", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>profile</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make profile</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:47:55+00:00</t>
+          <t>2026-10-25T11:14:52+00:00</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
+          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>dq</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>make model</t>
+          <t>make dq (dataset=stg)</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:48:55+00:00</t>
+          <t>2026-10-25T11:15:12+00:00</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
+          <t>{"run_id": "bd005a32-4474-4779-b235-1cd6a8d91e0b", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 19.75, "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>model</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make model</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:48:59+00:00</t>
+          <t>2026-10-25T11:15:25+00:00</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2254,7 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:00:47+00:00</t>
+          <t>2026-10-25T11:15:30+00:00</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -2254,286 +2266,286 @@
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make reference</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:03:42+00:00</t>
+          <t>2026-10-25T11:15:32+00:00</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
+          <t>{"questions": 10, "failures": []}</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>ingest</t>
+          <t>semantic</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>make ingest</t>
+          <t>make semantic</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:05:45+00:00</t>
+          <t>2026-10-25T11:15:34+00:00</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "768f6d57-1008-4ba7-a1a1-7995e12504a9", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
+          <t>{"entities": 11, "columns": 106, "context_pack_chars": 29500, "problems": []}</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>make profile</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:06:54+00:00</t>
+          <t>2026-10-25T11:15:38+00:00</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>dq</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>make dq (dataset=stg)</t>
+          <t>make demo</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:07:14+00:00</t>
+          <t>2026-10-25T11:17:00+00:00</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "8bc261dd-5837-4eaf-8864-bf398749cfcb", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 18.74, "defect_types": 14}</t>
+          <t>{"principals": 8, "attempts": 13, "leaks": 0}</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>questions</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>make model</t>
+          <t>make questions (provider=claude_cli, model=claude-sonnet-5-5)</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:07:27+00:00</t>
+          <t>2026-10-25T11:21:30+00:00</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
+          <t>{"answered": 10, "total": 10, "answered_first_attempt": 10, "run_as": "cro_global"}</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>evaluate</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make evaluate</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:07:31+00:00</t>
+          <t>2026-10-25T11:21:30+00:00</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
+          <t>{"tally": {"match": 10}}</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>workbook</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>make reference</t>
+          <t>make workbook</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:07:33+00:00</t>
+          <t>2026-10-25T11:24:05+00:00</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>{"questions": 10, "failures": []}</t>
+          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Cleaning", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>ddr</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>make semantic</t>
+          <t>make ddr</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:07:34+00:00</t>
+          <t>2026-10-25T11:24:11+00:00</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>{"entities": 11, "columns": 101, "context_pack_chars": 28453, "problems": ["ai.client.client_ref: present in the view but not described (an undocumented column is one the model will guess at)", "ai.account.account_ref: present in the view but not described (an undocumented column is one the model will guess at)", "ai.account_owner.account_ref: present in the view but not described (an undocumented column is one the model will guess at)", "ai.account_owner.owner_client_ref: present in the view but not described (an undocumented column is one the model will guess at)"]}</t>
+          <t>{"words": 1900, "pages": 2}</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>make semantic</t>
+          <t>make zip</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:07:58+00:00</t>
+          <t>2026-10-25T11:24:14+00:00</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>{"entities": 11, "columns": 106, "context_pack_chars": 29500, "problems": []}</t>
+          <t>{"files": 148, "size_kb": 3139.3}</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>ingest</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>make ingest</t>
+          <t>make zip</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:08:07+00:00</t>
+          <t>2026-10-25T11:31:24+00:00</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "64293db3-d4d0-429e-a99d-74d6a0aa3959", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
+          <t>{"files": 154, "size_kb": 4029.9}</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>workbook</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>make profile</t>
+          <t>make workbook</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:09:15+00:00</t>
+          <t>2026-10-25T11:34:44+00:00</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
+          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Cleaning", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>dq</t>
+          <t>ddr</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>make dq (dataset=stg)</t>
+          <t>make ddr</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:09:40+00:00</t>
+          <t>2026-10-25T11:34:46+00:00</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "313199cc-62d3-4583-ae3d-70a1b1bc1750", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 24.2, "defect_types": 14}</t>
+          <t>{"words": 1900, "pages": 2}</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>make model</t>
+          <t>make zip</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:09:56+00:00</t>
+          <t>2026-10-25T11:34:47+00:00</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
+          <t>{"files": 155, "size_kb": 4038.5}</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2562,7 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:10:01+00:00</t>
+          <t>2026-10-25T20:49:19+00:00</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
@@ -2562,990 +2574,990 @@
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>ingest</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>make reference</t>
+          <t>make ingest</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:10:03+00:00</t>
+          <t>2026-10-25T20:50:32+00:00</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>{"questions": 10, "failures": []}</t>
+          <t>{"run_id": "aa7fd23a-28e9-4a31-b699-5fc876ca60d8", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>profile</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>make semantic</t>
+          <t>make profile</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:10:04+00:00</t>
+          <t>2026-10-25T20:52:04+00:00</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>{"entities": 11, "columns": 106, "context_pack_chars": 29500, "problems": []}</t>
+          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>dq</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make dq (dataset=stg)</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:10:09+00:00</t>
+          <t>2026-10-25T20:52:29+00:00</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
+          <t>{"run_id": "92e26d58-e139-4e07-a394-36542d070828", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 23.73, "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>model</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>make demo</t>
+          <t>make model</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:13:30+00:00</t>
+          <t>2026-10-25T20:52:45+00:00</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>{"principals": 8, "attempts": 13, "leaks": 0}</t>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>ingest</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>make ingest</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:13:40+00:00</t>
+          <t>2026-10-25T20:52:49+00:00</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "126fe0e9-fd23-4ca4-96ab-2c2c6d16d0af", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>make profile</t>
+          <t>make reference</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:14:52+00:00</t>
+          <t>2026-10-25T20:52:51+00:00</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
+          <t>{"questions": 10, "failures": []}</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>dq</t>
+          <t>semantic</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>make dq (dataset=stg)</t>
+          <t>make semantic</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:15:12+00:00</t>
+          <t>2026-10-25T20:52:54+00:00</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "bd005a32-4474-4779-b235-1cd6a8d91e0b", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 19.75, "defect_types": 14}</t>
+          <t>{"entities": 11, "columns": 106, "context_pack_chars": 29500, "problems": []}</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>make model</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:15:25+00:00</t>
+          <t>2026-10-25T20:52:58+00:00</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make demo</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:15:30+00:00</t>
+          <t>2026-10-25T20:54:00+00:00</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
+          <t>{"principals": 8, "attempts": 13, "leaks": 0}</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>questions</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>make reference</t>
+          <t>make questions (provider=none, model=claude-sonnet-5-5)</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:15:32+00:00</t>
+          <t>2026-10-25T21:00:32+00:00</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>{"questions": 10, "failures": []}</t>
+          <t>{"answered": 0, "total": 10, "answered_first_attempt": 0, "run_as": "cro_global"}</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>evaluate</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>make semantic</t>
+          <t>make evaluate</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:15:34+00:00</t>
+          <t>2026-10-25T21:00:47+00:00</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>{"entities": 11, "columns": 106, "context_pack_chars": 29500, "problems": []}</t>
+          <t>{"tally": {"match": 10}}</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make zip</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:15:38+00:00</t>
+          <t>2026-10-25T21:03:34+00:00</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
+          <t>{"files": 157, "size_kb": 4049.3}</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>ingest</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>make demo</t>
+          <t>make ingest</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:17:00+00:00</t>
+          <t>2026-10-25T21:12:55+00:00</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>{"principals": 8, "attempts": 13, "leaks": 0}</t>
+          <t>{"run_id": "9a0380cf-ad55-474f-8fb3-3889e3a75adb", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>questions</t>
+          <t>profile</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>make questions (provider=claude_cli, model=claude-sonnet-5-5)</t>
+          <t>make profile</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:21:30+00:00</t>
+          <t>2026-10-25T21:14:14+00:00</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>{"answered": 10, "total": 10, "answered_first_attempt": 10, "run_as": "cro_global"}</t>
+          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>evaluate</t>
+          <t>dq</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>make evaluate</t>
+          <t>make dq (dataset=stg)</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:21:30+00:00</t>
+          <t>2026-10-25T21:14:40+00:00</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>{"tally": {"match": 10}}</t>
+          <t>{"run_id": "08db5c80-bb78-4ac9-9ba0-336249b231e1", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 25.5, "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>workbook</t>
+          <t>model</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>make workbook</t>
+          <t>make model</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:24:05+00:00</t>
+          <t>2026-10-25T21:14:56+00:00</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Cleaning", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>ddr</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>make ddr</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:24:11+00:00</t>
+          <t>2026-10-25T21:15:00+00:00</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>{"words": 1900, "pages": 2}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>make zip</t>
+          <t>make reference</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:24:14+00:00</t>
+          <t>2026-10-25T21:15:02+00:00</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>{"files": 148, "size_kb": 3139.3}</t>
+          <t>{"questions": 10, "failures": []}</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>semantic</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>make zip</t>
+          <t>make semantic</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:31:24+00:00</t>
+          <t>2026-10-25T21:15:05+00:00</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>{"files": 154, "size_kb": 4029.9}</t>
+          <t>{"entities": 11, "columns": 106, "context_pack_chars": 29500, "problems": []}</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>workbook</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>make workbook</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:34:44+00:00</t>
+          <t>2026-10-25T21:15:10+00:00</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Cleaning", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>ddr</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>make ddr</t>
+          <t>make demo</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:34:46+00:00</t>
+          <t>2026-10-25T21:16:30+00:00</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>{"words": 1900, "pages": 2}</t>
+          <t>{"principals": 8, "attempts": 13, "leaks": 0}</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>make zip</t>
+          <t>make demo</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T11:34:47+00:00</t>
+          <t>2026-10-25T21:21:30+00:00</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>{"files": 155, "size_kb": 4038.5}</t>
+          <t>{"principals": 8, "attempts": 13, "leaks": 0}</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>workbook</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make workbook</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T20:49:19+00:00</t>
+          <t>2026-10-25T21:26:06+00:00</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
+          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Cleaning", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>ingest</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>make ingest</t>
+          <t>make zip</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T20:50:32+00:00</t>
+          <t>2026-10-25T21:26:06+00:00</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "aa7fd23a-28e9-4a31-b699-5fc876ca60d8", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
+          <t>{"files": 157, "size_kb": 4050.9}</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>make profile</t>
+          <t>make zip</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T20:52:04+00:00</t>
+          <t>2026-10-26T00:16:21+00:00</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
+          <t>{"files": 163, "size_kb": 4083.2}</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>dq</t>
+          <t>semantic</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>make dq (dataset=stg)</t>
+          <t>make semantic</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T20:52:29+00:00</t>
+          <t>2026-10-28T09:06:20+00:00</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "92e26d58-e139-4e07-a394-36542d070828", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 23.73, "defect_types": 14}</t>
+          <t>{"entities": 11, "columns": 105, "context_pack_chars": 33391, "problems": []}</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>semantic</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>make model</t>
+          <t>make semantic</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T20:52:45+00:00</t>
+          <t>2026-10-28T09:06:31+00:00</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
+          <t>{"entities": 11, "columns": 105, "context_pack_chars": 33388, "problems": []}</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>dq</t>
         </is>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make dq (dataset=stg)</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T20:52:49+00:00</t>
+          <t>2026-10-28T10:28:59+00:00</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
+          <t>{"run_id": "b3a8fff4-a4c4-4a66-adbd-f7056262f8b6", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 388, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 268, "district": 0, "order": 0, "all": 0}, "duration_sec": 26.28, "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>model</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>make reference</t>
+          <t>make model</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T20:52:51+00:00</t>
+          <t>2026-10-28T10:29:19+00:00</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>{"questions": 10, "failures": []}</t>
+          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>entitlements</t>
         </is>
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>make semantic</t>
+          <t>make entitlements</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T20:52:54+00:00</t>
+          <t>2026-10-28T10:29:25+00:00</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>{"entities": 11, "columns": 106, "context_pack_chars": 29500, "problems": []}</t>
+          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>dq</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make dq (dataset=stg)</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T20:52:58+00:00</t>
+          <t>2026-10-28T10:31:41+00:00</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
+          <t>{"run_id": "dbcf6848-4d1f-461e-b339-fc26fe0d71be", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 388, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 268, "district": 0, "order": 0, "all": 0}, "duration_sec": 23.55, "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>make demo</t>
+          <t>make reference</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T20:54:00+00:00</t>
+          <t>2026-10-28T10:31:42+00:00</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>{"principals": 8, "attempts": 13, "leaks": 0}</t>
+          <t>{"questions": 10, "failures": []}</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>questions</t>
+          <t>semantic</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>make questions (provider=none, model=claude-sonnet-5-5)</t>
+          <t>make semantic</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T21:00:32+00:00</t>
+          <t>2026-10-28T10:51:34+00:00</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>{"answered": 0, "total": 10, "answered_first_attempt": 0, "run_as": "cro_global"}</t>
+          <t>{"entities": 11, "columns": 106, "context_pack_chars": 36331, "problems": []}</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>evaluate</t>
+          <t>semantic</t>
         </is>
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>make evaluate</t>
+          <t>make semantic</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T21:00:47+00:00</t>
+          <t>2026-10-28T10:54:40+00:00</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>{"tally": {"match": 10}}</t>
+          <t>{"entities": 11, "columns": 106, "context_pack_chars": 36877, "problems": []}</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>make zip</t>
+          <t>make reference (suite=extra)</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T21:03:34+00:00</t>
+          <t>2026-10-28T11:02:48+00:00</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>{"files": 157, "size_kb": 4049.3}</t>
+          <t>{"suite": "extra", "questions": 4, "failures": []}</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>ingest</t>
+          <t>questions</t>
         </is>
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>make ingest</t>
+          <t>make questions (suite=extra, provider=claude_cli, model=claude-sonnet-5-5)</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T21:12:55+00:00</t>
+          <t>2026-10-28T11:13:00+00:00</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "9a0380cf-ad55-474f-8fb3-3889e3a75adb", "row_counts": {"account": 4500, "client": 5369, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320, "district": 77}, "mismatches": []}</t>
+          <t>{"suite": "extra", "out": "/home/user/Loan-valid-DQ/dq/results/llm_results_extra.json", "answered": 1, "total": 1, "answered_first_attempt": 1, "run_as": "cro_global"}</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="6" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>questions</t>
         </is>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>make profile</t>
+          <t>make questions (suite=extra, provider=claude_cli, model=claude-sonnet-5-5)</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T21:14:14+00:00</t>
+          <t>2026-10-28T11:15:00+00:00</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>{"tables": {"district": 77, "client": 5369, "account": 4500, "disp": 5369, "card": 892, "loan": 682, "order": 6471, "trans": 1056320}, "candidates_present": 13, "candidates_total": 17}</t>
+          <t>{"suite": "extra", "out": "/home/user/Loan-valid-DQ/dq/results/llm_results_extra.json", "answered": 4, "total": 4, "answered_first_attempt": 4, "run_as": "cro_global"}</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>dq</t>
+          <t>questions</t>
         </is>
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>make dq (dataset=stg)</t>
+          <t>make questions (suite=core, provider=claude_cli, model=claude-sonnet-5-5)</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T21:14:40+00:00</t>
+          <t>2026-10-28T11:20:02+00:00</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>{"run_id": "08db5c80-bb78-4ac9-9ba0-336249b231e1", "dataset": "stg", "rules_executed": 124, "rules_fired": 19, "rules_errored": 0, "by_severity": {"block": 1, "warn": 6, "info": 12}, "rows_quarantined": 1, "quarantined_by_table": {"trans": 1}, "rows_flagged": 440, "flagged_by_table": {"account": 0, "client": 114, "disp": 0, "card": 0, "loan": 6, "trans": 320, "district": 0, "order": 0, "all": 0}, "duration_sec": 25.5, "defect_types": 14}</t>
+          <t>{"suite": "core", "out": "/home/user/Loan-valid-DQ/dq/results/llm_results.json", "answered": 9, "total": 10, "answered_first_attempt": 8, "run_as": "cro_global"}</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="6" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>questions</t>
         </is>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>make model</t>
+          <t>make questions (suite=core, provider=claude_cli, model=claude-sonnet-5-5)</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T21:14:56+00:00</t>
+          <t>2026-10-28T11:40:00+00:00</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>{"row_counts": {"dim_date": 2191, "dim_district": 77, "dim_client": 5369, "dim_account": 4500, "bridge_disposition": 5369, "dim_card": 892, "fact_loan": 682, "fact_transaction": 1056319, "fact_account_month_end_balance": 185615}, "ref_codes": 28, "problems": [], "reconciliation_checks": 9}</t>
+          <t>{"suite": "core", "out": "/home/user/Loan-valid-DQ/dq/results/llm_results.json", "answered": 10, "total": 10, "answered_first_attempt": 10, "run_as": "cro_global"}</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>questions</t>
         </is>
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make questions (suite=extra, provider=claude_cli, model=claude-sonnet-5-5)</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T21:15:00+00:00</t>
+          <t>2026-10-28T11:42:00+00:00</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
+          <t>{"suite": "extra", "out": "/home/user/Loan-valid-DQ/dq/results/llm_results_extra.json", "answered": 4, "total": 4, "answered_first_attempt": 4, "run_as": "cro_global"}</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>evaluate</t>
         </is>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>make reference</t>
+          <t>make evaluate (suite=core)</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T21:15:02+00:00</t>
+          <t>2026-10-28T11:42:01+00:00</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>{"questions": 10, "failures": []}</t>
+          <t>{"suite": "core", "llm_results_file": "/home/user/Loan-valid-DQ/dq/results/llm_results.json", "tally": {"match": 10}}</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>evaluate</t>
         </is>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>make semantic</t>
+          <t>make evaluate (suite=extra)</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T21:15:05+00:00</t>
+          <t>2026-10-28T11:42:01+00:00</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>{"entities": 11, "columns": 106, "context_pack_chars": 29500, "problems": []}</t>
+          <t>{"suite": "extra", "llm_results_file": "/home/user/Loan-valid-DQ/dq/results/llm_results_extra.json", "tally": {"match": 4}}</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
         <is>
-          <t>entitlements</t>
+          <t>ddr</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>make entitlements</t>
+          <t>make ddr</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T21:15:10+00:00</t>
+          <t>2026-10-28T11:49:14+00:00</t>
         </is>
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>{"policies": 7, "visible_rows": [{"db_role": "admin_demo", "display_name": "Demo administrator (data owner's view, via a portfolio)", "user_type": "administrator", "subject_client_id": null, "clients": 5369, "accounts": 4500, "loans": 682, "transactions": 1056319, "districts": 77, "portfolios": "ALL_CLIENTS"}, {"db_role": "client_11409", "display_name": "Self-service customer (client 11409)", "user_type": "client", "subject_client_id": 11409, "clients": 1, "accounts": 1, "loans": 1, "transactions": 643, "districts": 77, "portfolios": "SELF:11409"}, {"db_role": "client_3763", "display_name": "Self-service customer (client 3763)", "user_type": "client", "subject_client_id": 3763, "clients": 1, "accounts": 1, "loans": 1, "transactions": 439, "districts": 77, "portfolios": "SELF:3763"}, {"db_role": "client_3764", "display_name": "Self-service customer (client 3764)", "user_type": "client", "</t>
+          <t>{"words": 1942, "pages": 2}</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>workbook</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>make demo</t>
+          <t>make workbook</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T21:16:30+00:00</t>
+          <t>2026-10-28T11:49:40+00:00</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>{"principals": 8, "attempts": 13, "leaks": 0}</t>
+          <t>{"tabs": ["Overview", "Defect types", "Model", "Questions", "Q detail", "DQ rules", "Cleaning", "Assumptions", "Entitlements", "Run log"], "defect_types": 14}</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="6" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>make demo</t>
+          <t>make zip</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T21:21:30+00:00</t>
+          <t>2026-10-28T11:49:41+00:00</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>{"principals": 8, "attempts": 13, "leaks": 0}</t>
+          <t>{"files": 181, "size_kb": 4222.2}</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3692,7 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Closing balance of the account's last day is not uniquely determined</t>
+          <t>Account has several postings on its latest date (closing posting must be derived)</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
@@ -3705,7 +3717,7 @@
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>trans_id is not chronological within a date, so when an account has several postings on one day there is no way to tell which one closed the day. For 183 accounts that ambiguity falls on their most recent date, which is precisely the balance Q9 reports. The answer is therefore a documented choice (highest trans_id on the latest date) rather than a fact, and the count of affected accounts belongs next to the answer. Warn: the data is not wrong, the determinism is missing.</t>
+          <t>trans_id is not chronological within a date and the source has no time of day, so when an account has several postings on one day the closing one has to be derived. 183 accounts have this on their most recent date, which is the balance Q9 reports. The running balance resolves it (D028): each posting starts at balance_after - signed_amount, and the closing posting is the end of that chain. That settles 141 of the 183; for the other 42 the chain does not order the postings, the documented fallback is used and the month-end row is marked closing_basis = 'ambiguous'. Warn: the data is not wrong, the order has to be inferred.</t>
         </is>
       </c>
       <c r="G3" s="6" t="n">
@@ -3713,7 +3725,7 @@
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>Tie-break documented in the semantic layer and applied identically in the reference SQL and in core.fact_account_month_end_balance; affected accounts flagged so the caveat can be quantified.</t>
+          <t>Closing posting taken from the running-balance chain in core.fact_account_month_end_balance (closing_basis records how); accounts flagged so the caveat can be quantified.</t>
         </is>
       </c>
       <c r="I3" s="6" t="inlineStr">
@@ -3723,29 +3735,29 @@
       </c>
       <c r="J3" s="6" t="inlineStr">
         <is>
-          <t>account has 2 postings on its latest date 1998-12-31; the closing balance depends on the tie-break</t>
+          <t>account has 2 postings on its latest date 1998-12-31; the closing posting is derived from the running-balance chain</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Running balance does not reconcile</t>
+          <t>Implausible age</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>trans</t>
+          <t>client, loan</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>CON_BALANCE_RECONCILIATION_MATERIAL, CON_BALANCE_RECONCILIATION_ROUNDING</t>
+          <t>VAL_OWNER_AGE_AT_ACCOUNT_OPEN, VAL_OWNER_AGE_AT_LOAN_START</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>consistency</t>
+          <t>validity</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
@@ -3755,47 +3767,47 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Tested order independently: the sum of all signed amounts on an account should equal its last reported balance, whatever order the postings are read in. 136 accounts breach a 1 CZK tolerance; 81 of those are within 100 CZK and sit in the rounding band (every amount in the source carries a single decimal, so residuals accumulate). Warn, because the account is still usable and the Q9 average moves by cents; the band is reported so nobody confuses it with the material tier below. | 55 accounts are off by more than 100 CZK and one by exactly 1,200.00 CZK with only 55 postings, which is a missing or extra posting rather than rounding. This is the single most material finding for Q9, because the answer is an average balance and these accounts' balances cannot be derived from their own flows. It stays warn rather than block on purpose: the balance column is what Q9 reads, and it is internally plausible -- it is the *flows* that disagree with it. Quarantining the accounts would remove real balances from an average; blocking the postings would break the chain further. The defensible treatment is to publish the answer with the affected population and the residual attached, which is what the semantic layer makes the LLM do.</t>
+          <t>114 owners were under 15 when their account was opened, the youngest 10.3 years. A ten year old cannot be the legal holder of a current account, so either the birth number or the owner flag is wrong. It is warn rather than block because the accounts and their transactions are otherwise well-formed and feed Q5, Q6 and Q9 correctly: quarantining 114 accounts to protect the age metric would damage four answers to improve one. Q7 and Q8 report their coverage instead. | 6 loans were granted to owners recorded as under 15. Q7 reports exactly this number -- the average age of the owner at loan start, per status -- so these rows pull the answer directly. Warn rather than block because the loan amount and status are themselves sound and feed Q2, Q3, Q4 and Q10: removing the loans would make the certified loan total disagree with the source. Q7 publishes the flagged count next to the average, which is the honest treatment of a value that is probably wrong but not certainly so.</t>
         </is>
       </c>
       <c r="G4" s="6" t="n">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Account flagged; the month-end balance fact carries the residual so a user can see the size of the discrepancy next to the balance. | Account flagged as balance_unreconciled; Q9 reports the average together with the number of affected accounts and the total residual, so the reader can size the uncertainty instead of guessing at it.</t>
+          <t>Rows kept and flagged (_dq_flags carries 'owner_age_implausible'); the semantic layer attaches the caveat to the age metric so the LLM can repeat it. | Rows kept and flagged; Q7 reports the average with and without the flagged loans so the sensitivity is visible.</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>Q7, Q8</t>
         </is>
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>sum(signed_amount) = 13298.70 but last reported balance = 13312.90 (difference -14.20)</t>
+          <t>owner was 11.9 years old when account 9 was opened</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Implausible age</t>
+          <t>Running balance does not reconcile</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>client, loan</t>
+          <t>trans</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>VAL_OWNER_AGE_AT_ACCOUNT_OPEN, VAL_OWNER_AGE_AT_LOAN_START</t>
+          <t>CON_BALANCE_RECONCILIATION_MATERIAL, CON_BALANCE_RECONCILIATION_ROUNDING</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>validity</t>
+          <t>consistency</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -3805,25 +3817,25 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>114 owners were under 15 when their account was opened, the youngest 10.3 years. A ten year old cannot be the legal holder of a current account, so either the birth number or the owner flag is wrong. It is warn rather than block because the accounts and their transactions are otherwise well-formed and feed Q5, Q6 and Q9 correctly: quarantining 114 accounts to protect the age metric would damage four answers to improve one. Q7 and Q8 report their coverage instead. | 6 loans were granted to owners recorded as under 15. Q7 reports exactly this number -- the average age of the owner at loan start, per status -- so these rows pull the answer directly. Warn rather than block because the loan amount and status are themselves sound and feed Q2, Q3, Q4 and Q10: removing the loans would make the certified loan total disagree with the source. Q7 publishes the flagged count next to the average, which is the honest treatment of a value that is probably wrong but not certainly so.</t>
+          <t>Tested order independently: the sum of all signed amounts on an account should equal its last reported balance, whatever order the postings are read in. The last reported balance is the end of the last day's running-balance chain (D028). 84 accounts breach a 1 CZK tolerance; 70 of those are within 100 CZK and sit in the rounding band (every amount in the source carries a single decimal, so residuals accumulate). The earlier highest-trans_id choice of "last balance" made 136 accounts appear to breach, 52 of them only because it read a mid-day balance. Warn, because the account is still usable and the Q9 average moves by cents; the band is reported so nobody confuses it with the material tier below. | 14 accounts are off by more than 100 CZK (largest 488.30 CZK, account 8856), which is a missing or extra posting rather than rounding. Before D028 the rule read a mid-day balance as the last one and reported 55, including an apparent 1,200 CZK break that was not real. This is the single most material finding for Q9, because the answer is an average balance and these accounts' balances cannot be derived from their own flows. It stays warn rather than block on purpose: the balance column is what Q9 reads, and it is internally plausible -- it is the *flows* that disagree with it. Quarantining the accounts would remove real balances from an average; blocking the postings would break the chain further. The defensible treatment is to publish the answer with the affected population and the residual attached, which is what the semantic layer makes the LLM do.</t>
         </is>
       </c>
       <c r="G5" s="6" t="n">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>Rows kept and flagged (_dq_flags carries 'owner_age_implausible'); the semantic layer attaches the caveat to the age metric so the LLM can repeat it. | Rows kept and flagged; Q7 reports the average with and without the flagged loans so the sensitivity is visible.</t>
+          <t>Account flagged; the month-end balance fact carries the residual so a user can see the size of the discrepancy next to the balance. | Account flagged as balance_unreconciled; Q9 reports the average together with the number of affected accounts and the total residual, so the reader can size the uncertainty instead of guessing at it.</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>Q7, Q8</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>owner was 11.9 years old when account 9 was opened</t>
+          <t>sum(signed_amount) = 59941.10 but last reported balance = 59939.30 (difference 1.80)</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3985,7 @@
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>partner_bank and partner_account are both NULL; operation = VKLAD</t>
+          <t>partner_bank and partner_account are both NULL; operation = NULL</t>
         </is>
       </c>
     </row>
@@ -4123,7 +4135,7 @@
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>balance_after = -1142.60</t>
+          <t>balance_after = -13466.40</t>
         </is>
       </c>
     </row>
@@ -4662,7 +4674,7 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>'The balance at the end of December 1998' (Q9) is a modelling decision, not a column: it needs a tie-break for intra-day order and a carry-forward for months with no posting. Both are decided here, once, and marked with is_carried_forward.</t>
+          <t>'The balance at the end of December 1998' (Q9) is a modelling decision, not a column: it needs the closing posting of a day with several (the end of the running-balance chain, D028) and a carry-forward for months with no posting. Both are decided here, once, and marked with closing_basis and is_carried_forward.</t>
         </is>
       </c>
     </row>
@@ -5172,7 +5184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5184,6 +5196,8 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5196,7 +5210,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>REFERENCE columns are hand-written SQL, used as ground truth and never shown to the model. LLM columns are the unedited output of claude_cli / claude-sonnet-5-5, called with no tools, no database access and no reference answers -- it saw only the rendered semantic layer. Generated SQL is reproduced exactly as the model produced it; nothing was hand-corrected. Executed as the consumer role 'cro_global', so every query passed through the row level security policies.</t>
+          <t>REFERENCE columns are hand-written SQL, used as ground truth and never shown to the model. LLM columns are the unedited output of claude_cli / claude-sonnet-5-5, called with no tools, no database access and no reference answers -- it saw only the rendered semantic layer. Generated SQL is reproduced exactly as the model produced it; nothing was hand-corrected. Executed as the consumer role 'cro_global', so every query passed through the row level security policies. Each answer also carries the intent (IR) the model declared; an answer is shown only when the SQL was verified against that intent and the semantic layer, and the metric recomputed from it agreed (D029). Passing the SQL guard alone is not evidence of a correct answer.</t>
         </is>
       </c>
     </row>
@@ -5244,6 +5258,16 @@
       <c r="I4" s="5" t="inlineStr">
         <is>
           <t>Interpretation applied (see Assumptions tab)</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Declared intent (IR)</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Intent check (src/sql_ir.py)</t>
         </is>
       </c>
     </row>
@@ -5283,19 +5307,19 @@
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>SELECT region, count(*) AS client_count FROM ai.client GROUP BY region ORDER BY client_count DESC, region</t>
+          <t>SELECT region, count(*) AS client_count FROM ai.client GROUP BY region ORDER BY region</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>region=south Moravia | client_count=937
-region=north Moravia | client_count=920
+          <t>region=Prague | client_count=663
 region=central Bohemia | client_count=664
-region=Prague | client_count=663
 region=east Bohemia | client_count=660
 region=north Bohemia | client_count=561
-region=west Bohemia | client_count=515
-region=south Bohemia | client_count=449</t>
+region=north Moravia | client_count=920
+region=south Bohemia | client_count=449
+region=south Moravia | client_count=937
+region=west Bohemia | client_count=515</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
@@ -5311,6 +5335,27 @@
       <c r="I5" s="6" t="inlineStr">
         <is>
           <t>Interpretation (A1): "region" is the region of the CLIENT'S OWN district</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>{
+ "metric": "client_count",
+ "entity": "ai.client",
+ "counting_grain": "client_id",
+ "time": null,
+ "group_by": [
+  "region"
+ ],
+ "filters": [],
+ "order": null,
+ "limit": null
+}</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>VERIFIED: ir, columns, entity, joins, measure, grouping, filters, limit, guard, plan, recompute</t>
         </is>
       </c>
     </row>
@@ -5349,17 +5394,17 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>SELECT l.loan_year, count(*) AS loan_count, sum(l.amount) AS total_loan_amount FROM ai.loan AS l GROUP BY l.loan_year ORDER BY l.loan_year</t>
+          <t>SELECT l.loan_year AS loan_year, sum(l.amount) AS total_loan_amount, count(*) AS loan_count FROM ai.loan AS l WHERE l.loan_date &gt;= DATE '1993-01-01' AND l.loan_date &lt; DATE '1999-01-01' GROUP BY l.loan_year ORDER BY l.loan_year</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>loan_year=1993 | loan_count=20 | total_loan_amount=2619276.0
-loan_year=1994 | loan_count=101 | total_loan_amount=13379904.0
-loan_year=1995 | loan_count=90 | total_loan_amount=13344372.0
-loan_year=1996 | loan_count=117 | total_loan_amount=18317676.0
-loan_year=1997 | loan_count=196 | total_loan_amount=30731364.0
-loan_year=1998 | loan_count=158 | total_loan_amount=24869148.0</t>
+          <t>loan_year=1993 | total_loan_amount=2619276.0 | loan_count=20
+loan_year=1994 | total_loan_amount=13379904.0 | loan_count=101
+loan_year=1995 | total_loan_amount=13344372.0 | loan_count=90
+loan_year=1996 | total_loan_amount=18317676.0 | loan_count=117
+loan_year=1997 | total_loan_amount=30731364.0 | loan_count=196
+loan_year=1998 | total_loan_amount=24869148.0 | loan_count=158</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
@@ -5375,6 +5420,35 @@
       <c r="I6" s="6" t="inlineStr">
         <is>
           <t>Interpretation (A3): "granted" is dated by loan.date (the loan start date),</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>{
+ "metric": "total_loan_amount",
+ "entity": "ai.loan",
+ "counting_grain": "loan_id",
+ "time": {
+  "column": "loan_date",
+  "periods": [
+   {
+    "from": "1993-01-01",
+    "to": "1999-01-01"
+   }
+  ]
+ },
+ "group_by": [
+  "loan_year"
+ ],
+ "filters": [],
+ "order": "asc",
+ "limit": null
+}</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>VERIFIED: ir, columns, entity, joins, periods, measure, grouping, filters, limit, guard, plan, recompute</t>
         </is>
       </c>
     </row>
@@ -5408,12 +5482,12 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>SELECT count(*) AS loan_count, count(*) FILTER (WHERE is_problematic) AS problematic_loan_count, round(100.0 * count(*) FILTER (WHERE is_problematic) / count(*), 2) AS problematic_loan_share_pct FROM ai.loan</t>
+          <t>SELECT count(*) AS loan_count, count(*) FILTER (WHERE is_problematic) AS problematic_loan_count, round(100.0 * count(*) FILTER (WHERE is_problematic) / count(*), 2) AS problematic_loan_share FROM ai.loan</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>loan_count=682 | problematic_loan_count=76 | problematic_loan_share_pct=11.14</t>
+          <t>loan_count=682 | problematic_loan_count=76 | problematic_loan_share=11.14</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
@@ -5429,6 +5503,25 @@
       <c r="I7" s="6" t="inlineStr">
         <is>
           <t>Interpretation (A4): "problematic" = loan status B (finished, not repaid) or</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>{
+ "metric": "problematic_loan_share",
+ "entity": "ai.loan",
+ "counting_grain": "loan_id",
+ "time": null,
+ "group_by": [],
+ "filters": [],
+ "order": null,
+ "limit": null
+}</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>VERIFIED: ir, columns, entity, joins, measure, grouping, filters, limit, guard, plan, recompute</t>
         </is>
       </c>
     </row>
@@ -5465,15 +5558,15 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>SELECT owner_card_type, count(*) AS loan_count, round(avg(amount), 2) AS average_loan_amount FROM ai.loan GROUP BY owner_card_type ORDER BY owner_card_type</t>
+          <t>SELECT owner_card_type, round(avg(amount), 2) AS average_loan_amount, count(*) AS loan_count FROM ai.loan GROUP BY owner_card_type ORDER BY owner_card_type</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>owner_card_type=classic | loan_count=133 | average_loan_amount=148808.57
-owner_card_type=gold | loan_count=16 | average_loan_amount=161880.75
-owner_card_type=junior | loan_count=21 | average_loan_amount=221970.29
-owner_card_type=no card | loan_count=512 | average_loan_amount=148864.71</t>
+          <t>owner_card_type=classic | average_loan_amount=148808.57 | loan_count=133
+owner_card_type=gold | average_loan_amount=161880.75 | loan_count=16
+owner_card_type=junior | average_loan_amount=221970.29 | loan_count=21
+owner_card_type=no card | average_loan_amount=148864.71 | loan_count=512</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
@@ -5489,6 +5582,27 @@
       <c r="I8" s="6" t="inlineStr">
         <is>
           <t>Interpretation (A5): the card is the card held by the account's OWNER</t>
+        </is>
+      </c>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>{
+ "metric": "average_loan_amount",
+ "entity": "ai.loan",
+ "counting_grain": "loan_id",
+ "time": null,
+ "group_by": [
+  "owner_card_type"
+ ],
+ "filters": [],
+ "order": null,
+ "limit": null
+}</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>VERIFIED: ir, columns, entity, joins, measure, grouping, filters, limit, guard, plan, recompute</t>
         </is>
       </c>
     </row>
@@ -5549,21 +5663,21 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>SELECT t.account_district_id, t.account_district_name, t.account_region, sum(t.amount) AS incoming_amount_czk, count(*) AS credit_postings, count(DISTINCT t.account_id) AS accounts_with_credits FROM ai.transaction t WHERE t.direction = 'credit' AND t.trans_date &gt;= DATE '1997-01-01' AND t.trans_date &lt; DATE '1998-01-01' GROUP BY t.account_district_id, t.account_district_name, t.account_region ORDER BY sum(t.amount) DESC, t.account_district_name ASC LIMIT 10</t>
+          <t>SELECT account_district_name AS district_name, sum(amount) AS incoming_transaction_amount, count(*) AS credit_postings FROM ai.transaction WHERE direction = 'credit' AND trans_date &gt;= DATE '1997-01-01' AND trans_date &lt; DATE '1998-01-01' GROUP BY account_district_name ORDER BY incoming_transaction_amount DESC LIMIT 10</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>account_district_id=1 | account_district_name=Hl.m. Praha | account_region=Prague | incoming_amount_czk=115130200.1 | credit_postings=13611 | accounts_with_credits=554
-account_district_id=70 | account_district_name=Karvina | account_region=north Moravia | incoming_amount_czk=28506437.1 | credit_postings=3802 | accounts_with_credits=152
-account_district_id=74 | account_district_name=Ostrava - mesto | account_region=north Moravia | incoming_amount_czk=27689271.9 | credit_postings=3378 | accounts_with_credits=135
-account_district_id=54 | account_district_name=Brno - mesto | account_region=south Moravia | incoming_amount_czk=23095083.4 | credit_postings=3041 | accounts_with_credits=128
-account_district_id=64 | account_district_name=Zlin | account_region=south Moravia | incoming_amount_czk=19723168.5 | credit_postings=2299 | accounts_with_credits=92
-account_district_id=68 | account_district_name=Frydek - Mistek | account_region=north Moravia | incoming_amount_czk=19087598.8 | credit_postings=2006 | accounts_with_credits=83
-account_district_id=72 | account_district_name=Olomouc | account_region=north Moravia | incoming_amount_czk=15916397.0 | credit_postings=2129 | accounts_with_credits=88
-account_district_id=5 | account_district_name=Kolin | account_region=central Bohemia | incoming_amount_czk=14471603.6 | credit_postings=1542 | accounts_with_credits=65
-account_district_id=52 | account_district_name=Usti nad Orlici | account_region=east Bohemia | incoming_amount_czk=14085167.4 | credit_postings=1431 | accounts_with_credits=57
-account_district_id=19 | account_district_name=Prachatice | account_region=south Bohemia | incoming_amount_czk=12163147.0 | credit_postings=1359 | accounts_with_credits=55</t>
+          <t>district_name=Hl.m. Praha | incoming_transaction_amount=115130200.1 | credit_postings=13611
+district_name=Karvina | incoming_transaction_amount=28506437.1 | credit_postings=3802
+district_name=Ostrava - mesto | incoming_transaction_amount=27689271.9 | credit_postings=3378
+district_name=Brno - mesto | incoming_transaction_amount=23095083.4 | credit_postings=3041
+district_name=Zlin | incoming_transaction_amount=19723168.5 | credit_postings=2299
+district_name=Frydek - Mistek | incoming_transaction_amount=19087598.8 | credit_postings=2006
+district_name=Olomouc | incoming_transaction_amount=15916397.0 | credit_postings=2129
+district_name=Kolin | incoming_transaction_amount=14471603.6 | credit_postings=1542
+district_name=Usti nad Orlici | incoming_transaction_amount=14085167.4 | credit_postings=1431
+district_name=Prachatice | incoming_transaction_amount=12163147.0 | credit_postings=1359</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
@@ -5573,13 +5687,48 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>C5, C7</t>
+          <t>C5, C6, C7</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
           <t>Interpretation (A7): "incoming" = transaction type PRIJEM, that is
 Interpretation (A8): the district is the district the ACCOUNT is registered</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>{
+ "metric": "incoming_transaction_amount",
+ "entity": "ai.transaction",
+ "counting_grain": "trans_id",
+ "time": {
+  "column": "trans_date",
+  "periods": [
+   {
+    "from": "1997-01-01",
+    "to": "1998-01-01"
+   }
+  ]
+ },
+ "group_by": [
+  "account_district_name"
+ ],
+ "filters": [
+  {
+   "column": "direction",
+   "op": "=",
+   "value": "credit"
+  }
+ ],
+ "order": "desc",
+ "limit": 10
+}</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>VERIFIED: ir, columns, entity, joins, periods, measure, grouping, filters, limit, guard, plan, recompute</t>
         </is>
       </c>
     </row>
@@ -5630,23 +5779,23 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>SELECT c.year_month AS month, c.month_start, COUNT(a.account_id) AS new_accounts FROM (SELECT DISTINCT year_month, month_start FROM ai.calendar WHERE year = 1996) AS c LEFT JOIN ai.account AS a ON a.open_date &gt;= c.month_start AND a.open_date &lt; (c.month_start + INTERVAL '1 month') GROUP BY c.year_month, c.month_start ORDER BY c.month_start</t>
+          <t>SELECT c.year_month AS month, count(a.account_id) AS account_count FROM ai.calendar c LEFT JOIN ai.account a ON a.open_date = c.date_key WHERE c.date_key &gt;= DATE '1996-01-01' AND c.date_key &lt; DATE '1997-01-01' GROUP BY c.year_month ORDER BY c.year_month</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>month=1996-01 | month_start=1996-01-01 | new_accounts=106
-month=1996-02 | month_start=1996-02-01 | new_accounts=104
-month=1996-03 | month_start=1996-03-01 | new_accounts=124
-month=1996-04 | month_start=1996-04-01 | new_accounts=101
-month=1996-05 | month_start=1996-05-01 | new_accounts=91
-month=1996-06 | month_start=1996-06-01 | new_accounts=113
-month=1996-07 | month_start=1996-07-01 | new_accounts=137
-month=1996-08 | month_start=1996-08-01 | new_accounts=133
-month=1996-09 | month_start=1996-09-01 | new_accounts=108
-month=1996-10 | month_start=1996-10-01 | new_accounts=115
-month=1996-11 | month_start=1996-11-01 | new_accounts=106
-month=1996-12 | month_start=1996-12-01 | new_accounts=125</t>
+          <t>month=1996-01 | account_count=106
+month=1996-02 | account_count=104
+month=1996-03 | account_count=124
+month=1996-04 | account_count=101
+month=1996-05 | account_count=91
+month=1996-06 | account_count=113
+month=1996-07 | account_count=137
+month=1996-08 | account_count=133
+month=1996-09 | account_count=108
+month=1996-10 | account_count=115
+month=1996-11 | account_count=106
+month=1996-12 | account_count=125</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
@@ -5656,12 +5805,41 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
           <t>Interpretation (A9): "new account" is dated by account.date (the opening</t>
+        </is>
+      </c>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>{
+ "metric": "account_count",
+ "entity": "ai.account",
+ "counting_grain": "account_id",
+ "time": {
+  "column": "open_date",
+  "periods": [
+   {
+    "from": "1996-01-01",
+    "to": "1997-01-01"
+   }
+  ]
+ },
+ "group_by": [
+  "month"
+ ],
+ "filters": [],
+ "order": "asc",
+ "limit": null
+}</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>VERIFIED: ir, columns, entity, joins, periods, measure, grouping, filters, limit, guard, plan, recompute</t>
         </is>
       </c>
     </row>
@@ -5705,15 +5883,15 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>SELECT loan_status, status_code, count(*) AS loan_count, round(avg(owner_age_at_loan_start), 2) AS average_age_at_loan_start, count(*) FILTER (WHERE 'val_owner_age_at_loan_start' = ANY(data_quality_flags)) AS flagged_under_15_loans, round(avg(owner_age_at_loan_start) FILTER (WHERE NOT ('val_owner_age_at_loan_start' = ANY(data_quality_flags))), 2) AS average_age_excluding_flagged FROM ai.loan GROUP BY loan_status, status_code ORDER BY status_code</t>
+          <t>SELECT loan_status, round(avg(owner_age_at_loan_start), 2) AS average_age_at_loan_start, count(*) AS loan_count, round(avg(owner_age_at_loan_start) FILTER (WHERE NOT ('val_owner_age_at_loan_start' = ANY(data_quality_flags))), 2) AS average_age_excluding_flagged, count(*) FILTER (WHERE 'val_owner_age_at_loan_start' = ANY(data_quality_flags)) AS flagged_under_15_loans FROM ai.loan GROUP BY loan_status ORDER BY loan_status</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>loan_status=finished, paid in full | status_code=A | loan_count=203 | average_age_at_loan_start=37.07 | flagged_under_15_loans=4 | average_age_excluding_flagged=37.53
-loan_status=finished, unpaid (default) | status_code=B | loan_count=31 | average_age_at_loan_start=39.61 | flagged_under_15_loans=0 | average_age_excluding_flagged=39.61
-loan_status=running, no problem | status_code=C | loan_count=403 | average_age_at_loan_start=38.7 | flagged_under_15_loans=2 | average_age_excluding_flagged=38.82
-loan_status=running, client in debt | status_code=D | loan_count=45 | average_age_at_loan_start=37.0 | flagged_under_15_loans=0 | average_age_excluding_flagged=37.0</t>
+          <t>loan_status=finished, paid in full | average_age_at_loan_start=37.07 | loan_count=203 | average_age_excluding_flagged=37.53 | flagged_under_15_loans=4
+loan_status=finished, unpaid (default) | average_age_at_loan_start=39.61 | loan_count=31 | average_age_excluding_flagged=39.61 | flagged_under_15_loans=0
+loan_status=running, client in debt | average_age_at_loan_start=37.0 | loan_count=45 | average_age_excluding_flagged=37.0 | flagged_under_15_loans=0
+loan_status=running, no problem | average_age_at_loan_start=38.7 | loan_count=403 | average_age_excluding_flagged=38.82 | flagged_under_15_loans=2</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
@@ -5731,6 +5909,27 @@
           <t>Interpretation (A10): age is exact, computed from the owner's date of birth
 Interpretation (A11): the owner is the OWNER disposition of the loan's
 Data quality caveat: 6 loans were granted to owners recorded as under 15</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>{
+ "metric": "average_age_at_loan_start",
+ "entity": "ai.loan",
+ "counting_grain": "loan_id",
+ "time": null,
+ "group_by": [
+  "loan_status"
+ ],
+ "filters": [],
+ "order": null,
+ "limit": null
+}</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>VERIFIED: ir, columns, entity, joins, measure, grouping, filters, limit, guard, plan, recompute</t>
         </is>
       </c>
     </row>
@@ -5766,13 +5965,13 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>SELECT owner_gender AS gender, count(*) AS owner_count, round(100.0 * count(*) / sum(count(*)) OVER (), 2) AS share_pct, sum(count(*)) OVER () AS total_gold_card_owners FROM ai.account_owner WHERE owner_card_type = 'gold' GROUP BY owner_gender ORDER BY owner_gender</t>
+          <t>SELECT owner_gender, count(*) AS owner_count, round(100.0 * count(*) / sum(count(*)) OVER (), 2) AS gender_share_pct FROM ai.account_owner WHERE owner_card_type = 'gold' GROUP BY owner_gender ORDER BY owner_gender</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>gender=female | owner_count=35 | share_pct=39.77 | total_gold_card_owners=88.0
-gender=male | owner_count=53 | share_pct=60.23 | total_gold_card_owners=88.0</t>
+          <t>owner_gender=female | owner_count=35 | gender_share_pct=39.77
+owner_gender=male | owner_count=53 | gender_share_pct=60.23</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
@@ -5782,13 +5981,40 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
           <t>Interpretation (A12): the population is account OWNERS whose own disposition
 Interpretation (A13): the unit counted is the owner (one row per account in</t>
+        </is>
+      </c>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>{
+ "metric": "gender_share",
+ "entity": "ai.account_owner",
+ "counting_grain": "account_id",
+ "time": null,
+ "group_by": [
+  "owner_gender"
+ ],
+ "filters": [
+  {
+   "column": "owner_card_type",
+   "op": "=",
+   "value": "gold"
+  }
+ ],
+ "order": null,
+ "limit": null
+}</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>VERIFIED: ir, columns, entity, joins, measure, grouping, filters, limit, guard, plan, recompute</t>
         </is>
       </c>
     </row>
@@ -5815,7 +6041,8 @@
     count(*) FILTER (WHERE b.is_carried_forward)          AS accounts_carried_forward,
     count(*) FILTER (WHERE 'con_balance_reconciliation_material' = ANY (a._dq_flags))
                                                           AS accounts_balance_unreconciled,
-    count(*) FILTER (WHERE b.closing_balance &lt; 0)         AS accounts_overdrawn
+    count(*) FILTER (WHERE b.closing_balance &lt; 0)         AS accounts_overdrawn,
+    count(*) FILTER (WHERE b.closing_basis = 'ambiguous') AS accounts_closing_ambiguous
 FROM core.fact_account_month_end_balance b
 JOIN core.dim_account a ON a.account_id = b.account_id
 WHERE b.month_end_date = DATE '1998-12-31'</t>
@@ -5823,17 +6050,17 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>accounts_with_known_balance=4500 | average_balance=43808.94 | median_balance=38494.55 | min_balance=-25821.2 | max_balance=138317.2 | accounts_carried_forward=76 | accounts_balance_unreconciled=55 | accounts_overdrawn=39</t>
+          <t>accounts_with_known_balance=4500 | average_balance=43810.47 | median_balance=38494.55 | min_balance=-25821.2 | max_balance=137829.5 | accounts_carried_forward=76 | accounts_balance_unreconciled=14 | accounts_overdrawn=39 | accounts_closing_ambiguous=42</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>SELECT DATE '1998-12-31' AS month_end_date, round(avg(closing_balance), 2) AS average_month_end_balance, count(*) AS accounts_with_balance, count(*) FILTER (WHERE is_carried_forward) AS carried_forward_balances, count(*) FILTER (WHERE 'con_balance_reconciliation_material' = ANY(account_data_quality_flags)) AS accounts_with_reconciliation_flag FROM ai.account_month_end_balance WHERE month_end_date = DATE '1998-12-31'</t>
+          <t>SELECT round(avg(closing_balance), 2) AS average_month_end_balance, count(*) AS accounts_with_balance, count(*) FILTER (WHERE is_carried_forward) AS carried_forward_count, count(*) FILTER (WHERE closing_basis = 'ambiguous') AS ambiguous_count FROM ai.account_month_end_balance WHERE month_end_date &gt;= DATE '1998-12-31' AND month_end_date &lt; DATE '1999-01-01'</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>month_end_date=1998-12-31 | average_month_end_balance=43808.94 | accounts_with_balance=4500 | carried_forward_balances=76 | accounts_with_reconciliation_flag=55</t>
+          <t>average_month_end_balance=43810.47 | accounts_with_balance=4500 | carried_forward_count=76 | ambiguous_count=42</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
@@ -5851,6 +6078,33 @@
           <t>Interpretation (A14): the balance of an account at 1998-12-31 is the balance
 Interpretation (A15): the average is over accounts that have a known balance
 Data quality caveats, both reported next to the number rather than in a</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>{
+ "metric": "average_month_end_balance",
+ "entity": "ai.account_month_end_balance",
+ "counting_grain": "account_id, month_end_date",
+ "time": {
+  "column": "month_end_date",
+  "periods": [
+   {
+    "from": "1998-12-31",
+    "to": "1999-01-01"
+   }
+  ]
+ },
+ "group_by": [],
+ "filters": [],
+ "order": null,
+ "limit": null
+}</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>VERIFIED: ir, columns, entity, joins, periods, measure, grouping, filters, limit, guard, plan, recompute</t>
         </is>
       </c>
     </row>
@@ -5890,14 +6144,14 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>SELECT statement_frequency, count(*) AS loan_count, count(*) FILTER (WHERE is_problematic) AS problematic_loan_count, round(100.0 * count(*) FILTER (WHERE is_problematic) / count(*), 2) AS problematic_loan_share_pct FROM ai.loan GROUP BY statement_frequency ORDER BY problematic_loan_share_pct DESC, statement_frequency</t>
+          <t>SELECT statement_frequency, count(*) AS loan_count, count(*) FILTER (WHERE is_problematic) AS problematic_loan_count, round(100.0 * count(*) FILTER (WHERE is_problematic) / count(*), 2) AS problematic_loan_share FROM ai.loan GROUP BY statement_frequency ORDER BY problematic_loan_share DESC</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>statement_frequency=after transaction | loan_count=32 | problematic_loan_count=6 | problematic_loan_share_pct=18.75
-statement_frequency=weekly | loan_count=91 | problematic_loan_count=11 | problematic_loan_share_pct=12.09
-statement_frequency=monthly | loan_count=559 | problematic_loan_count=59 | problematic_loan_share_pct=10.55</t>
+          <t>statement_frequency=after transaction | loan_count=32 | problematic_loan_count=6 | problematic_loan_share=18.75
+statement_frequency=weekly | loan_count=91 | problematic_loan_count=11 | problematic_loan_share=12.09
+statement_frequency=monthly | loan_count=559 | problematic_loan_count=59 | problematic_loan_share=10.55</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
@@ -5915,10 +6169,385 @@
           <t>Interpretation (A16): the share is problematic loans divided by all loans</t>
         </is>
       </c>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>{
+ "metric": "problematic_loan_share",
+ "entity": "ai.loan",
+ "counting_grain": "loan_id",
+ "time": null,
+ "group_by": [
+  "statement_frequency"
+ ],
+ "filters": [],
+ "order": "desc",
+ "limit": null
+}</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>VERIFIED: ir, columns, entity, joins, measure, grouping, filters, limit, guard, plan, recompute</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Additional questions, not in the brief: the gender and calendar-quarter cases (sql/61_reference_extra.sql; assumptions A47, A48)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="150" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Find male or female loans in Q1 1995.</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>SELECT
+    c.gender                                              AS gender,
+    count(*)                                              AS loans,
+    count(DISTINCT l.loan_id)                             AS distinct_loans,
+    sum(l.amount)                                         AS total_amount
+FROM core.fact_loan l
+JOIN core.bridge_disposition d ON d.account_id = l.account_id AND d.is_owner
+JOIN core.dim_client c         ON c.client_id = d.client_id
+WHERE l.loan_date &gt;= DATE '1995-01-01'
+  AND l.loan_date &lt;  DATE '1995-04-01'
+GROUP BY c.gender
+ORDER BY c.gender</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>gender=female | loans=10 | distinct_loans=10 | total_amount=1199448.0
+gender=male | loans=18 | distinct_loans=18 | total_amount=3034104.0</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>SELECT owner_gender, count(*) AS loan_count FROM ai.loan WHERE loan_date &gt;= DATE '1995-01-01' AND loan_date &lt; DATE '1995-04-01' GROUP BY owner_gender ORDER BY owner_gender</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>owner_gender=female | loan_count=10
+owner_gender=male | loan_count=18</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>Interpretation (A47): loans are counted once each and grouped by the gender</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>{
+ "metric": "loan_count",
+ "entity": "ai.loan",
+ "counting_grain": "loan_id",
+ "time": {
+  "column": "loan_date",
+  "periods": [
+   {
+    "from": "1995-01-01",
+    "to": "1995-04-01"
+   }
+  ]
+ },
+ "group_by": [
+  "owner_gender"
+ ],
+ "filters": [],
+ "order": null,
+ "limit": null
+}</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>VERIFIED: ir, columns, entity, joins, periods, measure, grouping, filters, limit, guard, plan, recompute</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="150" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Compare the total amount of loans granted in Q1-Q3 of 1995 with Q1-Q3 of 1998.</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>SELECT
+    extract(year FROM loan_date)::int                     AS year,
+    count(*)                                              AS loans,
+    sum(amount)                                           AS total_amount
+FROM core.fact_loan
+WHERE (loan_date &gt;= DATE '1995-01-01' AND loan_date &lt; DATE '1995-10-01')
+   OR (loan_date &gt;= DATE '1998-01-01' AND loan_date &lt; DATE '1998-10-01')
+GROUP BY 1
+ORDER BY 1</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>year=1995 | loans=63 | total_amount=9033564.0
+year=1998 | loans=132 | total_amount=21046932.0</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>SELECT loan_year, sum(amount) AS total_loan_amount, count(*) AS loan_count FROM ai.loan WHERE (loan_date &gt;= DATE '1995-01-01' AND loan_date &lt; DATE '1995-10-01') OR (loan_date &gt;= DATE '1998-01-01' AND loan_date &lt; DATE '1998-10-01') GROUP BY loan_year ORDER BY loan_year</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>loan_year=1995 | total_loan_amount=9033564.0 | loan_count=63
+loan_year=1998 | total_loan_amount=21046932.0 | loan_count=132</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>Interpretation (A3, A48): granted = loan_date; Q1-Q3 = calendar quarters 1</t>
+        </is>
+      </c>
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>{
+ "metric": "total_loan_amount",
+ "entity": "ai.loan",
+ "counting_grain": "loan_id",
+ "time": {
+  "column": "loan_date",
+  "periods": [
+   {
+    "from": "1995-01-01",
+    "to": "1995-10-01"
+   },
+   {
+    "from": "1998-01-01",
+    "to": "1998-10-01"
+   }
+  ]
+ },
+ "group_by": [
+  "loan_year"
+ ],
+ "filters": [],
+ "order": null,
+ "limit": null
+}</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>VERIFIED: ir, columns, entity, joins, periods, measure, grouping, filters, limit, guard, plan, recompute</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="150" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>How many new accounts were opened in Q1 1996?</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>SELECT count(*)                                           AS new_accounts
+FROM core.dim_account
+WHERE open_date &gt;= DATE '1996-01-01'
+  AND open_date &lt;  DATE '1996-04-01'</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>new_accounts=334</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>SELECT count(*) AS account_count FROM ai.account WHERE open_date &gt;= DATE '1996-01-01' AND open_date &lt; DATE '1996-04-01'</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>account_count=334</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>Interpretation (A10, A48): an account is new on its open_date; Q1 1996 is</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>{
+ "metric": "account_count",
+ "entity": "ai.account",
+ "counting_grain": "account_id",
+ "time": {
+  "column": "open_date",
+  "periods": [
+   {
+    "from": "1996-01-01",
+    "to": "1996-04-01"
+   }
+  ]
+ },
+ "group_by": [],
+ "filters": [],
+ "order": null,
+ "limit": null
+}</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>VERIFIED: ir, columns, entity, joins, periods, measure, grouping, filters, limit, guard, plan, recompute</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="150" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>How many loans were granted per quarter in 1996?</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>SELECT
+    extract(quarter FROM loan_date)::int                  AS quarter,
+    count(*)                                              AS loans,
+    sum(amount)                                           AS total_amount
+FROM core.fact_loan
+WHERE loan_date &gt;= DATE '1996-01-01'
+  AND loan_date &lt;  DATE '1997-01-01'
+GROUP BY 1
+ORDER BY 1</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>quarter=1 | loans=20 | total_amount=2907960.0
+quarter=2 | loans=23 | total_amount=4103220.0
+quarter=3 | loans=39 | total_amount=5196876.0
+quarter=4 | loans=35 | total_amount=6109620.0</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>SELECT c.quarter AS quarter, count(l.loan_id) AS loan_count FROM (SELECT DISTINCT quarter FROM ai.calendar WHERE date_key &gt;= DATE '1996-01-01' AND date_key &lt; DATE '1997-01-01') AS c LEFT JOIN ai.loan AS l ON extract(quarter FROM l.loan_date) = c.quarter AND l.loan_date &gt;= DATE '1996-01-01' AND l.loan_date &lt; DATE '1997-01-01' GROUP BY c.quarter ORDER BY c.quarter</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>quarter=1 | loan_count=20
+quarter=2 | loan_count=23
+quarter=3 | loan_count=39
+quarter=4 | loan_count=35</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>Interpretation (A3, A48): granted = loan_date; quarters are calendar</t>
+        </is>
+      </c>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>{
+ "metric": "loan_count",
+ "entity": "ai.loan",
+ "counting_grain": "loan_id",
+ "time": {
+  "column": "loan_date",
+  "periods": [
+   {
+    "from": "1996-01-01",
+    "to": "1997-01-01"
+   }
+  ]
+ },
+ "group_by": [
+  "quarter"
+ ],
+ "filters": [],
+ "order": null,
+ "limit": null
+}</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>VERIFIED: ir, columns, entity, joins, periods, measure, grouping, filters, limit, guard, plan, recompute</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:I2"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A16:K16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5930,7 +6559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H182"/>
+  <dimension ref="A1:I182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6107,81 +6736,81 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>south Moravia</t>
+          <t>Prague</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
-        <v>937</v>
+        <v>663</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>north Moravia</t>
+          <t>central Bohemia</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
-        <v>920</v>
+        <v>664</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>central Bohemia</t>
+          <t>east Bohemia</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
-        <v>664</v>
+        <v>660</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>Prague</t>
+          <t>north Bohemia</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
-        <v>663</v>
+        <v>561</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>east Bohemia</t>
+          <t>north Moravia</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
-        <v>660</v>
+        <v>920</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>north Bohemia</t>
+          <t>south Bohemia</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
-        <v>561</v>
+        <v>449</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>west Bohemia</t>
+          <t>south Moravia</t>
         </is>
       </c>
       <c r="B23" s="15" t="n">
-        <v>515</v>
+        <v>937</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>south Bohemia</t>
+          <t>west Bohemia</t>
         </is>
       </c>
       <c r="B24" s="15" t="n">
-        <v>449</v>
+        <v>515</v>
       </c>
     </row>
     <row r="27">
@@ -6319,12 +6948,12 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
+          <t>total_loan_amount</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
           <t>loan_count</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>total_loan_amount</t>
         </is>
       </c>
     </row>
@@ -6333,10 +6962,10 @@
         <v>1993</v>
       </c>
       <c r="B39" s="15" t="n">
+        <v>2619276</v>
+      </c>
+      <c r="C39" s="15" t="n">
         <v>20</v>
-      </c>
-      <c r="C39" s="15" t="n">
-        <v>2619276</v>
       </c>
     </row>
     <row r="40">
@@ -6344,10 +6973,10 @@
         <v>1994</v>
       </c>
       <c r="B40" s="15" t="n">
+        <v>13379904</v>
+      </c>
+      <c r="C40" s="15" t="n">
         <v>101</v>
-      </c>
-      <c r="C40" s="15" t="n">
-        <v>13379904</v>
       </c>
     </row>
     <row r="41">
@@ -6355,10 +6984,10 @@
         <v>1995</v>
       </c>
       <c r="B41" s="15" t="n">
+        <v>13344372</v>
+      </c>
+      <c r="C41" s="15" t="n">
         <v>90</v>
-      </c>
-      <c r="C41" s="15" t="n">
-        <v>13344372</v>
       </c>
     </row>
     <row r="42">
@@ -6366,10 +6995,10 @@
         <v>1996</v>
       </c>
       <c r="B42" s="15" t="n">
+        <v>18317676</v>
+      </c>
+      <c r="C42" s="15" t="n">
         <v>117</v>
-      </c>
-      <c r="C42" s="15" t="n">
-        <v>18317676</v>
       </c>
     </row>
     <row r="43">
@@ -6377,10 +7006,10 @@
         <v>1997</v>
       </c>
       <c r="B43" s="15" t="n">
+        <v>30731364</v>
+      </c>
+      <c r="C43" s="15" t="n">
         <v>196</v>
-      </c>
-      <c r="C43" s="15" t="n">
-        <v>30731364</v>
       </c>
     </row>
     <row r="44">
@@ -6388,10 +7017,10 @@
         <v>1998</v>
       </c>
       <c r="B44" s="15" t="n">
+        <v>24869148</v>
+      </c>
+      <c r="C44" s="15" t="n">
         <v>158</v>
-      </c>
-      <c r="C44" s="15" t="n">
-        <v>24869148</v>
       </c>
     </row>
     <row r="47">
@@ -6472,7 +7101,7 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>problematic_loan_share_pct</t>
+          <t>problematic_loan_share</t>
         </is>
       </c>
     </row>
@@ -6602,12 +7231,12 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
+          <t>average_loan_amount</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
           <t>loan_count</t>
-        </is>
-      </c>
-      <c r="C66" s="5" t="inlineStr">
-        <is>
-          <t>average_loan_amount</t>
         </is>
       </c>
     </row>
@@ -6618,10 +7247,10 @@
         </is>
       </c>
       <c r="B67" s="15" t="n">
+        <v>148808.57</v>
+      </c>
+      <c r="C67" s="15" t="n">
         <v>133</v>
-      </c>
-      <c r="C67" s="15" t="n">
-        <v>148808.57</v>
       </c>
     </row>
     <row r="68">
@@ -6631,10 +7260,10 @@
         </is>
       </c>
       <c r="B68" s="15" t="n">
+        <v>161880.75</v>
+      </c>
+      <c r="C68" s="15" t="n">
         <v>16</v>
-      </c>
-      <c r="C68" s="15" t="n">
-        <v>161880.75</v>
       </c>
     </row>
     <row r="69">
@@ -6644,10 +7273,10 @@
         </is>
       </c>
       <c r="B69" s="15" t="n">
+        <v>221970.29</v>
+      </c>
+      <c r="C69" s="15" t="n">
         <v>21</v>
-      </c>
-      <c r="C69" s="15" t="n">
-        <v>221970.29</v>
       </c>
     </row>
     <row r="70">
@@ -6657,10 +7286,10 @@
         </is>
       </c>
       <c r="B70" s="15" t="n">
+        <v>148864.71</v>
+      </c>
+      <c r="C70" s="15" t="n">
         <v>512</v>
-      </c>
-      <c r="C70" s="15" t="n">
-        <v>148864.71</v>
       </c>
     </row>
     <row r="73">
@@ -6994,273 +7623,148 @@
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>account_district_id</t>
+          <t>district_name</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>account_district_name</t>
+          <t>incoming_transaction_amount</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>account_region</t>
-        </is>
-      </c>
-      <c r="D88" s="5" t="inlineStr">
-        <is>
-          <t>incoming_amount_czk</t>
-        </is>
-      </c>
-      <c r="E88" s="5" t="inlineStr">
-        <is>
           <t>credit_postings</t>
         </is>
       </c>
-      <c r="F88" s="5" t="inlineStr">
-        <is>
-          <t>accounts_with_credits</t>
-        </is>
-      </c>
     </row>
     <row r="89">
-      <c r="A89" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="B89" s="15" t="inlineStr">
+      <c r="A89" s="15" t="inlineStr">
         <is>
           <t>Hl.m. Praha</t>
         </is>
       </c>
-      <c r="C89" s="15" t="inlineStr">
-        <is>
-          <t>Prague</t>
-        </is>
-      </c>
-      <c r="D89" s="15" t="n">
+      <c r="B89" s="15" t="n">
         <v>115130200.1</v>
       </c>
-      <c r="E89" s="15" t="n">
+      <c r="C89" s="15" t="n">
         <v>13611</v>
       </c>
-      <c r="F89" s="15" t="n">
-        <v>554</v>
-      </c>
     </row>
     <row r="90">
-      <c r="A90" s="15" t="n">
-        <v>70</v>
-      </c>
-      <c r="B90" s="15" t="inlineStr">
+      <c r="A90" s="15" t="inlineStr">
         <is>
           <t>Karvina</t>
         </is>
       </c>
-      <c r="C90" s="15" t="inlineStr">
-        <is>
-          <t>north Moravia</t>
-        </is>
-      </c>
-      <c r="D90" s="15" t="n">
+      <c r="B90" s="15" t="n">
         <v>28506437.1</v>
       </c>
-      <c r="E90" s="15" t="n">
+      <c r="C90" s="15" t="n">
         <v>3802</v>
       </c>
-      <c r="F90" s="15" t="n">
-        <v>152</v>
-      </c>
     </row>
     <row r="91">
-      <c r="A91" s="15" t="n">
-        <v>74</v>
-      </c>
-      <c r="B91" s="15" t="inlineStr">
+      <c r="A91" s="15" t="inlineStr">
         <is>
           <t>Ostrava - mesto</t>
         </is>
       </c>
-      <c r="C91" s="15" t="inlineStr">
-        <is>
-          <t>north Moravia</t>
-        </is>
-      </c>
-      <c r="D91" s="15" t="n">
+      <c r="B91" s="15" t="n">
         <v>27689271.9</v>
       </c>
-      <c r="E91" s="15" t="n">
+      <c r="C91" s="15" t="n">
         <v>3378</v>
       </c>
-      <c r="F91" s="15" t="n">
-        <v>135</v>
-      </c>
     </row>
     <row r="92">
-      <c r="A92" s="15" t="n">
-        <v>54</v>
-      </c>
-      <c r="B92" s="15" t="inlineStr">
+      <c r="A92" s="15" t="inlineStr">
         <is>
           <t>Brno - mesto</t>
         </is>
       </c>
-      <c r="C92" s="15" t="inlineStr">
-        <is>
-          <t>south Moravia</t>
-        </is>
-      </c>
-      <c r="D92" s="15" t="n">
+      <c r="B92" s="15" t="n">
         <v>23095083.4</v>
       </c>
-      <c r="E92" s="15" t="n">
+      <c r="C92" s="15" t="n">
         <v>3041</v>
       </c>
-      <c r="F92" s="15" t="n">
-        <v>128</v>
-      </c>
     </row>
     <row r="93">
-      <c r="A93" s="15" t="n">
-        <v>64</v>
-      </c>
-      <c r="B93" s="15" t="inlineStr">
+      <c r="A93" s="15" t="inlineStr">
         <is>
           <t>Zlin</t>
         </is>
       </c>
-      <c r="C93" s="15" t="inlineStr">
-        <is>
-          <t>south Moravia</t>
-        </is>
-      </c>
-      <c r="D93" s="15" t="n">
+      <c r="B93" s="15" t="n">
         <v>19723168.5</v>
       </c>
-      <c r="E93" s="15" t="n">
+      <c r="C93" s="15" t="n">
         <v>2299</v>
       </c>
-      <c r="F93" s="15" t="n">
-        <v>92</v>
-      </c>
     </row>
     <row r="94">
-      <c r="A94" s="15" t="n">
-        <v>68</v>
-      </c>
-      <c r="B94" s="15" t="inlineStr">
+      <c r="A94" s="15" t="inlineStr">
         <is>
           <t>Frydek - Mistek</t>
         </is>
       </c>
-      <c r="C94" s="15" t="inlineStr">
-        <is>
-          <t>north Moravia</t>
-        </is>
-      </c>
-      <c r="D94" s="15" t="n">
+      <c r="B94" s="15" t="n">
         <v>19087598.8</v>
       </c>
-      <c r="E94" s="15" t="n">
+      <c r="C94" s="15" t="n">
         <v>2006</v>
       </c>
-      <c r="F94" s="15" t="n">
-        <v>83</v>
-      </c>
     </row>
     <row r="95">
-      <c r="A95" s="15" t="n">
-        <v>72</v>
-      </c>
-      <c r="B95" s="15" t="inlineStr">
+      <c r="A95" s="15" t="inlineStr">
         <is>
           <t>Olomouc</t>
         </is>
       </c>
-      <c r="C95" s="15" t="inlineStr">
-        <is>
-          <t>north Moravia</t>
-        </is>
-      </c>
-      <c r="D95" s="15" t="n">
+      <c r="B95" s="15" t="n">
         <v>15916397</v>
       </c>
-      <c r="E95" s="15" t="n">
+      <c r="C95" s="15" t="n">
         <v>2129</v>
       </c>
-      <c r="F95" s="15" t="n">
-        <v>88</v>
-      </c>
     </row>
     <row r="96">
-      <c r="A96" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="B96" s="15" t="inlineStr">
+      <c r="A96" s="15" t="inlineStr">
         <is>
           <t>Kolin</t>
         </is>
       </c>
-      <c r="C96" s="15" t="inlineStr">
-        <is>
-          <t>central Bohemia</t>
-        </is>
-      </c>
-      <c r="D96" s="15" t="n">
+      <c r="B96" s="15" t="n">
         <v>14471603.6</v>
       </c>
-      <c r="E96" s="15" t="n">
+      <c r="C96" s="15" t="n">
         <v>1542</v>
       </c>
-      <c r="F96" s="15" t="n">
-        <v>65</v>
-      </c>
     </row>
     <row r="97">
-      <c r="A97" s="15" t="n">
-        <v>52</v>
-      </c>
-      <c r="B97" s="15" t="inlineStr">
+      <c r="A97" s="15" t="inlineStr">
         <is>
           <t>Usti nad Orlici</t>
         </is>
       </c>
-      <c r="C97" s="15" t="inlineStr">
-        <is>
-          <t>east Bohemia</t>
-        </is>
-      </c>
-      <c r="D97" s="15" t="n">
+      <c r="B97" s="15" t="n">
         <v>14085167.4</v>
       </c>
-      <c r="E97" s="15" t="n">
+      <c r="C97" s="15" t="n">
         <v>1431</v>
       </c>
-      <c r="F97" s="15" t="n">
-        <v>57</v>
-      </c>
     </row>
     <row r="98">
-      <c r="A98" s="15" t="n">
-        <v>19</v>
-      </c>
-      <c r="B98" s="15" t="inlineStr">
+      <c r="A98" s="15" t="inlineStr">
         <is>
           <t>Prachatice</t>
         </is>
       </c>
-      <c r="C98" s="15" t="inlineStr">
-        <is>
-          <t>south Bohemia</t>
-        </is>
-      </c>
-      <c r="D98" s="15" t="n">
+      <c r="B98" s="15" t="n">
         <v>12163147</v>
       </c>
-      <c r="E98" s="15" t="n">
+      <c r="C98" s="15" t="n">
         <v>1359</v>
-      </c>
-      <c r="F98" s="15" t="n">
-        <v>55</v>
       </c>
     </row>
     <row r="101">
@@ -7530,12 +8034,7 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>month_start</t>
-        </is>
-      </c>
-      <c r="C118" s="5" t="inlineStr">
-        <is>
-          <t>new_accounts</t>
+          <t>account_count</t>
         </is>
       </c>
     </row>
@@ -7545,12 +8044,7 @@
           <t>1996-01</t>
         </is>
       </c>
-      <c r="B119" s="15" t="inlineStr">
-        <is>
-          <t>1996-01-01</t>
-        </is>
-      </c>
-      <c r="C119" s="15" t="n">
+      <c r="B119" s="15" t="n">
         <v>106</v>
       </c>
     </row>
@@ -7560,12 +8054,7 @@
           <t>1996-02</t>
         </is>
       </c>
-      <c r="B120" s="15" t="inlineStr">
-        <is>
-          <t>1996-02-01</t>
-        </is>
-      </c>
-      <c r="C120" s="15" t="n">
+      <c r="B120" s="15" t="n">
         <v>104</v>
       </c>
     </row>
@@ -7575,12 +8064,7 @@
           <t>1996-03</t>
         </is>
       </c>
-      <c r="B121" s="15" t="inlineStr">
-        <is>
-          <t>1996-03-01</t>
-        </is>
-      </c>
-      <c r="C121" s="15" t="n">
+      <c r="B121" s="15" t="n">
         <v>124</v>
       </c>
     </row>
@@ -7590,12 +8074,7 @@
           <t>1996-04</t>
         </is>
       </c>
-      <c r="B122" s="15" t="inlineStr">
-        <is>
-          <t>1996-04-01</t>
-        </is>
-      </c>
-      <c r="C122" s="15" t="n">
+      <c r="B122" s="15" t="n">
         <v>101</v>
       </c>
     </row>
@@ -7605,12 +8084,7 @@
           <t>1996-05</t>
         </is>
       </c>
-      <c r="B123" s="15" t="inlineStr">
-        <is>
-          <t>1996-05-01</t>
-        </is>
-      </c>
-      <c r="C123" s="15" t="n">
+      <c r="B123" s="15" t="n">
         <v>91</v>
       </c>
     </row>
@@ -7620,12 +8094,7 @@
           <t>1996-06</t>
         </is>
       </c>
-      <c r="B124" s="15" t="inlineStr">
-        <is>
-          <t>1996-06-01</t>
-        </is>
-      </c>
-      <c r="C124" s="15" t="n">
+      <c r="B124" s="15" t="n">
         <v>113</v>
       </c>
     </row>
@@ -7635,12 +8104,7 @@
           <t>1996-07</t>
         </is>
       </c>
-      <c r="B125" s="15" t="inlineStr">
-        <is>
-          <t>1996-07-01</t>
-        </is>
-      </c>
-      <c r="C125" s="15" t="n">
+      <c r="B125" s="15" t="n">
         <v>137</v>
       </c>
     </row>
@@ -7650,12 +8114,7 @@
           <t>1996-08</t>
         </is>
       </c>
-      <c r="B126" s="15" t="inlineStr">
-        <is>
-          <t>1996-08-01</t>
-        </is>
-      </c>
-      <c r="C126" s="15" t="n">
+      <c r="B126" s="15" t="n">
         <v>133</v>
       </c>
     </row>
@@ -7665,12 +8124,7 @@
           <t>1996-09</t>
         </is>
       </c>
-      <c r="B127" s="15" t="inlineStr">
-        <is>
-          <t>1996-09-01</t>
-        </is>
-      </c>
-      <c r="C127" s="15" t="n">
+      <c r="B127" s="15" t="n">
         <v>108</v>
       </c>
     </row>
@@ -7680,12 +8134,7 @@
           <t>1996-10</t>
         </is>
       </c>
-      <c r="B128" s="15" t="inlineStr">
-        <is>
-          <t>1996-10-01</t>
-        </is>
-      </c>
-      <c r="C128" s="15" t="n">
+      <c r="B128" s="15" t="n">
         <v>115</v>
       </c>
     </row>
@@ -7695,12 +8144,7 @@
           <t>1996-11</t>
         </is>
       </c>
-      <c r="B129" s="15" t="inlineStr">
-        <is>
-          <t>1996-11-01</t>
-        </is>
-      </c>
-      <c r="C129" s="15" t="n">
+      <c r="B129" s="15" t="n">
         <v>106</v>
       </c>
     </row>
@@ -7710,12 +8154,7 @@
           <t>1996-12</t>
         </is>
       </c>
-      <c r="B130" s="15" t="inlineStr">
-        <is>
-          <t>1996-12-01</t>
-        </is>
-      </c>
-      <c r="C130" s="15" t="n">
+      <c r="B130" s="15" t="n">
         <v>125</v>
       </c>
     </row>
@@ -7893,7 +8332,7 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>status_code</t>
+          <t>average_age_at_loan_start</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
@@ -7903,17 +8342,12 @@
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>average_age_at_loan_start</t>
+          <t>average_age_excluding_flagged</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
           <t>flagged_under_15_loans</t>
-        </is>
-      </c>
-      <c r="F142" s="5" t="inlineStr">
-        <is>
-          <t>average_age_excluding_flagged</t>
         </is>
       </c>
     </row>
@@ -7923,23 +8357,18 @@
           <t>finished, paid in full</t>
         </is>
       </c>
-      <c r="B143" s="15" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+      <c r="B143" s="15" t="n">
+        <v>37.07</v>
       </c>
       <c r="C143" s="15" t="n">
         <v>203</v>
       </c>
       <c r="D143" s="15" t="n">
-        <v>37.07</v>
+        <v>37.53</v>
       </c>
       <c r="E143" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="F143" s="15" t="n">
-        <v>37.53</v>
-      </c>
     </row>
     <row r="144">
       <c r="A144" s="15" t="inlineStr">
@@ -7947,10 +8376,8 @@
           <t>finished, unpaid (default)</t>
         </is>
       </c>
-      <c r="B144" s="15" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
+      <c r="B144" s="15" t="n">
+        <v>39.61</v>
       </c>
       <c r="C144" s="15" t="n">
         <v>31</v>
@@ -7961,56 +8388,43 @@
       <c r="E144" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F144" s="15" t="n">
-        <v>39.61</v>
-      </c>
     </row>
     <row r="145">
       <c r="A145" s="15" t="inlineStr">
         <is>
-          <t>running, no problem</t>
-        </is>
-      </c>
-      <c r="B145" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
+          <t>running, client in debt</t>
+        </is>
+      </c>
+      <c r="B145" s="15" t="n">
+        <v>37</v>
       </c>
       <c r="C145" s="15" t="n">
-        <v>403</v>
+        <v>45</v>
       </c>
       <c r="D145" s="15" t="n">
-        <v>38.7</v>
+        <v>37</v>
       </c>
       <c r="E145" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="F145" s="15" t="n">
-        <v>38.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="15" t="inlineStr">
         <is>
-          <t>running, client in debt</t>
-        </is>
-      </c>
-      <c r="B146" s="15" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
+          <t>running, no problem</t>
+        </is>
+      </c>
+      <c r="B146" s="15" t="n">
+        <v>38.7</v>
       </c>
       <c r="C146" s="15" t="n">
-        <v>45</v>
+        <v>403</v>
       </c>
       <c r="D146" s="15" t="n">
-        <v>37</v>
+        <v>38.82</v>
       </c>
       <c r="E146" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F146" s="15" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
@@ -8091,7 +8505,7 @@
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>gender</t>
+          <t>owner_gender</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
@@ -8101,12 +8515,7 @@
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>share_pct</t>
-        </is>
-      </c>
-      <c r="D156" s="5" t="inlineStr">
-        <is>
-          <t>total_gold_card_owners</t>
+          <t>gender_share_pct</t>
         </is>
       </c>
     </row>
@@ -8122,9 +8531,6 @@
       <c r="C157" s="15" t="n">
         <v>39.77</v>
       </c>
-      <c r="D157" s="15" t="n">
-        <v>88</v>
-      </c>
     </row>
     <row r="158">
       <c r="A158" s="15" t="inlineStr">
@@ -8138,9 +8544,6 @@
       <c r="C158" s="15" t="n">
         <v>60.23</v>
       </c>
-      <c r="D158" s="15" t="n">
-        <v>88</v>
-      </c>
     </row>
     <row r="161">
       <c r="A161" s="13" t="inlineStr">
@@ -8195,6 +8598,11 @@
       <c r="H163" s="5" t="inlineStr">
         <is>
           <t>accounts_overdrawn</t>
+        </is>
+      </c>
+      <c r="I163" s="5" t="inlineStr">
+        <is>
+          <t>accounts_closing_ambiguous</t>
         </is>
       </c>
     </row>
@@ -8203,7 +8611,7 @@
         <v>4500</v>
       </c>
       <c r="B164" s="15" t="n">
-        <v>43808.94</v>
+        <v>43810.47</v>
       </c>
       <c r="C164" s="15" t="n">
         <v>38494.55</v>
@@ -8212,17 +8620,20 @@
         <v>-25821.2</v>
       </c>
       <c r="E164" s="15" t="n">
-        <v>138317.2</v>
+        <v>137829.5</v>
       </c>
       <c r="F164" s="15" t="n">
         <v>76</v>
       </c>
       <c r="G164" s="15" t="n">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="H164" s="15" t="n">
         <v>39</v>
       </c>
+      <c r="I164" s="15" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="14" t="inlineStr">
@@ -8234,47 +8645,37 @@
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>month_end_date</t>
+          <t>average_month_end_balance</t>
         </is>
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>average_month_end_balance</t>
+          <t>accounts_with_balance</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>accounts_with_balance</t>
+          <t>carried_forward_count</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>carried_forward_balances</t>
-        </is>
-      </c>
-      <c r="E167" s="5" t="inlineStr">
-        <is>
-          <t>accounts_with_reconciliation_flag</t>
+          <t>ambiguous_count</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="15" t="inlineStr">
-        <is>
-          <t>1998-12-31</t>
-        </is>
+      <c r="A168" s="15" t="n">
+        <v>43810.47</v>
       </c>
       <c r="B168" s="15" t="n">
-        <v>43808.94</v>
+        <v>4500</v>
       </c>
       <c r="C168" s="15" t="n">
-        <v>4500</v>
+        <v>76</v>
       </c>
       <c r="D168" s="15" t="n">
-        <v>76</v>
-      </c>
-      <c r="E168" s="15" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
     </row>
     <row r="171">
@@ -8400,7 +8801,7 @@
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>problematic_loan_share_pct</t>
+          <t>problematic_loan_share</t>
         </is>
       </c>
     </row>
@@ -10912,7 +11313,7 @@
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>55 accounts are off by more than 100 CZK and one by exactly 1,200.00 CZK with only 55 postings, which is a missing or extra posting rather than rounding. This is the single most material finding for Q9, because the answer is an average balance and these accounts' balances cannot be derived from their own flows. It stays warn rather than block on purpose: the balance column is what Q9 reads, and it is internally plausible -- it is the *flows* that disagree with it. Quarantining the accounts would remove real balances from an average; blocking the postings would break the chain further. The defensible treatment is to publish the answer with the affected population and the residual attached, which is what the semantic layer makes the LLM do.</t>
+          <t>14 accounts are off by more than 100 CZK (largest 488.30 CZK, account 8856), which is a missing or extra posting rather than rounding. Before D028 the rule read a mid-day balance as the last one and reported 55, including an apparent 1,200 CZK break that was not real. This is the single most material finding for Q9, because the answer is an average balance and these accounts' balances cannot be derived from their own flows. It stays warn rather than block on purpose: the balance column is what Q9 reads, and it is internally plausible -- it is the *flows* that disagree with it. Quarantining the accounts would remove real balances from an average; blocking the postings would break the chain further. The defensible treatment is to publish the answer with the affected population and the residual attached, which is what the semantic layer makes the LLM do.</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
@@ -10954,7 +11355,7 @@
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>Tested order independently: the sum of all signed amounts on an account should equal its last reported balance, whatever order the postings are read in. 136 accounts breach a 1 CZK tolerance; 81 of those are within 100 CZK and sit in the rounding band (every amount in the source carries a single decimal, so residuals accumulate). Warn, because the account is still usable and the Q9 average moves by cents; the band is reported so nobody confuses it with the material tier below.</t>
+          <t>Tested order independently: the sum of all signed amounts on an account should equal its last reported balance, whatever order the postings are read in. The last reported balance is the end of the last day's running-balance chain (D028). 84 accounts breach a 1 CZK tolerance; 70 of those are within 100 CZK and sit in the rounding band (every amount in the source carries a single decimal, so residuals accumulate). The earlier highest-trans_id choice of "last balance" made 136 accounts appear to breach, 52 of them only because it read a mid-day balance. Warn, because the account is still usable and the Q9 average moves by cents; the band is reported so nobody confuses it with the material tier below.</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
@@ -11028,7 +11429,7 @@
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>Closing balance of the account's last day is not uniquely determined</t>
+          <t>Account has several postings on its latest date (closing posting must be derived)</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
@@ -11038,7 +11439,7 @@
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>trans_id is not chronological within a date, so when an account has several postings on one day there is no way to tell which one closed the day. For 183 accounts that ambiguity falls on their most recent date, which is precisely the balance Q9 reports. The answer is therefore a documented choice (highest trans_id on the latest date) rather than a fact, and the count of affected accounts belongs next to the answer. Warn: the data is not wrong, the determinism is missing.</t>
+          <t>trans_id is not chronological within a date and the source has no time of day, so when an account has several postings on one day the closing one has to be derived. 183 accounts have this on their most recent date, which is the balance Q9 reports. The running balance resolves it (D028): each posting starts at balance_after - signed_amount, and the closing posting is the end of that chain. That settles 141 of the 183; for the other 42 the chain does not order the postings, the documented fallback is used and the month-end row is marked closing_basis = 'ambiguous'. Warn: the data is not wrong, the order has to be inferred.</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
@@ -11048,7 +11449,7 @@
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>Tie-break documented in the semantic layer and applied identically in the reference SQL and in core.fact_account_month_end_balance; affected accounts flagged so the caveat can be quantified.</t>
+          <t>Closing posting taken from the running-balance chain in core.fact_account_month_end_balance (closing_basis records how); accounts flagged so the caveat can be quantified.</t>
         </is>
       </c>
     </row>
@@ -13229,7 +13630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -13539,7 +13940,7 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>A calendar-year difference (year(loan) - year(birth)) reports ages roughly 0.5 years higher.</t>
+          <t>Truncating to completed years (date_part('year', age(loan, birth))) reports ages about 0.5 years lower (36.59 vs 37.07 for status A). A calendar-year difference (year(loan) - year(birth)) lands within 0.11 years of the exact average per status, but is wrong for any individual loan. (Corrected 2026-10-28: an earlier version said the calendar-year difference reads 0.5 years high; measured, it does not.)</t>
         </is>
       </c>
     </row>
@@ -13637,17 +14038,17 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>The balance at 1998-12-31 is the balance after the last posting on or before that date, from core.fact_account_month_end_balance, with ties on a date broken by the highest trans_id.</t>
+          <t>The balance at 1998-12-31 is the balance after the last posting on or before that date, from core.fact_account_month_end_balance. When several postings share the last date, the closing one is the end of that day's running-balance chain (each posting starts at balance_after - signed_amount); where the chain cannot order them, the lowest trans_id among the chain ends is used and the row is marked closing_basis = 'ambiguous' (D028).</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>trans_id is not chronological within a day, so a tie-break is unavoidable; it is documented and applied identically in the reference SQL, in the model and in the semantic layer.</t>
+          <t>The source has no time of day and trans_id is not chronological; the running balance is the only recorded evidence of order. Where the chain resolves the order, lowest id agrees with it 96.9% of the time and highest id 0.4%.</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>183 accounts have several postings on their latest date (rule CON_INTRADAY_ORDER_AMBIGUOUS, warn), so for those the closing balance is a documented choice rather than a fact.</t>
+          <t>183 accounts have several postings on their latest date: 141 are resolved by the chain, 42 remain ambiguous. Before D028 the highest trans_id was used, which put Q9 at 43,808.94 instead of 43,810.47.</t>
         </is>
       </c>
     </row>
@@ -13708,808 +14109,889 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>A17</t>
+          <t>A47</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Dates</t>
+          <t>E1 (gender of loans)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>A two-digit source year is always 19xx.</t>
+          <t>"Male or female loans" counts loans, once each, grouped by the gender of the loan's account owner (ai.loan.owner_gender, i.e. core.dim_client.gender through the OWNER disposition). Pending business confirmation.</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>The dataset runs 1993-1998 and was published in 1999; there is no 20xx data.</t>
+          <t>Gender is an attribute of a client only (ai.client.gender); ai.loan and ai.account_owner carry it as owner_gender. A loan has no borrower of its own in the source; it reaches a person through its account, and A5/A11 already attribute loans to the owner. Every account has exactly one owner, so the join cannot repeat a loan.</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>A 20xx reading would move dates out of the validity window, which rule VAL_DATE_OUT_OF_RANGE would block -- so the assumption fails loudly rather than silently.</t>
+          <t>Q1 1995: 28 loans, 18 male-owned and 10 female-owned. Counting every client on the account (owners and disponents) counts loan-client pairs, not loans: 34 pairs, because 6 loans have a disponent of the other gender, so the two groups would overlap. The verifier refuses that join path for loan_count unless the metric is redefined.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>A18</t>
+          <t>A48</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Gender</t>
+          <t>E1-E4 (quarters)</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>birth_number encodes sex as month + 50 for women, and that is the only available source for gender.</t>
+          <t>"Q1"-"Q4" in a question are calendar quarters (Jan-Mar, Apr-Jun, Jul-Sep, Oct-Dec), written as half-open date ranges, and a comparison across periods returns one row per period. Q1-Q10 in the context pack only label the reference questions. Pending business confirmation.</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Documented with the dataset; CON_GENDER_MATCHES_BIRTH_NUMBER checks the decode against the raw digits on every run.</t>
+          <t>The book has no fiscal calendar and nothing in the source defines one. One row per period is what the verifier can check against the IR and what the evaluator compares.</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Q8 is entirely built on it. The rule turns a decoder regression into a build failure.</t>
+          <t>A fiscal year starting in another month moves every quarter boundary; it would be one change to ai.calendar and the IR periods, and the day-by-day period check would then enforce the new boundaries. A pivoted answer (one column per period) is refused today and would need the verifier extended.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>A19</t>
+          <t>A49</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>Q5 (interest)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>All amounts are in the same currency (CZK) and no conversion is needed.</t>
+          <t>Bank-credited interest (category_code = 'UROK', 48,788 credits in 1997) counts as incoming money. Pending business confirmation.</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Single-country dataset from one bank; no currency column exists.</t>
+          <t>A7 defines incoming as every PRIJEM credit, and interest is one. The previous audit listed this as an open decision; nothing in the source settles it.</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>If a second currency appeared, every sum (Q2, Q4, Q5, Q9) would be adding unlike units. There is no rule that could detect it from this schema, which is why it is written down.</t>
+          <t>Measured for 1997: interest is 7,372,897.70 of 864,692,326.70 CZK incoming (0.85%). Excluding it lowers every district's total by about that share and leaves the top-10 order unchanged.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>A20</t>
+          <t>A17</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Rounding</t>
+          <t>Dates</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Source amounts carry one decimal place, and the per-account balance chain is therefore reconciled with a tolerance (1 CZK rounding band, 100 CZK materiality band) rather than exactly.</t>
+          <t>A two-digit source year is always 19xx.</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Measured: every one of 1,056,320 amounts has a zero in the second decimal.</t>
+          <t>The dataset runs 1993-1998 and was published in 1999; there is no 20xx data.</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>631 of 4,500 accounts reconcile exactly, 4,364 within 1 CZK, 55 are off by more than 100 CZK. Without the bands the rule would report 3,869 "defects" and hide the 55 that matter.</t>
+          <t>A 20xx reading would move dates out of the validity window, which rule VAL_DATE_OUT_OF_RANGE would block -- so the assumption fails loudly rather than silently.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>A21</t>
+          <t>A18</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Entitlements</t>
+          <t>Gender</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>A user entitled to a client sees that client, the accounts that client owns, and everything hanging off those accounts. A disponent relationship does not grant the portfolio holder access to the account.</t>
+          <t>birth_number encodes sex as month + 50 for women, and that is the only available source for gender.</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>"Each user sees only rows for their own clients": ownership is the relationship a relationship manager is accountable for.</t>
+          <t>Documented with the dataset; CON_GENDER_MATCHES_BIRTH_NUMBER checks the decode against the raw digits on every run.</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Including disponent relationships would widen every portfolio; sec.portfolio_client plus the policy predicate is where that choice is changed, and it is one SQL predicate, not a model change.</t>
+          <t>Q8 is entirely built on it. The rule turns a decoder regression into a build failure.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>A22</t>
+          <t>A19</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Entitlements</t>
+          <t>Currency</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Reference data (dim_district, dim_date, ref_codes) is not entitlement filtered.</t>
+          <t>All amounts are in the same currency (CZK) and no conversion is needed.</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>They contain no client information, and filtering them would break every group-by for every user.</t>
+          <t>Single-country dataset from one bank; no currency column exists.</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>If districts were considered sensitive, the policy would be added to those tables too; nothing else in the design changes.</t>
+          <t>If a second currency appeared, every sum (Q2, Q4, Q5, Q9) would be adding unlike units. There is no rule that could detect it from this schema, which is why it is written down.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>A23</t>
+          <t>A20</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Data copy</t>
+          <t>Rounding</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>The public Berka copy is the primary dataset, because data/raw/provided/ is empty. Its row counts match the published reference exactly, so it carries no injected defects.</t>
+          <t>Source amounts carry one decimal place, and the per-account balance chain is therefore reconciled with a tolerance (1 CZK rounding band, 100 CZK materiality band) rather than exactly.</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>No bank-supplied copy was received (decision point HD1).</t>
+          <t>Measured: every one of 1,056,320 amounts has a zero in the second decimal.</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>On the bank's copy the counts would differ, REC_ROWCOUNT_RAW_TO_STG and REC_LOAN_STATUS_DISTRIBUTION would fire, and the same 123 rules would run unchanged against data/raw/provided/.</t>
+          <t>637 of 4,500 accounts reconcile exactly, 4,416 within 1 CZK, 14 are off by more than 100 CZK (largest 488.30). Without the bands the rule would report 3,863 "defects" and hide the 14 that matter. (Before D028 the figures were 631 / 4,364 / 55: 41 of the 55 came from reading the wrong closing posting, not from the source.)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>A24</t>
+          <t>A21</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>LLM</t>
+          <t>Entitlements</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>The LLM is treated as an untrusted query author: it sees the semantic layer and the question, never the database, and its SQL is parsed and rewritten before execution.</t>
+          <t>A user entitled to a client sees that client, the accounts that client owns, and everything hanging off those accounts. A disponent relationship does not grant the portfolio holder access to the account.</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>It is the only assumption under which "an LLM-generated query cannot bypass the filter" can be true.</t>
+          <t>"Each user sees only rows for their own clients": ownership is the relationship a relationship manager is accountable for.</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>If the model were trusted, the entitlement filter would have to live in the prompt -- which is a request, not a control.</t>
+          <t>Including disponent relationships would widen every portfolio; sec.portfolio_client plus the policy predicate is where that choice is changed, and it is one SQL predicate, not a model change.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>A25</t>
+          <t>A22</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>C03</t>
+          <t>Entitlements</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>The placeholder list ('', '?', 'NA', 'N/A', 'NULL', '-', 'unknown') is the complete set of ways this source writes "missing".</t>
+          <t>Reference data (dim_district, dim_date, ref_codes) is not entitlement filtered.</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>Derived by profiling every text column, not assumed up front; the profiler reports the full distinct-value distribution per column and no other placeholder-shaped value appeared.</t>
+          <t>They contain no client information, and filtering them would break every group-by for every user.</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>An eighth spelling would be counted as a real value, overstating completeness for that column. It would not corrupt anything downstream, and the profile report is where it would show up. Low risk, cheap to extend: one tuple in src/config.NULL_PLACEHOLDERS.</t>
+          <t>If districts were considered sensitive, the policy would be added to those tables too; nothing else in the design changes.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>A26</t>
+          <t>A23</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>C03, C09</t>
+          <t>Data copy</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>A NULL after cleaning means "the source did not record this", never "the pipeline lost it".</t>
+          <t>The public Berka copy is the primary dataset, because data/raw/provided/ is empty. Its row counts match the published reference exactly, so it carries no injected defects.</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Every value the cleaning dropped or changed is kept in a &lt;column&gt;_raw column and listed in _conversion_notes, so the two cases are distinguishable by construction.</t>
+          <t>No bank-supplied copy was received (decision point HD1).</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>This is the assumption the whole ledger exists to make checkable. If it were false, every completeness number would be measuring the loader rather than the source.</t>
+          <t>On the bank's copy the counts would differ, REC_ROWCOUNT_RAW_TO_STG and REC_LOAN_STATUS_DISTRIBUTION would fire, and the same 123 rules would run unchanged against data/raw/provided/.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>A27</t>
+          <t>A24</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>C09</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>operation_code IS NULL on a transaction means a bank-generated posting, not a missing value.</t>
+          <t>The LLM is treated as an untrusted query author: it sees the semantic layer and the question, never the database, and its SQL is parsed and rewritten before execution.</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>Measured: all 183,114 rows with no operation carry k_symbol = UROK (interest credited), and no other category has a NULL operation. The bank books interest without a customer-facing operation.</t>
+          <t>It is the only assumption under which "an LLM-generated query cannot bypass the filter" can be true.</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>If some of those NULLs were genuinely missing data, the completeness rule on that column would have to be warn rather than info, and "transactions by operation" would be understating one category. The measurement is re-run every build, so a mixed population would show up as UROK no longer being the only value.</t>
+          <t>If the model were trusted, the entitlement filter would have to live in the prompt -- which is a request, not a control.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>A28</t>
+          <t>A25</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>C09, D017</t>
+          <t>C03</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>The code sets are open: the source may contain a code the catalogue does not know, and the right response is to fail the build rather than guess a label.</t>
+          <t>The placeholder list ('', '?', 'NA', 'N/A', 'NULL', '-', 'unknown') is the complete set of ways this source writes "missing".</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>It already happened. LEASING appeared on 341 standing orders and was not in the map; because the catalogue check did not cover that table, nothing failed and the rows shipped unlabelled.</t>
+          <t>Derived by profiling every text column, not assumed up front; the profiler reports the full distinct-value distribution per column and no other placeholder-shaped value appeared.</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>The assumption now has teeth: check_codes_against_staging covers every coded column and tests/test_dq.py::test_every_present_code_resolves_to_a_label fails if any staged row carries a code with no label. A new code stops a build, which is the intended cost.</t>
+          <t>An eighth spelling would be counted as a real value, overstating completeness for that column. It would not corrupt anything downstream, and the profile report is where it would show up. Low risk, cheap to extend: one tuple in src/config.NULL_PLACEHOLDERS.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>A29</t>
+          <t>A26</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>C10</t>
+          <t>C03, C09</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>PRIJEM is the only credit type; VYDAJ and VYBER are both debits.</t>
+          <t>A NULL after cleaning means "the source did not record this", never "the pipeline lost it".</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>Documented with the dataset, and consistent with the reported running balance: the balance chain reconciles for 4,364 of 4,500 accounts under this sign convention and would reconcile for almost none under any other.</t>
+          <t>Every value the cleaning dropped or changed is kept in a &lt;column&gt;_raw column and listed in _conversion_notes, so the two cases are distinguishable by construction.</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Every monetary answer that nets or directs money (Q5, Q9) depends on it. The balance reconciliation rule is the check: a wrong sign convention would make it fail at scale rather than for 55 accounts.</t>
+          <t>This is the assumption the whole ledger exists to make checkable. If it were false, every completeness number would be measuring the loader rather than the source.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>A30</t>
+          <t>A27</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>C10, C20</t>
+          <t>C09</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>balance_after as reported by the bank is authoritative; the pipeline never recomputes it from the amounts.</t>
+          <t>operation_code IS NULL on a transaction means a bank-generated posting, not a missing value.</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>It is the bank's own record of the account state after the posting. Recomputing would substitute this pipeline's arithmetic for the bank's ledger.</t>
+          <t>Measured: all 183,114 rows with no operation carry k_symbol = UROK (interest credited), and no other category has a NULL operation. The bank books interest without a customer-facing operation.</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>The 55 accounts whose chain does not reconcile beyond 100 CZK are reported as a defect rather than corrected (D013). If the bank's balances were known to be unreliable, the derived balance would become the published one and those 55 would become silent.</t>
+          <t>If some of those NULLs were genuinely missing data, the completeness rule on that column would have to be warn rather than info, and "transactions by operation" would be understating one category. The measurement is re-run every build, so a mixed population would show up as UROK no longer being the only value.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>A31</t>
+          <t>A28</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>C19, C20</t>
+          <t>C09, D017</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>The extract is a point-in-time snapshot with no history: no attribute of a client, account or district changes over time within it.</t>
+          <t>The code sets are open: the source may contain a code the catalogue does not know, and the right response is to fail the build rather than guess a label.</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>There is no effective-date column anywhere in the eight files, and no table carries two versions of the same key.</t>
+          <t>It already happened. LEASING appeared on 341 standing orders and was not in the map; because the catalogue check did not cover that table, nothing failed and the rows shipped unlabelled.</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>No slowly changing dimensions are needed, which is why dim_client and dim_district are plain. A feed with history would need SCD2 on at least district attributes, since the 1995/1996 socio-economic columns are already two snapshots flattened into one row.</t>
+          <t>The assumption now has teeth: check_codes_against_staging covers every coded column and tests/test_dq.py::test_every_present_code_resolves_to_a_label fails if any staged row carries a code with no label. A new code stops a build, which is the intended cost.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>A32</t>
+          <t>A29</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>C19</t>
+          <t>C10</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>The dataset window is 1993-01-01 to 1998-12-31, and dim_date is generated to exactly that span.</t>
+          <t>PRIJEM is the only credit type; VYDAJ and VYBER are both debits.</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Measured from the data: the earliest and latest transaction dates are exactly those two days.</t>
+          <t>Documented with the dataset, and consistent with the reported running balance: the balance chain reconciles within 1 CZK for 4,416 of 4,500 accounts under this sign convention and would reconcile for almost none under any other.</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>A date outside the window would not join to dim_date and would drop out of any date-driven aggregate. VAL_DATE_OUT_OF_RANGE is the rule that makes that fail loudly rather than quietly.</t>
+          <t>Every monetary answer that nets or directs money (Q5, Q9) depends on it. The balance reconciliation rule is the check: a wrong sign convention would make it fail at scale rather than for 14 accounts.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>A33</t>
+          <t>A30</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>C16</t>
+          <t>C10, C20</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Row order within a source file carries no meaning; the only ordering is by the date and key columns.</t>
+          <t>balance_after as reported by the bank is authoritative; the pipeline never recomputes it from the amounts.</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>The files are flat extracts with no sequence column beyond the surrogate ids, and trans_id is demonstrably not chronological within a day (CON_INTRADAY_ORDER_AMBIGUOUS, 183 accounts).</t>
+          <t>It is the bank's own record of the account state after the posting. Recomputing would substitute this pipeline's arithmetic for the bank's ledger.</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>If file order were the true posting order, the Q9 tie-break would have a better answer available and those 183 accounts would stop being ambiguous. _source_row is retained on every row, so that reading could be tested without a reload.</t>
+          <t>The 14 accounts whose chain does not reconcile beyond 100 CZK are reported as a defect rather than corrected (D013). If the bank's balances were known to be unreliable, the derived balance would become the published one and those 14 would become silent. The same balances are also what orders same-day postings (D028), so this assumption now carries Q9's closing posting as well.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>A34</t>
+          <t>A31</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Identity</t>
+          <t>C19, C20</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>A self-service customer authenticates as their own database login role, and that role is never shared, pooled or re-pointed.</t>
+          <t>The extract is a point-in-time snapshot with no history: no attribute of a client, account or district changes over time within it.</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Same reasoning as A21/D009 for staff: session_user cannot be changed by any statement the caller or an LLM emits, because changing it needs a password neither ever sees.</t>
+          <t>There is no effective-date column anywhere in the eight files, and no table carries two versions of the same key.</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>This is the load-bearing assumption of the whole privacy claim. If customer logins were pooled behind one shared role, the entitlement would resolve to that shared role and every customer would see every other customer's data. Connection pooling is therefore named in the DDR as the first thing that must be redesigned, not quietly added.</t>
+          <t>No slowly changing dimensions are needed, which is why dim_client and dim_district are plain. A feed with history would need SCD2 on at least district attributes, since the 1995/1996 socio-economic columns are already two snapshots flattened into one row.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>A35</t>
+          <t>A32</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Identity</t>
+          <t>C19</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>A customer is entitled to exactly the client record that sec.app_user.subject_client_id names, and the mapping from a real person to that client id is correct and is made outside this system.</t>
+          <t>The dataset window is 1993-01-01 to 1998-12-31, and dim_date is generated to exactly that span.</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>This dataset has no identity documents, no logins and no names; the mapping from "the person at the counter" to client_id is the bank's KYC process, not a data-product concern.</t>
+          <t>Measured from the data: the earliest and latest transaction dates are exactly those two days.</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>The product enforces the mapping it is given. A wrong mapping shows the wrong person's data with the full force of a correct-looking entitlement, and nothing in this build could detect it. In a real deployment the insert into sec.app_user is the output of an identity-proofing process and should be auditable on that basis.</t>
+          <t>A date outside the window would not join to dim_date and would drop out of any date-driven aggregate. VAL_DATE_OUT_OF_RANGE is the rule that makes that fail loudly rather than quietly.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>A36</t>
+          <t>A33</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Identity</t>
+          <t>C16</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>A customer sees the accounts they own, not the accounts they may merely operate as a disponent.</t>
+          <t>Row order within a source file carries no meaning; the only ordering is by the date and key columns.</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Consistency with A21 and the safer default for a privacy boundary (D022).</t>
+          <t>The files are flat extracts with no sequence column beyond the surrogate ids, and trans_id is demonstrably not chronological within a day (CON_INTRADAY_ORDER_AMBIGUOUS, 183 accounts).</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>869 clients hold a disponent relationship. Under the other reading each of them would additionally see that account and its postings. It is one predicate in sec.v_my_accounts and it is a business decision, not a technical one.</t>
+          <t>The running balance orders 141 of those 183 (D028); 42 remain ambiguous. If file order were the true posting order, those 42 would have an answer too. _source_row is retained on every row, so that reading could be tested without a reload.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>A37</t>
+          <t>A34</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Privacy</t>
+          <t>Identity</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Reference data (districts, calendar, code catalogue) is not sensitive, so a customer may read all 77 districts even though they belong to one.</t>
+          <t>A self-service customer authenticates as their own database login role, and that role is never shared, pooled or re-pointed.</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>Same as A22: filtering it would break every group-by, and a district list reveals nothing about any client.</t>
+          <t>Same reasoning as A21/D009 for staff: session_user cannot be changed by any statement the caller or an LLM emits, because changing it needs a password neither ever sees.</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>If district-level data were considered identifying in combination with other attributes, the policy would extend to it. Nothing else in the design changes.</t>
+          <t>This is the load-bearing assumption of the whole privacy claim. If customer logins were pooled behind one shared role, the entitlement would resolve to that shared role and every customer would see every other customer's data. Connection pooling is therefore named in the DDR as the first thing that must be redesigned, not quietly added.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>A38</t>
+          <t>A35</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Privacy</t>
+          <t>Identity</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>No read audit is required for this submission.</t>
+          <t>A customer is entitled to exactly the client record that sec.app_user.subject_client_id names, and the mapping from a real person to that client id is correct and is made outside this system.</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>The brief asks who *can* see what, not what was actually read.</t>
+          <t>This dataset has no identity documents, no logins and no names; the mapping from "the person at the counter" to client_id is the bank's KYC process, not a data-product concern.</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>For a real bank this is a regulatory gap, not a simplification. It is listed in the worked example's limits and in the build review as the largest missing control.</t>
+          <t>The product enforces the mapping it is given. A wrong mapping shows the wrong person's data with the full force of a correct-looking entitlement, and nothing in this build could detect it. In a real deployment the insert into sec.app_user is the output of an identity-proofing process and should be auditable on that basis.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>A39</t>
+          <t>A36 (superseded by A39 / D023)</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Access</t>
+          <t>Identity</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>A customer may see every account they are authorised to OPERATE, including accounts they do not own.</t>
+          <t>A customer sees the accounts they own, not the accounts they may merely operate as a disponent.</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>What the bank tells its customers their app will show. Supersedes A36, which narrowed them to ownership; the decision was taken to the business reading and settled (D023).</t>
+          <t>Consistency with A21 and the safer default for a privacy boundary (D022).</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>869 clients hold a disposition on an account they do not own. Under the narrow reading each of them sees one fewer account. It is one branch in sec.v_access_grant.</t>
+          <t>869 clients hold a disponent relationship. Under the other reading each of them would additionally see that account and its postings. It is one predicate in sec.v_my_accounts and it is a business decision, not a technical one.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>A40</t>
+          <t>A37</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Access</t>
+          <t>Privacy</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>A disposition grants the ACCOUNT and nothing else -- not the owner's client record, not their other accounts.</t>
+          <t>Reference data (districts, calendar, code catalogue) is not sensitive, so a customer may read all 77 districts even though they belong to one.</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Authorising someone to pay a bill from your account is not authorising them to read you. Nobody signing that arrangement would expect otherwise.</t>
+          <t>Same as A22: filtering it would break every group-by, and a district list reveals nothing about any client.</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>If a disposition granted the owning client instead, every disponent would see their co-holder's full customer record. This is the single most consequential line in the access model, and it is tested by name.</t>
+          <t>If district-level data were considered identifying in combination with other attributes, the policy would extend to it. Nothing else in the design changes.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>A41</t>
+          <t>A38</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Access</t>
+          <t>Privacy</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>A staff portfolio grants view and never operate.</t>
+          <t>No read audit is required for this submission.</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>Being accountable for a client is not authority to move their money.</t>
+          <t>The brief asks who *can* see what, not what was actually read.</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Nothing acts on operate in this read-only product, so the distinction costs nothing today and cannot be recovered later if it is dropped now. A test pins it.</t>
+          <t>For a real bank this is a regulatory gap, not a simplification. It is listed in the worked example's limits and in the build review as the largest missing control.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>A42</t>
+          <t>A39</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Identity</t>
+          <t>Access</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>An opaque client_ref is sufficient protection for an identifier that appears in a URL or on a statement; it does not need to be rotated per session.</t>
+          <t>A customer may see every account they are authorised to OPERATE, including accounts they do not own.</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>It is unguessable without the salt, and row level security stops access regardless. The reference prevents enumeration and correlation, not access.</t>
+          <t>What the bank tells its customers their app will show. Supersedes A36, which narrowed them to ownership; the decision was taken to the business reading and settled (D023).</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>If a reference leaked in bulk, rebuilding under a new salt reissues all of them. Per-session identifiers would be stronger and would make every support conversation impossible.</t>
+          <t>869 clients hold a disposition on an account they do not own. Under the narrow reading each of them sees one fewer account. It is one branch in sec.v_access_grant.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>A43</t>
+          <t>A40</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Access</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>A time-based one-time code is an adequate second factor for this demonstration.</t>
+          <t>A disposition grants the ACCOUNT and nothing else -- not the owner's client record, not their other accounts.</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>It is the standard most people already have an app for, and it is verifiable offline against RFC 6238.</t>
+          <t>Authorising someone to pay a bill from your account is not authorising them to read you. Nobody signing that arrangement would expect otherwise.</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>TOTP is phishable in real time: a victim relaying a live code to an attacker defeats it. A deployment handling real money should prefer a phishing-resistant factor (WebAuthn/passkeys). The session model here would not change; only the factor would.</t>
+          <t>If a disposition granted the owning client instead, every disponent would see their co-holder's full customer record. This is the single most consequential line in the access model, and it is tested by name.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>A44</t>
+          <t>A41</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Access</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Storing TOTP shared secrets in a recoverable form is acceptable here.</t>
+          <t>A staff portfolio grants view and never operate.</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Verification requires the secret, so it cannot be hashed.</t>
+          <t>Being accountable for a client is not authority to move their money.</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>sec.auth_factor.secret is the most sensitive column in the schema. A real deployment encrypts it with a key held outside the database, so that a dump of the data is not a dump of everyone's second factor.</t>
+          <t>Nothing acts on operate in this read-only product, so the distinction costs nothing today and cannot be recovered later if it is dropped now. A test pins it.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>A45</t>
+          <t>A42</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Identity</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Binding a session to (db_role, pg_backend_pid) is sufficient to stop replay.</t>
+          <t>An opaque client_ref is sufficient protection for an identifier that appears in a URL or on a statement; it does not need to be rotated per session.</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>A stolen session id is useless on a different connection, and the holder cannot forge session_user either.</t>
+          <t>It is unguessable without the salt, and row level security stops access regardless. The reference prevents enumeration and correlation, not access.</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Backend pids are reused after wraparound. A replay would need the same pid, the same role and the session still inside its 30-minute window; the combination is thin but not impossible, and a production system would add the backend start time to the binding.</t>
+          <t>If a reference leaked in bulk, rebuilding under a new salt reissues all of them. Per-session identifiers would be stronger and would make every support conversation impossible.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
+          <t>A43</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>A time-based one-time code is an adequate second factor for this demonstration.</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>It is the standard most people already have an app for, and it is verifiable offline against RFC 6238.</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>TOTP is phishable in real time: a victim relaying a live code to an attacker defeats it. A deployment handling real money should prefer a phishing-resistant factor (WebAuthn/passkeys). The session model here would not change; only the factor would.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>A44</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>Storing TOTP shared secrets in a recoverable form is acceptable here.</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>Verification requires the secret, so it cannot be hashed.</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>sec.auth_factor.secret is the most sensitive column in the schema. A real deployment encrypts it with a key held outside the database, so that a dump of the data is not a dump of everyone's second factor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>A45</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>Binding a session to (db_role, pg_backend_pid) is sufficient to stop replay.</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>A stolen session id is useless on a different connection, and the holder cannot forge session_user either.</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>Backend pids are reused after wraparound. A replay would need the same pid, the same role and the session still inside its 30-minute window; the combination is thin but not impossible, and a production system would add the backend start time to the binding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
           <t>A46</t>
         </is>
       </c>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>Demo</t>
         </is>
       </c>
-      <c r="C49" s="6" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>Printing the one-time code in the demo console does not weaken the claims being demonstrated.</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t>The control being shown is what the second factor *stops*, not where the code comes from; every other part of the path is the production one.</t>
         </is>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="E52" s="6" t="inlineStr">
         <is>
           <t>A system that can display your own second factor has one factor. It is marked as a demo affordance at every call site and is the first thing a deployment removes.</t>
         </is>
